--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
   <si>
     <t xml:space="preserve">sample_id</t>
   </si>
@@ -869,27 +869,6 @@
     <t xml:space="preserve">flux_n20</t>
   </si>
   <si>
-    <t xml:space="preserve">...8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN CH4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN CO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UG CH4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UG CO2</t>
-  </si>
-  <si>
     <t xml:space="preserve">depth_id</t>
   </si>
   <si>
@@ -968,346 +947,16 @@
     <t xml:space="preserve">T</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">M</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">B</t>
   </si>
   <si>
-    <t xml:space="preserve">64.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2133.6666666666665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4447.333333333333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">18-KK130202024</t>
   </si>
   <si>
-    <t xml:space="preserve">2382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4836</t>
-  </si>
-  <si>
     <t xml:space="preserve">19-K-13022024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">457.33333333333331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13937</t>
   </si>
 </sst>
 </file>
@@ -8214,15 +7863,6 @@
       <c r="G1" t="s">
         <v>283</v>
       </c>
-      <c r="H1" t="s">
-        <v>284</v>
-      </c>
-      <c r="I1" t="s">
-        <v>285</v>
-      </c>
-      <c r="J1" t="s">
-        <v>286</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -8246,15 +7886,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.74139977587757</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.75202977425222</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -8278,15 +7909,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>288</v>
-      </c>
-      <c r="I3" t="n">
-        <v>18.5928233291599</v>
-      </c>
-      <c r="J3" t="n">
-        <v>21.3322419492014</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -8310,9 +7932,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -8336,15 +7955,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>289</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.76157894736842</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.8019938598511</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -8368,15 +7978,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>290</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.67142857142857</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11.7026655490269</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -8400,9 +8001,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -8426,9 +8024,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -8452,9 +8047,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -8478,9 +8070,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -8504,9 +8093,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -8530,9 +8116,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -8556,9 +8139,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -8582,9 +8162,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -8608,9 +8185,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -8634,9 +8208,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -8660,9 +8231,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -8686,9 +8254,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -8712,9 +8277,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -8738,9 +8300,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -8764,9 +8323,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -8790,9 +8346,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -8816,9 +8369,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -8842,9 +8392,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
@@ -8868,9 +8415,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
@@ -8894,9 +8438,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
@@ -8920,9 +8461,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
@@ -8946,9 +8484,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28"/>
-      <c r="I28"/>
-      <c r="J28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
@@ -8972,9 +8507,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
@@ -8998,9 +8530,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
@@ -9024,9 +8553,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31"/>
-      <c r="I31"/>
-      <c r="J31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
@@ -9050,9 +8576,6 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
@@ -9076,9 +8599,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
@@ -9102,9 +8622,6 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
@@ -9128,9 +8645,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
@@ -9154,9 +8668,6 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
@@ -9180,9 +8691,6 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="J37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
@@ -9206,9 +8714,6 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
@@ -9232,9 +8737,6 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
@@ -9258,9 +8760,6 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
@@ -9284,9 +8783,6 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
@@ -9310,9 +8806,6 @@
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9336,82 +8829,82 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E1" t="s">
         <v>276</v>
       </c>
       <c r="F1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K1" t="s">
+        <v>290</v>
+      </c>
+      <c r="L1" t="s">
+        <v>291</v>
+      </c>
+      <c r="M1" t="s">
         <v>292</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>293</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>294</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>295</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>296</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" t="s">
         <v>297</v>
       </c>
-      <c r="L1" t="s">
+      <c r="S1" t="s">
         <v>298</v>
       </c>
-      <c r="M1" t="s">
+      <c r="T1" t="s">
         <v>299</v>
       </c>
-      <c r="N1" t="s">
+      <c r="U1" t="s">
         <v>300</v>
       </c>
-      <c r="O1" t="s">
+      <c r="V1" t="s">
         <v>301</v>
       </c>
-      <c r="P1" t="s">
+      <c r="W1" t="s">
         <v>302</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="X1" t="s">
         <v>303</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Y1" t="s">
         <v>304</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Z1" t="s">
         <v>305</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AA1" t="s">
         <v>306</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AB1" t="s">
         <v>307</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AC1" t="s">
         <v>308</v>
-      </c>
-      <c r="W1" t="s">
-        <v>309</v>
-      </c>
-      <c r="X1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>311</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>312</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="2">
@@ -9425,7 +8918,7 @@
         <v>45022</v>
       </c>
       <c r="D2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9478,8 +8971,8 @@
       <c r="U2" t="n">
         <v>13.6</v>
       </c>
-      <c r="V2" t="s">
-        <v>317</v>
+      <c r="V2" t="n">
+        <v>38.7</v>
       </c>
       <c r="W2" t="n">
         <v>0.208673835125423</v>
@@ -9514,7 +9007,7 @@
         <v>45022</v>
       </c>
       <c r="D3" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E3" t="n">
         <v>0.65</v>
@@ -9567,8 +9060,8 @@
       <c r="U3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V3" t="s">
-        <v>319</v>
+      <c r="V3" t="n">
+        <v>32.4</v>
       </c>
       <c r="W3" t="n">
         <v>0.220000000000198</v>
@@ -9603,7 +9096,7 @@
         <v>45022</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E4" t="n">
         <v>1.31</v>
@@ -9656,8 +9149,8 @@
       <c r="U4" t="n">
         <v>66.1</v>
       </c>
-      <c r="V4" t="s">
-        <v>321</v>
+      <c r="V4" t="n">
+        <v>64.9</v>
       </c>
       <c r="W4" t="n">
         <v>0.66333333333309</v>
@@ -9692,7 +9185,7 @@
         <v>45022</v>
       </c>
       <c r="D5" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -9745,8 +9238,8 @@
       <c r="U5" t="n">
         <v>22.9</v>
       </c>
-      <c r="V5" t="s">
-        <v>322</v>
+      <c r="V5" t="n">
+        <v>88</v>
       </c>
       <c r="W5" t="n">
         <v>0.806250000000119</v>
@@ -9781,7 +9274,7 @@
         <v>45022</v>
       </c>
       <c r="D6" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
@@ -9834,8 +9327,8 @@
       <c r="U6" t="n">
         <v>31.9</v>
       </c>
-      <c r="V6" t="s">
-        <v>323</v>
+      <c r="V6" t="n">
+        <v>60</v>
       </c>
       <c r="W6" t="n">
         <v>1.30999999999991</v>
@@ -9870,7 +9363,7 @@
         <v>45022</v>
       </c>
       <c r="D7" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E7" t="n">
         <v>1.82</v>
@@ -9923,8 +9416,8 @@
       <c r="U7" t="n">
         <v>13.67</v>
       </c>
-      <c r="V7" t="s">
-        <v>324</v>
+      <c r="V7" t="n">
+        <v>25</v>
       </c>
       <c r="W7" t="n">
         <v>0.58200716845891</v>
@@ -9959,7 +9452,7 @@
         <v>45028</v>
       </c>
       <c r="D8" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10012,8 +9505,8 @@
       <c r="U8" t="n">
         <v>150</v>
       </c>
-      <c r="V8" t="s">
-        <v>325</v>
+      <c r="V8" t="n">
+        <v>100</v>
       </c>
       <c r="W8" t="n">
         <v>0.983333333333292</v>
@@ -10048,7 +9541,7 @@
         <v>45028</v>
       </c>
       <c r="D9" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
@@ -10101,8 +9594,8 @@
       <c r="U9" t="n">
         <v>51.6</v>
       </c>
-      <c r="V9" t="s">
-        <v>326</v>
+      <c r="V9" t="n">
+        <v>54.9</v>
       </c>
       <c r="W9" t="n">
         <v>0.506666666666433</v>
@@ -10137,7 +9630,7 @@
         <v>45028</v>
       </c>
       <c r="D10" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E10" t="n">
         <v>1.85</v>
@@ -10190,8 +9683,8 @@
       <c r="U10" t="n">
         <v>77.8</v>
       </c>
-      <c r="V10" t="s">
-        <v>327</v>
+      <c r="V10" t="n">
+        <v>41.2</v>
       </c>
       <c r="W10" t="n">
         <v>0.613620071684487</v>
@@ -10226,7 +9719,7 @@
         <v>45028</v>
       </c>
       <c r="D11" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10279,8 +9772,8 @@
       <c r="U11" t="n">
         <v>125.4</v>
       </c>
-      <c r="V11" t="s">
-        <v>328</v>
+      <c r="V11" t="n">
+        <v>63.6</v>
       </c>
       <c r="W11" t="n">
         <v>0.990322580645031</v>
@@ -10315,7 +9808,7 @@
         <v>45028</v>
       </c>
       <c r="D12" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -10368,8 +9861,8 @@
       <c r="U12" t="n">
         <v>78.2</v>
       </c>
-      <c r="V12" t="s">
-        <v>329</v>
+      <c r="V12" t="n">
+        <v>66</v>
       </c>
       <c r="W12" t="n">
         <v>0.500000000000095</v>
@@ -10404,7 +9897,7 @@
         <v>45028</v>
       </c>
       <c r="D13" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E13" t="n">
         <v>1.05</v>
@@ -10457,8 +9950,8 @@
       <c r="U13" t="n">
         <v>180</v>
       </c>
-      <c r="V13" t="s">
-        <v>330</v>
+      <c r="V13" t="n">
+        <v>808</v>
       </c>
       <c r="W13" t="n">
         <v>3.10469534050162</v>
@@ -10493,7 +9986,7 @@
         <v>45035</v>
       </c>
       <c r="D14" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -10546,8 +10039,8 @@
       <c r="U14" t="n">
         <v>460</v>
       </c>
-      <c r="V14" t="s">
-        <v>331</v>
+      <c r="V14" t="n">
+        <v>648</v>
       </c>
       <c r="W14" t="n">
         <v>2.72333333333326</v>
@@ -10582,7 +10075,7 @@
         <v>45035</v>
       </c>
       <c r="D15" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E15" t="n">
         <v>0.46</v>
@@ -10635,8 +10128,8 @@
       <c r="U15" t="n">
         <v>457</v>
       </c>
-      <c r="V15" t="s">
-        <v>332</v>
+      <c r="V15" t="n">
+        <v>699</v>
       </c>
       <c r="W15" t="n">
         <v>3.71999999999986</v>
@@ -10671,7 +10164,7 @@
         <v>45035</v>
       </c>
       <c r="D16" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E16" t="n">
         <v>0.92</v>
@@ -10724,8 +10217,8 @@
       <c r="U16" t="n">
         <v>457.5</v>
       </c>
-      <c r="V16" t="s">
-        <v>333</v>
+      <c r="V16" t="n">
+        <v>98.2</v>
       </c>
       <c r="W16" t="n">
         <v>1.25161290322564</v>
@@ -10760,7 +10253,7 @@
         <v>45035</v>
       </c>
       <c r="D17" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10813,8 +10306,8 @@
       <c r="U17" t="n">
         <v>449.5</v>
       </c>
-      <c r="V17" t="s">
-        <v>334</v>
+      <c r="V17" t="n">
+        <v>1142</v>
       </c>
       <c r="W17" t="n">
         <v>9.54881944444436</v>
@@ -10849,7 +10342,7 @@
         <v>45035</v>
       </c>
       <c r="D18" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E18" t="n">
         <v>0.7</v>
@@ -10902,8 +10395,8 @@
       <c r="U18" t="n">
         <v>463.5</v>
       </c>
-      <c r="V18" t="s">
-        <v>335</v>
+      <c r="V18" t="n">
+        <v>463</v>
       </c>
       <c r="W18" t="n">
         <v>2.28333333333334</v>
@@ -10938,7 +10431,7 @@
         <v>45035</v>
       </c>
       <c r="D19" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E19" t="n">
         <v>1.39</v>
@@ -10991,8 +10484,8 @@
       <c r="U19" t="n">
         <v>427.5</v>
       </c>
-      <c r="V19" t="s">
-        <v>336</v>
+      <c r="V19" t="n">
+        <v>275</v>
       </c>
       <c r="W19" t="n">
         <v>1.26555555555541</v>
@@ -11027,7 +10520,7 @@
         <v>45042</v>
       </c>
       <c r="D20" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -11080,8 +10573,8 @@
       <c r="U20" t="n">
         <v>460.5</v>
       </c>
-      <c r="V20" t="s">
-        <v>337</v>
+      <c r="V20" t="n">
+        <v>1570</v>
       </c>
       <c r="W20" t="n">
         <v>8.59536439665456</v>
@@ -11116,7 +10609,7 @@
         <v>45042</v>
       </c>
       <c r="D21" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E21" t="n">
         <v>0.7</v>
@@ -11169,8 +10662,8 @@
       <c r="U21" t="n">
         <v>460</v>
       </c>
-      <c r="V21" t="s">
-        <v>338</v>
+      <c r="V21" t="n">
+        <v>1305</v>
       </c>
       <c r="W21" t="n">
         <v>11.6066666666669</v>
@@ -11205,7 +10698,7 @@
         <v>45042</v>
       </c>
       <c r="D22" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E22" t="n">
         <v>1.41</v>
@@ -11258,8 +10751,8 @@
       <c r="U22" t="n">
         <v>461.5</v>
       </c>
-      <c r="V22" t="s">
-        <v>339</v>
+      <c r="V22" t="n">
+        <v>752</v>
       </c>
       <c r="W22" t="n">
         <v>8.39393939393942</v>
@@ -11294,7 +10787,7 @@
         <v>45042</v>
       </c>
       <c r="D23" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -11347,8 +10840,8 @@
       <c r="U23" t="n">
         <v>467.5</v>
       </c>
-      <c r="V23" t="s">
-        <v>340</v>
+      <c r="V23" t="n">
+        <v>1163</v>
       </c>
       <c r="W23" t="n">
         <v>12.5562499999998</v>
@@ -11383,7 +10876,7 @@
         <v>45042</v>
       </c>
       <c r="D24" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E24" t="n">
         <v>0.52</v>
@@ -11436,8 +10929,8 @@
       <c r="U24" t="n">
         <v>464.5</v>
       </c>
-      <c r="V24" t="s">
-        <v>341</v>
+      <c r="V24" t="n">
+        <v>1058</v>
       </c>
       <c r="W24" t="n">
         <v>8.51469534050182</v>
@@ -11472,7 +10965,7 @@
         <v>45042</v>
       </c>
       <c r="D25" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E25" t="n">
         <v>1.04</v>
@@ -11525,8 +11018,8 @@
       <c r="U25" t="n">
         <v>462</v>
       </c>
-      <c r="V25" t="s">
-        <v>342</v>
+      <c r="V25" t="n">
+        <v>1292</v>
       </c>
       <c r="W25" t="n">
         <v>10.6333333333334</v>
@@ -11561,7 +11054,7 @@
         <v>45055</v>
       </c>
       <c r="D26" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -11614,8 +11107,8 @@
       <c r="U26" t="n">
         <v>7.93</v>
       </c>
-      <c r="V26" t="s">
-        <v>324</v>
+      <c r="V26" t="n">
+        <v>25</v>
       </c>
       <c r="W26" t="n">
         <v>0.345161290322578</v>
@@ -11650,7 +11143,7 @@
         <v>45055</v>
       </c>
       <c r="D27" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E27" t="n">
         <v>1.055</v>
@@ -11703,8 +11196,8 @@
       <c r="U27" t="n">
         <v>7.38</v>
       </c>
-      <c r="V27" t="s">
-        <v>324</v>
+      <c r="V27" t="n">
+        <v>25</v>
       </c>
       <c r="W27" t="n">
         <v>0.46999999999997</v>
@@ -11739,7 +11232,7 @@
         <v>45055</v>
       </c>
       <c r="D28" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E28" t="n">
         <v>2.11</v>
@@ -11792,8 +11285,8 @@
       <c r="U28" t="n">
         <v>455</v>
       </c>
-      <c r="V28" t="s">
-        <v>343</v>
+      <c r="V28" t="n">
+        <v>1500</v>
       </c>
       <c r="W28" t="n">
         <v>19.3383333333332</v>
@@ -11828,7 +11321,7 @@
         <v>45055</v>
       </c>
       <c r="D29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -11881,8 +11374,8 @@
       <c r="U29" t="n">
         <v>924</v>
       </c>
-      <c r="V29" t="s">
-        <v>344</v>
+      <c r="V29" t="n">
+        <v>1371</v>
       </c>
       <c r="W29" t="n">
         <v>17.8129032258064</v>
@@ -11917,7 +11410,7 @@
         <v>45055</v>
       </c>
       <c r="D30" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E30" t="n">
         <v>0.45</v>
@@ -11970,8 +11463,8 @@
       <c r="U30" t="n">
         <v>400</v>
       </c>
-      <c r="V30" t="s">
-        <v>345</v>
+      <c r="V30" t="n">
+        <v>161</v>
       </c>
       <c r="W30" t="n">
         <v>1.45499999999975</v>
@@ -12006,7 +11499,7 @@
         <v>45055</v>
       </c>
       <c r="D31" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E31" t="n">
         <v>1.92</v>
@@ -12059,8 +11552,8 @@
       <c r="U31" t="n">
         <v>877</v>
       </c>
-      <c r="V31" t="s">
-        <v>346</v>
+      <c r="V31" t="n">
+        <v>828</v>
       </c>
       <c r="W31" t="n">
         <v>27.4300000000001</v>
@@ -12095,7 +11588,7 @@
         <v>45071</v>
       </c>
       <c r="D32" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -12148,8 +11641,8 @@
       <c r="U32" t="n">
         <v>256</v>
       </c>
-      <c r="V32" t="s">
-        <v>347</v>
+      <c r="V32" t="n">
+        <v>57.7</v>
       </c>
       <c r="W32" t="n">
         <v>4.97096774193547</v>
@@ -12184,7 +11677,7 @@
         <v>45071</v>
       </c>
       <c r="D33" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -12237,8 +11730,8 @@
       <c r="U33" t="n">
         <v>903.67</v>
       </c>
-      <c r="V33" t="s">
-        <v>348</v>
+      <c r="V33" t="n">
+        <v>677</v>
       </c>
       <c r="W33" t="n">
         <v>2.96129032258039</v>
@@ -12273,7 +11766,7 @@
         <v>45071</v>
       </c>
       <c r="D34" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E34" t="n">
         <v>0.55</v>
@@ -12326,8 +11819,8 @@
       <c r="U34" t="n">
         <v>887</v>
       </c>
-      <c r="V34" t="s">
-        <v>349</v>
+      <c r="V34" t="n">
+        <v>250</v>
       </c>
       <c r="W34" t="n">
         <v>1.29666666666692</v>
@@ -12362,7 +11855,7 @@
         <v>45071</v>
       </c>
       <c r="D35" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E35" t="n">
         <v>1.15</v>
@@ -12415,8 +11908,8 @@
       <c r="U35" t="n">
         <v>826</v>
       </c>
-      <c r="V35" t="s">
-        <v>350</v>
+      <c r="V35" t="n">
+        <v>110</v>
       </c>
       <c r="W35" t="n">
         <v>0.746666666666348</v>
@@ -12451,7 +11944,7 @@
         <v>45077</v>
       </c>
       <c r="D36" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -12504,8 +11997,8 @@
       <c r="U36" t="n">
         <v>188</v>
       </c>
-      <c r="V36" t="s">
-        <v>351</v>
+      <c r="V36" t="n">
+        <v>70.4</v>
       </c>
       <c r="W36" t="n">
         <v>1.13333333333353</v>
@@ -12540,7 +12033,7 @@
         <v>45077</v>
       </c>
       <c r="D37" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E37" t="n">
         <v>0.94</v>
@@ -12593,8 +12086,8 @@
       <c r="U37" t="n">
         <v>171</v>
       </c>
-      <c r="V37" t="s">
-        <v>352</v>
+      <c r="V37" t="n">
+        <v>39.1</v>
       </c>
       <c r="W37" t="n">
         <v>1.09333333333363</v>
@@ -12629,7 +12122,7 @@
         <v>45077</v>
       </c>
       <c r="D38" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E38" t="n">
         <v>1.88</v>
@@ -12682,8 +12175,8 @@
       <c r="U38" t="n">
         <v>315</v>
       </c>
-      <c r="V38" t="s">
-        <v>353</v>
+      <c r="V38" t="n">
+        <v>83.9</v>
       </c>
       <c r="W38" t="n">
         <v>1.45444444444425</v>
@@ -12718,7 +12211,7 @@
         <v>45077</v>
       </c>
       <c r="D39" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -12771,8 +12264,8 @@
       <c r="U39" t="n">
         <v>914</v>
       </c>
-      <c r="V39" t="s">
-        <v>354</v>
+      <c r="V39" t="n">
+        <v>1020</v>
       </c>
       <c r="W39" t="n">
         <v>6.29374999999976</v>
@@ -12807,7 +12300,7 @@
         <v>45077</v>
       </c>
       <c r="D40" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E40" t="n">
         <v>0.52</v>
@@ -12860,8 +12353,8 @@
       <c r="U40" t="n">
         <v>672</v>
       </c>
-      <c r="V40" t="s">
-        <v>355</v>
+      <c r="V40" t="n">
+        <v>473</v>
       </c>
       <c r="W40" t="n">
         <v>2.11666666666635</v>
@@ -12896,7 +12389,7 @@
         <v>45077</v>
       </c>
       <c r="D41" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E41" t="n">
         <v>1.04</v>
@@ -12949,8 +12442,8 @@
       <c r="U41" t="n">
         <v>862.33</v>
       </c>
-      <c r="V41" t="s">
-        <v>356</v>
+      <c r="V41" t="n">
+        <v>631</v>
       </c>
       <c r="W41" t="n">
         <v>2.49999999999994</v>
@@ -12985,7 +12478,7 @@
         <v>45077</v>
       </c>
       <c r="D42" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -13038,8 +12531,8 @@
       <c r="U42" t="n">
         <v>195</v>
       </c>
-      <c r="V42" t="s">
-        <v>324</v>
+      <c r="V42" t="n">
+        <v>25</v>
       </c>
       <c r="W42" t="n">
         <v>0.463333333333556</v>
@@ -13074,7 +12567,7 @@
         <v>45077</v>
       </c>
       <c r="D43" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E43" t="n">
         <v>0.55</v>
@@ -13127,8 +12620,8 @@
       <c r="U43" t="n">
         <v>169</v>
       </c>
-      <c r="V43" t="s">
-        <v>357</v>
+      <c r="V43" t="n">
+        <v>45.2</v>
       </c>
       <c r="W43" t="n">
         <v>0.563333333333086</v>
@@ -13163,7 +12656,7 @@
         <v>45077</v>
       </c>
       <c r="D44" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E44" t="n">
         <v>1.11</v>
@@ -13216,8 +12709,8 @@
       <c r="U44" t="n">
         <v>445</v>
       </c>
-      <c r="V44" t="s">
-        <v>358</v>
+      <c r="V44" t="n">
+        <v>223</v>
       </c>
       <c r="W44" t="n">
         <v>1.21999999999976</v>
@@ -13252,7 +12745,7 @@
         <v>45084</v>
       </c>
       <c r="D45" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -13305,8 +12798,8 @@
       <c r="U45" t="n">
         <v>633</v>
       </c>
-      <c r="V45" t="s">
-        <v>359</v>
+      <c r="V45" t="n">
+        <v>168</v>
       </c>
       <c r="W45" t="n">
         <v>1.20000000000005</v>
@@ -13341,7 +12834,7 @@
         <v>45084</v>
       </c>
       <c r="D46" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E46" t="n">
         <v>0.42</v>
@@ -13394,8 +12887,8 @@
       <c r="U46" t="n">
         <v>604</v>
       </c>
-      <c r="V46" t="s">
-        <v>360</v>
+      <c r="V46" t="n">
+        <v>156</v>
       </c>
       <c r="W46" t="n">
         <v>0.796666666666586</v>
@@ -13430,7 +12923,7 @@
         <v>45084</v>
       </c>
       <c r="D47" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E47" t="n">
         <v>0.95</v>
@@ -13483,8 +12976,8 @@
       <c r="U47" t="n">
         <v>309</v>
       </c>
-      <c r="V47" t="s">
-        <v>361</v>
+      <c r="V47" t="n">
+        <v>112</v>
       </c>
       <c r="W47" t="n">
         <v>0.813333333333333</v>
@@ -13519,7 +13012,7 @@
         <v>45084</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -13572,8 +13065,8 @@
       <c r="U48" t="n">
         <v>1748</v>
       </c>
-      <c r="V48" t="s">
-        <v>362</v>
+      <c r="V48" t="n">
+        <v>424</v>
       </c>
       <c r="W48" t="n">
         <v>4.95666666666637</v>
@@ -13608,7 +13101,7 @@
         <v>45084</v>
       </c>
       <c r="D49" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E49" t="n">
         <v>0.67</v>
@@ -13661,8 +13154,8 @@
       <c r="U49" t="n">
         <v>1752.67</v>
       </c>
-      <c r="V49" t="s">
-        <v>363</v>
+      <c r="V49" t="n">
+        <v>250</v>
       </c>
       <c r="W49" t="n">
         <v>2.89000000000025</v>
@@ -13697,7 +13190,7 @@
         <v>45084</v>
       </c>
       <c r="D50" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E50" t="n">
         <v>1.34</v>
@@ -13750,8 +13243,8 @@
       <c r="U50" t="n">
         <v>1756</v>
       </c>
-      <c r="V50" t="s">
-        <v>364</v>
+      <c r="V50" t="n">
+        <v>441</v>
       </c>
       <c r="W50" t="n">
         <v>9.8999999999999</v>
@@ -13786,7 +13279,7 @@
         <v>45085</v>
       </c>
       <c r="D51" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -13839,8 +13332,8 @@
       <c r="U51" t="n">
         <v>781</v>
       </c>
-      <c r="V51" t="s">
-        <v>365</v>
+      <c r="V51" t="n">
+        <v>561</v>
       </c>
       <c r="W51" t="n">
         <v>1.91935483870967</v>
@@ -13875,7 +13368,7 @@
         <v>45085</v>
       </c>
       <c r="D52" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E52" t="n">
         <v>0.505</v>
@@ -13928,8 +13421,8 @@
       <c r="U52" t="n">
         <v>757</v>
       </c>
-      <c r="V52" t="s">
-        <v>366</v>
+      <c r="V52" t="n">
+        <v>687</v>
       </c>
       <c r="W52" t="n">
         <v>1.87777777777774</v>
@@ -13964,7 +13457,7 @@
         <v>45085</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E53" t="n">
         <v>1.01</v>
@@ -14017,8 +13510,8 @@
       <c r="U53" t="n">
         <v>874</v>
       </c>
-      <c r="V53" t="s">
-        <v>367</v>
+      <c r="V53" t="n">
+        <v>625</v>
       </c>
       <c r="W53" t="n">
         <v>3.9393939393938</v>
@@ -14053,7 +13546,7 @@
         <v>45085</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -14106,8 +13599,8 @@
       <c r="U54" t="n">
         <v>1754.67</v>
       </c>
-      <c r="V54" t="s">
-        <v>368</v>
+      <c r="V54" t="n">
+        <v>1145</v>
       </c>
       <c r="W54" t="n">
         <v>14.736666666667</v>
@@ -14142,7 +13635,7 @@
         <v>45085</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -14195,8 +13688,8 @@
       <c r="U55" t="n">
         <v>1766</v>
       </c>
-      <c r="V55" t="s">
-        <v>369</v>
+      <c r="V55" t="n">
+        <v>629</v>
       </c>
       <c r="W55" t="n">
         <v>4.111111111111</v>
@@ -14231,7 +13724,7 @@
         <v>45085</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E56" t="n">
         <v>0.61</v>
@@ -14284,8 +13777,8 @@
       <c r="U56" t="n">
         <v>1770</v>
       </c>
-      <c r="V56" t="s">
-        <v>349</v>
+      <c r="V56" t="n">
+        <v>250</v>
       </c>
       <c r="W56" t="n">
         <v>3.19189189189223</v>
@@ -14320,7 +13813,7 @@
         <v>45085</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E57" t="n">
         <v>1.22</v>
@@ -14373,8 +13866,8 @@
       <c r="U57" t="n">
         <v>1148</v>
       </c>
-      <c r="V57" t="s">
-        <v>370</v>
+      <c r="V57" t="n">
+        <v>466</v>
       </c>
       <c r="W57" t="n">
         <v>2.93000000000016</v>
@@ -14409,7 +13902,7 @@
         <v>45098</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -14462,8 +13955,8 @@
       <c r="U58" t="n">
         <v>903</v>
       </c>
-      <c r="V58" t="s">
-        <v>371</v>
+      <c r="V58" t="n">
+        <v>462</v>
       </c>
       <c r="W58" t="n">
         <v>2.23111111111128</v>
@@ -14498,7 +13991,7 @@
         <v>45098</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E59" t="n">
         <v>0.735</v>
@@ -14551,8 +14044,8 @@
       <c r="U59" t="n">
         <v>718.33</v>
       </c>
-      <c r="V59" t="s">
-        <v>372</v>
+      <c r="V59" t="n">
+        <v>454</v>
       </c>
       <c r="W59" t="n">
         <v>1.83225806451644</v>
@@ -14587,7 +14080,7 @@
         <v>45098</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E60" t="n">
         <v>1.47</v>
@@ -14640,8 +14133,8 @@
       <c r="U60" t="n">
         <v>650</v>
       </c>
-      <c r="V60" t="s">
-        <v>373</v>
+      <c r="V60" t="n">
+        <v>237</v>
       </c>
       <c r="W60" t="n">
         <v>1.50312499999972</v>
@@ -14676,7 +14169,7 @@
         <v>45098</v>
       </c>
       <c r="D61" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -14729,8 +14222,8 @@
       <c r="U61" t="n">
         <v>414</v>
       </c>
-      <c r="V61" t="s">
-        <v>374</v>
+      <c r="V61" t="n">
+        <v>71.2</v>
       </c>
       <c r="W61" t="n">
         <v>0.975096326165162</v>
@@ -14765,7 +14258,7 @@
         <v>45098</v>
       </c>
       <c r="D62" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E62" t="n">
         <v>0.575</v>
@@ -14818,8 +14311,8 @@
       <c r="U62" t="n">
         <v>368</v>
       </c>
-      <c r="V62" t="s">
-        <v>375</v>
+      <c r="V62" t="n">
+        <v>76.9</v>
       </c>
       <c r="W62" t="n">
         <v>0.933333333333527</v>
@@ -14854,7 +14347,7 @@
         <v>45098</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E63" t="n">
         <v>1.15</v>
@@ -14907,8 +14400,8 @@
       <c r="U63" t="n">
         <v>914</v>
       </c>
-      <c r="V63" t="s">
-        <v>376</v>
+      <c r="V63" t="n">
+        <v>104</v>
       </c>
       <c r="W63" t="n">
         <v>1.15333333333325</v>
@@ -14943,7 +14436,7 @@
         <v>45306</v>
       </c>
       <c r="D64" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -14994,8 +14487,8 @@
         <v>42.4</v>
       </c>
       <c r="U64"/>
-      <c r="V64" t="s">
-        <v>377</v>
+      <c r="V64" t="n">
+        <v>228</v>
       </c>
       <c r="W64" t="n">
         <v>2.51612903225816</v>
@@ -15030,7 +14523,7 @@
         <v>45306</v>
       </c>
       <c r="D65" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E65" t="n">
         <v>1.05</v>
@@ -15081,8 +14574,8 @@
         <v>45.3</v>
       </c>
       <c r="U65"/>
-      <c r="V65" t="s">
-        <v>378</v>
+      <c r="V65" t="n">
+        <v>1288</v>
       </c>
       <c r="W65" t="n">
         <v>19.0967741935483</v>
@@ -15117,7 +14610,7 @@
         <v>45306</v>
       </c>
       <c r="D66" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E66" t="n">
         <v>2.1</v>
@@ -15168,8 +14661,8 @@
         <v>54.7</v>
       </c>
       <c r="U66"/>
-      <c r="V66" t="s">
-        <v>379</v>
+      <c r="V66" t="n">
+        <v>2133.66666666667</v>
       </c>
       <c r="W66" t="n">
         <v>41.203225806452</v>
@@ -15204,7 +14697,7 @@
         <v>45307</v>
       </c>
       <c r="D67" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -15255,8 +14748,8 @@
         <v>8.55</v>
       </c>
       <c r="U67"/>
-      <c r="V67" t="s">
-        <v>380</v>
+      <c r="V67" t="n">
+        <v>51</v>
       </c>
       <c r="W67" t="n">
         <v>0.550000000000258</v>
@@ -15291,7 +14784,7 @@
         <v>45307</v>
       </c>
       <c r="D68" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E68" t="n">
         <v>1.75</v>
@@ -15344,8 +14837,8 @@
       <c r="U68" t="n">
         <v>436</v>
       </c>
-      <c r="V68" t="s">
-        <v>381</v>
+      <c r="V68" t="n">
+        <v>73.6</v>
       </c>
       <c r="W68" t="n">
         <v>0.5246</v>
@@ -15380,7 +14873,7 @@
         <v>45307</v>
       </c>
       <c r="D69" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E69" t="n">
         <v>3.5</v>
@@ -15433,8 +14926,8 @@
       <c r="U69" t="n">
         <v>495</v>
       </c>
-      <c r="V69" t="s">
-        <v>382</v>
+      <c r="V69" t="n">
+        <v>56.6</v>
       </c>
       <c r="W69" t="n">
         <v>0.500000000000095</v>
@@ -15469,7 +14962,7 @@
         <v>45307</v>
       </c>
       <c r="D70" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -15520,8 +15013,8 @@
         <v>24</v>
       </c>
       <c r="U70"/>
-      <c r="V70" t="s">
-        <v>383</v>
+      <c r="V70" t="n">
+        <v>92.1</v>
       </c>
       <c r="W70" t="n">
         <v>0.670967741935754</v>
@@ -15556,7 +15049,7 @@
         <v>45307</v>
       </c>
       <c r="D71" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -15607,8 +15100,8 @@
         <v>15.3</v>
       </c>
       <c r="U71"/>
-      <c r="V71" t="s">
-        <v>384</v>
+      <c r="V71" t="n">
+        <v>82.6</v>
       </c>
       <c r="W71" t="n">
         <v>0.643750000000054</v>
@@ -15643,7 +15136,7 @@
         <v>45307</v>
       </c>
       <c r="D72" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E72" t="n">
         <v>2.05</v>
@@ -15694,8 +15187,8 @@
         <v>48.1</v>
       </c>
       <c r="U72"/>
-      <c r="V72" t="s">
-        <v>385</v>
+      <c r="V72" t="n">
+        <v>1867</v>
       </c>
       <c r="W72" t="n">
         <v>110.5</v>
@@ -15730,7 +15223,7 @@
         <v>45307</v>
       </c>
       <c r="D73" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -15781,8 +15274,8 @@
         <v>11.6</v>
       </c>
       <c r="U73"/>
-      <c r="V73" t="s">
-        <v>386</v>
+      <c r="V73" t="n">
+        <v>157</v>
       </c>
       <c r="W73" t="n">
         <v>0.641935483870962</v>
@@ -15817,7 +15310,7 @@
         <v>45307</v>
       </c>
       <c r="D74" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -15868,8 +15361,8 @@
         <v>35</v>
       </c>
       <c r="U74"/>
-      <c r="V74" t="s">
-        <v>387</v>
+      <c r="V74" t="n">
+        <v>1506</v>
       </c>
       <c r="W74" t="n">
         <v>79.3433333333333</v>
@@ -15904,7 +15397,7 @@
         <v>45307</v>
       </c>
       <c r="D75" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E75" t="n">
         <v>2.05</v>
@@ -15957,8 +15450,8 @@
       <c r="U75" t="n">
         <v>5440</v>
       </c>
-      <c r="V75" t="s">
-        <v>388</v>
+      <c r="V75" t="n">
+        <v>1771</v>
       </c>
       <c r="W75" t="n">
         <v>216.451991341991</v>
@@ -15993,7 +15486,7 @@
         <v>45307</v>
       </c>
       <c r="D76" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -16044,8 +15537,8 @@
       <c r="U76" t="n">
         <v>1016</v>
       </c>
-      <c r="V76" t="s">
-        <v>389</v>
+      <c r="V76" t="n">
+        <v>1373</v>
       </c>
       <c r="W76" t="n">
         <v>0.603030303030297</v>
@@ -16080,7 +15573,7 @@
         <v>45307</v>
       </c>
       <c r="D77" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -16133,8 +15626,8 @@
       <c r="U77" t="n">
         <v>2375</v>
       </c>
-      <c r="V77" t="s">
-        <v>390</v>
+      <c r="V77" t="n">
+        <v>743</v>
       </c>
       <c r="W77" t="n">
         <v>48.7586206896552</v>
@@ -16169,7 +15662,7 @@
         <v>45307</v>
       </c>
       <c r="D78" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E78" t="n">
         <v>2.05</v>
@@ -16222,8 +15715,8 @@
       <c r="U78" t="n">
         <v>685</v>
       </c>
-      <c r="V78" t="s">
-        <v>391</v>
+      <c r="V78" t="n">
+        <v>60.2</v>
       </c>
       <c r="W78" t="n">
         <v>136.876923076923</v>
@@ -16258,7 +15751,7 @@
         <v>45313</v>
       </c>
       <c r="D79" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -16311,8 +15804,8 @@
       <c r="U79" t="n">
         <v>296</v>
       </c>
-      <c r="V79" t="s">
-        <v>392</v>
+      <c r="V79" t="n">
+        <v>96.6</v>
       </c>
       <c r="W79" t="n">
         <v>1.18620689655165</v>
@@ -16347,7 +15840,7 @@
         <v>45313</v>
       </c>
       <c r="D80" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E80" t="n">
         <v>1.35</v>
@@ -16400,8 +15893,8 @@
       <c r="U80" t="n">
         <v>260</v>
       </c>
-      <c r="V80" t="s">
-        <v>393</v>
+      <c r="V80" t="n">
+        <v>81.6</v>
       </c>
       <c r="W80" t="n">
         <v>1.26451612903206</v>
@@ -16436,7 +15929,7 @@
         <v>45313</v>
       </c>
       <c r="D81" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E81" t="n">
         <v>2.7</v>
@@ -16489,8 +15982,8 @@
       <c r="U81" t="n">
         <v>2103.33333333333</v>
       </c>
-      <c r="V81" t="s">
-        <v>394</v>
+      <c r="V81" t="n">
+        <v>1267</v>
       </c>
       <c r="W81" t="n">
         <v>4.54838709677437</v>
@@ -16525,7 +16018,7 @@
         <v>45314</v>
       </c>
       <c r="D82" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -16578,8 +16071,8 @@
       <c r="U82" t="n">
         <v>236</v>
       </c>
-      <c r="V82" t="s">
-        <v>395</v>
+      <c r="V82" t="n">
+        <v>71.1</v>
       </c>
       <c r="W82" t="n">
         <v>0.709090909090979</v>
@@ -16614,7 +16107,7 @@
         <v>45314</v>
       </c>
       <c r="D83" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E83" t="n">
         <v>0.7</v>
@@ -16667,8 +16160,8 @@
       <c r="U83" t="n">
         <v>294</v>
       </c>
-      <c r="V83" t="s">
-        <v>396</v>
+      <c r="V83" t="n">
+        <v>92.9</v>
       </c>
       <c r="W83" t="n">
         <v>0.71999999999998</v>
@@ -16703,7 +16196,7 @@
         <v>45314</v>
       </c>
       <c r="D84" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E84" t="n">
         <v>1.85</v>
@@ -16756,8 +16249,8 @@
       <c r="U84" t="n">
         <v>4746.66666666667</v>
       </c>
-      <c r="V84" t="s">
-        <v>397</v>
+      <c r="V84" t="n">
+        <v>2598</v>
       </c>
       <c r="W84" t="n">
         <v>37.8898412698412</v>
@@ -16792,7 +16285,7 @@
         <v>45320</v>
       </c>
       <c r="D85" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -16845,8 +16338,8 @@
       <c r="U85" t="n">
         <v>109</v>
       </c>
-      <c r="V85" t="s">
-        <v>398</v>
+      <c r="V85" t="n">
+        <v>79.5</v>
       </c>
       <c r="W85" t="n">
         <v>0.874193548387008</v>
@@ -16881,7 +16374,7 @@
         <v>45320</v>
       </c>
       <c r="D86" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E86" t="n">
         <v>0.5</v>
@@ -16934,8 +16427,8 @@
       <c r="U86" t="n">
         <v>795</v>
       </c>
-      <c r="V86" t="s">
-        <v>399</v>
+      <c r="V86" t="n">
+        <v>3785</v>
       </c>
       <c r="W86" t="n">
         <v>10.4656249999999</v>
@@ -16970,7 +16463,7 @@
         <v>45320</v>
       </c>
       <c r="D87" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E87" t="n">
         <v>1.05</v>
@@ -17021,7 +16514,7 @@
         <v>45320</v>
       </c>
       <c r="D88" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -17074,8 +16567,8 @@
       <c r="U88" t="n">
         <v>83</v>
       </c>
-      <c r="V88" t="s">
-        <v>400</v>
+      <c r="V88" t="n">
+        <v>85.6</v>
       </c>
       <c r="W88" t="n">
         <v>0.606250000000141</v>
@@ -17110,7 +16603,7 @@
         <v>45320</v>
       </c>
       <c r="D89" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E89" t="n">
         <v>0.5</v>
@@ -17163,8 +16656,8 @@
       <c r="U89" t="n">
         <v>2430</v>
       </c>
-      <c r="V89" t="s">
-        <v>401</v>
+      <c r="V89" t="n">
+        <v>5718</v>
       </c>
       <c r="W89" t="n">
         <v>110.45</v>
@@ -17199,7 +16692,7 @@
         <v>45320</v>
       </c>
       <c r="D90" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -17250,7 +16743,7 @@
         <v>45321</v>
       </c>
       <c r="D91" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -17303,8 +16796,8 @@
       <c r="U91" t="n">
         <v>340</v>
       </c>
-      <c r="V91" t="s">
-        <v>402</v>
+      <c r="V91" t="n">
+        <v>167</v>
       </c>
       <c r="W91" t="n">
         <v>0.759374999999896</v>
@@ -17339,7 +16832,7 @@
         <v>45321</v>
       </c>
       <c r="D92" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E92" t="n">
         <v>1.18</v>
@@ -17392,8 +16885,8 @@
       <c r="U92" t="n">
         <v>256</v>
       </c>
-      <c r="V92" t="s">
-        <v>403</v>
+      <c r="V92" t="n">
+        <v>164</v>
       </c>
       <c r="W92" t="n">
         <v>0.753333333333472</v>
@@ -17428,7 +16921,7 @@
         <v>45321</v>
       </c>
       <c r="D93" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E93" t="n">
         <v>2.34</v>
@@ -17481,8 +16974,8 @@
       <c r="U93" t="n">
         <v>3620</v>
       </c>
-      <c r="V93" t="s">
-        <v>404</v>
+      <c r="V93" t="n">
+        <v>7710</v>
       </c>
       <c r="W93" t="n">
         <v>27.0857142857141</v>
@@ -17517,7 +17010,7 @@
         <v>45321</v>
       </c>
       <c r="D94" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -17570,8 +17063,8 @@
       <c r="U94" t="n">
         <v>671</v>
       </c>
-      <c r="V94" t="s">
-        <v>405</v>
+      <c r="V94" t="n">
+        <v>1811</v>
       </c>
       <c r="W94" t="n">
         <v>2.4827586206895</v>
@@ -17606,7 +17099,7 @@
         <v>45321</v>
       </c>
       <c r="D95" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E95" t="n">
         <v>1.08</v>
@@ -17659,8 +17152,8 @@
       <c r="U95" t="n">
         <v>597</v>
       </c>
-      <c r="V95" t="s">
-        <v>406</v>
+      <c r="V95" t="n">
+        <v>361</v>
       </c>
       <c r="W95" t="n">
         <v>1.03225806451624</v>
@@ -17695,7 +17188,7 @@
         <v>45321</v>
       </c>
       <c r="D96" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E96" t="n">
         <v>2.15</v>
@@ -17748,8 +17241,8 @@
       <c r="U96" t="n">
         <v>6336.66666666667</v>
       </c>
-      <c r="V96" t="s">
-        <v>407</v>
+      <c r="V96" t="n">
+        <v>2212</v>
       </c>
       <c r="W96" t="n">
         <v>13.079063146998</v>
@@ -17784,7 +17277,7 @@
         <v>45321</v>
       </c>
       <c r="D97" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -17837,8 +17330,8 @@
       <c r="U97" t="n">
         <v>417</v>
       </c>
-      <c r="V97" t="s">
-        <v>408</v>
+      <c r="V97" t="n">
+        <v>302</v>
       </c>
       <c r="W97" t="n">
         <v>1.4033333333335</v>
@@ -17873,7 +17366,7 @@
         <v>45321</v>
       </c>
       <c r="D98" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E98" t="n">
         <v>1.5</v>
@@ -17926,8 +17419,8 @@
       <c r="U98" t="n">
         <v>239</v>
       </c>
-      <c r="V98" t="s">
-        <v>409</v>
+      <c r="V98" t="n">
+        <v>215</v>
       </c>
       <c r="W98" t="n">
         <v>1.03333333333329</v>
@@ -17962,7 +17455,7 @@
         <v>45321</v>
       </c>
       <c r="D99" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E99" t="n">
         <v>3</v>
@@ -18015,8 +17508,8 @@
       <c r="U99" t="n">
         <v>4140</v>
       </c>
-      <c r="V99" t="s">
-        <v>410</v>
+      <c r="V99" t="n">
+        <v>4447.33333333333</v>
       </c>
       <c r="W99" t="n">
         <v>87.3266666666675</v>
@@ -18051,7 +17544,7 @@
         <v>45327</v>
       </c>
       <c r="D100" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -18104,8 +17597,8 @@
       <c r="U100" t="n">
         <v>2530</v>
       </c>
-      <c r="V100" t="s">
-        <v>411</v>
+      <c r="V100" t="n">
+        <v>1131</v>
       </c>
       <c r="W100" t="n">
         <v>42.1689655172415</v>
@@ -18140,7 +17633,7 @@
         <v>45327</v>
       </c>
       <c r="D101" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E101" t="n">
         <v>0.9</v>
@@ -18191,8 +17684,8 @@
       <c r="U101" t="n">
         <v>7460</v>
       </c>
-      <c r="V101" t="s">
-        <v>412</v>
+      <c r="V101" t="n">
+        <v>1767</v>
       </c>
       <c r="W101" t="n">
         <v>29.4444444444445</v>
@@ -18227,7 +17720,7 @@
         <v>45327</v>
       </c>
       <c r="D102" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E102" t="n">
         <v>1.8</v>
@@ -18278,7 +17771,7 @@
         <v>45328</v>
       </c>
       <c r="D103" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -18331,8 +17824,8 @@
       <c r="U103" t="n">
         <v>1325</v>
       </c>
-      <c r="V103" t="s">
-        <v>413</v>
+      <c r="V103" t="n">
+        <v>376</v>
       </c>
       <c r="W103" t="n">
         <v>7.5764705882354</v>
@@ -18367,7 +17860,7 @@
         <v>45328</v>
       </c>
       <c r="D104" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E104" t="n">
         <v>0.9</v>
@@ -18420,8 +17913,8 @@
       <c r="U104" t="n">
         <v>960</v>
       </c>
-      <c r="V104" t="s">
-        <v>360</v>
+      <c r="V104" t="n">
+        <v>156</v>
       </c>
       <c r="W104" t="n">
         <v>1.0531250000001</v>
@@ -18456,7 +17949,7 @@
         <v>45328</v>
       </c>
       <c r="D105" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E105" t="n">
         <v>1.8</v>
@@ -18509,8 +18002,8 @@
       <c r="U105" t="n">
         <v>5140</v>
       </c>
-      <c r="V105" t="s">
-        <v>414</v>
+      <c r="V105" t="n">
+        <v>2049</v>
       </c>
       <c r="W105" t="n">
         <v>138.51052631579</v>
@@ -18545,7 +18038,7 @@
         <v>45328</v>
       </c>
       <c r="D106" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -18598,8 +18091,8 @@
       <c r="U106" t="n">
         <v>2190</v>
       </c>
-      <c r="V106" t="s">
-        <v>415</v>
+      <c r="V106" t="n">
+        <v>9000</v>
       </c>
       <c r="W106" t="n">
         <v>36.0227272727271</v>
@@ -18634,7 +18127,7 @@
         <v>45328</v>
       </c>
       <c r="D107" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E107" t="n">
         <v>0.8</v>
@@ -18687,8 +18180,8 @@
       <c r="U107" t="n">
         <v>7280</v>
       </c>
-      <c r="V107" t="s">
-        <v>416</v>
+      <c r="V107" t="n">
+        <v>2733</v>
       </c>
       <c r="W107" t="n">
         <v>126.633333333333</v>
@@ -18723,7 +18216,7 @@
         <v>45328</v>
       </c>
       <c r="D108" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E108" t="n">
         <v>1.65</v>
@@ -18774,7 +18267,7 @@
         <v>45334</v>
       </c>
       <c r="D109" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -18827,8 +18320,8 @@
       <c r="U109" t="n">
         <v>95.5</v>
       </c>
-      <c r="V109" t="s">
-        <v>417</v>
+      <c r="V109" t="n">
+        <v>42.1</v>
       </c>
       <c r="W109" t="n">
         <v>0.596875000000052</v>
@@ -18863,7 +18356,7 @@
         <v>45334</v>
       </c>
       <c r="D110" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E110" t="n">
         <v>0.7</v>
@@ -18916,8 +18409,8 @@
       <c r="U110" t="n">
         <v>64.5</v>
       </c>
-      <c r="V110" t="s">
-        <v>418</v>
+      <c r="V110" t="n">
+        <v>36.4</v>
       </c>
       <c r="W110" t="n">
         <v>0.532258064516149</v>
@@ -18952,7 +18445,7 @@
         <v>45334</v>
       </c>
       <c r="D111" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E111" t="n">
         <v>1.35</v>
@@ -19005,8 +18498,8 @@
       <c r="U111" t="n">
         <v>1360</v>
       </c>
-      <c r="V111" t="s">
-        <v>419</v>
+      <c r="V111" t="n">
+        <v>2980</v>
       </c>
       <c r="W111" t="n">
         <v>25.6399999999999</v>
@@ -19041,7 +18534,7 @@
         <v>45334</v>
       </c>
       <c r="D112" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -19094,8 +18587,8 @@
       <c r="U112" t="n">
         <v>139</v>
       </c>
-      <c r="V112" t="s">
-        <v>420</v>
+      <c r="V112" t="n">
+        <v>66.3</v>
       </c>
       <c r="W112" t="n">
         <v>1.05555555555546</v>
@@ -19130,7 +18623,7 @@
         <v>45334</v>
       </c>
       <c r="D113" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -19183,8 +18676,8 @@
       <c r="U113" t="n">
         <v>147.5</v>
       </c>
-      <c r="V113" t="s">
-        <v>421</v>
+      <c r="V113" t="n">
+        <v>86.9</v>
       </c>
       <c r="W113" t="n">
         <v>0.950000000000006</v>
@@ -19219,7 +18712,7 @@
         <v>45334</v>
       </c>
       <c r="D114" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E114" t="n">
         <v>4</v>
@@ -19272,8 +18765,8 @@
       <c r="U114" t="n">
         <v>124</v>
       </c>
-      <c r="V114" t="s">
-        <v>422</v>
+      <c r="V114" t="n">
+        <v>78.7</v>
       </c>
       <c r="W114" t="n">
         <v>0.829999999999842</v>
@@ -19299,7 +18792,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>423</v>
+        <v>312</v>
       </c>
       <c r="B115" t="s">
         <v>266</v>
@@ -19308,7 +18801,7 @@
         <v>45335</v>
       </c>
       <c r="D115" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -19361,8 +18854,8 @@
       <c r="U115" t="n">
         <v>2770</v>
       </c>
-      <c r="V115" t="s">
-        <v>424</v>
+      <c r="V115" t="n">
+        <v>2382</v>
       </c>
       <c r="W115" t="n">
         <v>8.78666666666656</v>
@@ -19388,7 +18881,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>423</v>
+        <v>312</v>
       </c>
       <c r="B116" t="s">
         <v>266</v>
@@ -19397,7 +18890,7 @@
         <v>45335</v>
       </c>
       <c r="D116" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E116" t="n">
         <v>0.9</v>
@@ -19450,8 +18943,8 @@
       <c r="U116" t="n">
         <v>2930</v>
       </c>
-      <c r="V116" t="s">
-        <v>425</v>
+      <c r="V116" t="n">
+        <v>2027</v>
       </c>
       <c r="W116" t="n">
         <v>6.40666666666666</v>
@@ -19477,7 +18970,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>423</v>
+        <v>312</v>
       </c>
       <c r="B117" t="s">
         <v>266</v>
@@ -19486,7 +18979,7 @@
         <v>45335</v>
       </c>
       <c r="D117" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E117" t="n">
         <v>1.8</v>
@@ -19539,8 +19032,8 @@
       <c r="U117" t="n">
         <v>2720</v>
       </c>
-      <c r="V117" t="s">
-        <v>426</v>
+      <c r="V117" t="n">
+        <v>4836</v>
       </c>
       <c r="W117" t="n">
         <v>14.1518082788671</v>
@@ -19566,7 +19059,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>427</v>
+        <v>313</v>
       </c>
       <c r="B118" t="s">
         <v>271</v>
@@ -19575,7 +19068,7 @@
         <v>45335</v>
       </c>
       <c r="D118" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -19628,8 +19121,8 @@
       <c r="U118" t="n">
         <v>3680</v>
       </c>
-      <c r="V118" t="s">
-        <v>428</v>
+      <c r="V118" t="n">
+        <v>457.333333333333</v>
       </c>
       <c r="W118" t="n">
         <v>2.89000000000001</v>
@@ -19655,7 +19148,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>427</v>
+        <v>313</v>
       </c>
       <c r="B119" t="s">
         <v>271</v>
@@ -19664,7 +19157,7 @@
         <v>45335</v>
       </c>
       <c r="D119" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E119" t="n">
         <v>1.05</v>
@@ -19717,8 +19210,8 @@
       <c r="U119" t="n">
         <v>306</v>
       </c>
-      <c r="V119" t="s">
-        <v>429</v>
+      <c r="V119" t="n">
+        <v>305</v>
       </c>
       <c r="W119" t="n">
         <v>2.82199999999996</v>
@@ -19744,7 +19237,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>427</v>
+        <v>313</v>
       </c>
       <c r="B120" t="s">
         <v>271</v>
@@ -19753,7 +19246,7 @@
         <v>45335</v>
       </c>
       <c r="D120" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E120" t="n">
         <v>2.15</v>
@@ -19806,8 +19299,8 @@
       <c r="U120" t="n">
         <v>1980</v>
       </c>
-      <c r="V120" t="s">
-        <v>430</v>
+      <c r="V120" t="n">
+        <v>13937</v>
       </c>
       <c r="W120" t="n">
         <v>95.6499999999998</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
   <si>
     <t xml:space="preserve">sample_id</t>
   </si>
@@ -167,9 +167,6 @@
     <t xml:space="preserve">Fiberglass</t>
   </si>
   <si>
-    <t xml:space="preserve">I don't know</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
@@ -197,12 +194,6 @@
     <t xml:space="preserve">Technician/Mason</t>
   </si>
   <si>
-    <t xml:space="preserve">Every 15 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na</t>
-  </si>
-  <si>
     <t xml:space="preserve">Old pipe, holding tank with pump, suspects leaking groundwater in winter, contents of tank very clear</t>
   </si>
   <si>
@@ -218,12 +209,6 @@
     <t xml:space="preserve">Bleach</t>
   </si>
   <si>
-    <t xml:space="preserve">Don't know - bought house less than 6 years ago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thick scum layer, two households connected (one main and one airbnb, equalization tank pumps both to septic field.</t>
   </si>
   <si>
@@ -242,9 +227,6 @@
     <t xml:space="preserve">Kitchen Laundry Bathing Toilet</t>
   </si>
   <si>
-    <t xml:space="preserve">5 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Septic field above - pumps up, 6 bathrooms, 2 kitchens, second chamber sampled</t>
   </si>
   <si>
@@ -263,9 +245,6 @@
     <t xml:space="preserve">Toilet Bathing</t>
   </si>
   <si>
-    <t xml:space="preserve">6 ish years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cement lined lid, two chambered</t>
   </si>
   <si>
@@ -281,9 +260,6 @@
     <t xml:space="preserve">Paper Water</t>
   </si>
   <si>
-    <t xml:space="preserve">Every 5 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thick scum layer</t>
   </si>
   <si>
@@ -305,9 +281,6 @@
     <t xml:space="preserve">Professional engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Twice per year</t>
-  </si>
-  <si>
     <t xml:space="preserve">Commercial place</t>
   </si>
   <si>
@@ -320,12 +293,6 @@
     <t xml:space="preserve">Leech field</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every ten years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pump issue, pink scum layer</t>
   </si>
   <si>
@@ -383,12 +350,6 @@
     <t xml:space="preserve">Pro-pump septic packets</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2000000000000002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-6 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Very shallow, only took one sample, bio additives added.</t>
   </si>
   <si>
@@ -416,12 +377,6 @@
     <t xml:space="preserve">Toilet Kitchen</t>
   </si>
   <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-7 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Community Hall Pender Island</t>
   </si>
   <si>
@@ -458,9 +413,6 @@
     <t xml:space="preserve">PVC or plastic</t>
   </si>
   <si>
-    <t xml:space="preserve">3-5 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Household deep cove</t>
   </si>
   <si>
@@ -482,9 +434,6 @@
     <t xml:space="preserve">Regular household cleaners</t>
   </si>
   <si>
-    <t xml:space="preserve">Every 2-3 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pender Island household</t>
   </si>
   <si>
@@ -500,12 +449,6 @@
     <t xml:space="preserve">Water</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9-10 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Could not measure volume; double thick scum layer</t>
   </si>
   <si>
@@ -521,9 +464,6 @@
     <t xml:space="preserve">10a</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Golf Course</t>
   </si>
   <si>
@@ -578,9 +518,6 @@
     <t xml:space="preserve">Kitchen Toilet Bathing Laundry</t>
   </si>
   <si>
-    <t xml:space="preserve">Every two years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Feminine products, plastic</t>
   </si>
   <si>
@@ -593,9 +530,6 @@
     <t xml:space="preserve">12b</t>
   </si>
   <si>
-    <t xml:space="preserve">Every 2 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 tanks compound - 2nd tank</t>
   </si>
   <si>
@@ -632,9 +566,6 @@
     <t xml:space="preserve">Toilet Bathing Kitchen</t>
   </si>
   <si>
-    <t xml:space="preserve">1 every two years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apartments "sandec"</t>
   </si>
   <si>
@@ -656,9 +587,6 @@
     <t xml:space="preserve">System has never been emptied</t>
   </si>
   <si>
-    <t xml:space="preserve">Just new</t>
-  </si>
-  <si>
     <t xml:space="preserve">Some plastic waste</t>
   </si>
   <si>
@@ -707,9 +635,6 @@
     <t xml:space="preserve">Kitchen Bathing Laundry</t>
   </si>
   <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apartments - two tanks (grey water)</t>
   </si>
   <si>
@@ -731,9 +656,6 @@
     <t xml:space="preserve">16c</t>
   </si>
   <si>
-    <t xml:space="preserve">Every 4 months</t>
-  </si>
-  <si>
     <t xml:space="preserve">Condoms, plastic wrappers, etc</t>
   </si>
   <si>
@@ -752,9 +674,6 @@
     <t xml:space="preserve">Standpipe outside building</t>
   </si>
   <si>
-    <t xml:space="preserve">1 in every 6 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Feminine products</t>
   </si>
   <si>
@@ -791,9 +710,6 @@
     <t xml:space="preserve">19a</t>
   </si>
   <si>
-    <t xml:space="preserve">Once a year</t>
-  </si>
-  <si>
     <t xml:space="preserve">Condoms</t>
   </si>
   <si>
@@ -818,9 +734,6 @@
     <t xml:space="preserve">20a</t>
   </si>
   <si>
-    <t xml:space="preserve">Every 5 months</t>
-  </si>
-  <si>
     <t xml:space="preserve">Feminine products, condoms, plastic</t>
   </si>
   <si>
@@ -831,9 +744,6 @@
   </si>
   <si>
     <t xml:space="preserve">20b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 times a year</t>
   </si>
   <si>
     <t xml:space="preserve">Plastic and feminine products</t>
@@ -1458,20 +1368,18 @@
       <c r="M2" t="s">
         <v>45</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2"/>
+      <c r="O2" t="s">
         <v>50</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>51</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>53</v>
-      </c>
-      <c r="R2" t="s">
-        <v>54</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1484,49 +1392,47 @@
       </c>
       <c r="V2"/>
       <c r="W2" t="s">
+        <v>54</v>
+      </c>
+      <c r="X2" t="s">
         <v>55</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD2" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="s">
         <v>57</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>58</v>
       </c>
-      <c r="AH2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI2" t="s">
+      <c r="AI2"/>
+      <c r="AJ2" t="s">
         <v>50</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>60</v>
+      <c r="AK2" t="n">
+        <v>15</v>
       </c>
       <c r="AL2" t="s">
         <v>45</v>
@@ -1534,19 +1440,17 @@
       <c r="AM2" t="s">
         <v>45</v>
       </c>
-      <c r="AN2" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN2"/>
       <c r="AO2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>45022</v>
@@ -1581,20 +1485,18 @@
       <c r="M3" t="s">
         <v>45</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3"/>
+      <c r="O3" t="s">
         <v>50</v>
       </c>
-      <c r="O3" t="s">
-        <v>51</v>
-      </c>
       <c r="P3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="s">
+        <v>52</v>
+      </c>
+      <c r="R3" t="s">
         <v>53</v>
-      </c>
-      <c r="R3" t="s">
-        <v>54</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1607,75 +1509,69 @@
       </c>
       <c r="V3"/>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="X3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD3" t="s">
         <v>56</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="s">
         <v>57</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>58</v>
       </c>
-      <c r="AH3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="AI3"/>
+      <c r="AJ3" t="s">
         <v>50</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>67</v>
-      </c>
+      <c r="AK3"/>
       <c r="AL3" t="s">
         <v>45</v>
       </c>
       <c r="AM3" t="s">
         <v>45</v>
       </c>
-      <c r="AN3" t="s">
-        <v>68</v>
-      </c>
+      <c r="AN3"/>
       <c r="AO3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>44</v>
@@ -1687,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I4" t="s">
         <v>46</v>
@@ -1695,29 +1591,25 @@
       <c r="J4" t="s">
         <v>47</v>
       </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
+      <c r="K4"/>
       <c r="L4" t="s">
         <v>49</v>
       </c>
       <c r="M4" t="s">
         <v>45</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4"/>
+      <c r="O4" t="s">
         <v>50</v>
       </c>
-      <c r="O4" t="s">
-        <v>51</v>
-      </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="Q4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" t="s">
         <v>53</v>
-      </c>
-      <c r="R4" t="s">
-        <v>54</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1729,11 +1621,9 @@
         <v>45</v>
       </c>
       <c r="V4"/>
-      <c r="W4" t="s">
-        <v>68</v>
-      </c>
+      <c r="W4"/>
       <c r="X4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
@@ -1748,31 +1638,29 @@
         <v>1</v>
       </c>
       <c r="AC4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="s">
         <v>57</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>58</v>
       </c>
-      <c r="AH4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="AI4"/>
+      <c r="AJ4" t="s">
         <v>50</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>75</v>
+      <c r="AK4" t="n">
+        <v>5</v>
       </c>
       <c r="AL4" t="s">
         <v>45</v>
@@ -1780,25 +1668,23 @@
       <c r="AM4" t="s">
         <v>45</v>
       </c>
-      <c r="AN4" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN4"/>
       <c r="AO4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>44</v>
@@ -1810,7 +1696,7 @@
         <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
         <v>46</v>
@@ -1822,25 +1708,25 @@
         <v>48</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M5" t="s">
         <v>45</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q5" t="s">
+        <v>52</v>
+      </c>
+      <c r="R5" t="s">
         <v>53</v>
-      </c>
-      <c r="R5" t="s">
-        <v>54</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1852,11 +1738,9 @@
         <v>45</v>
       </c>
       <c r="V5"/>
-      <c r="W5" t="s">
-        <v>61</v>
-      </c>
+      <c r="W5"/>
       <c r="X5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
@@ -1871,31 +1755,29 @@
         <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="s">
         <v>57</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="s">
+      <c r="AH5" t="s">
         <v>58</v>
       </c>
-      <c r="AH5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI5" t="s">
+      <c r="AI5"/>
+      <c r="AJ5" t="s">
         <v>50</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>82</v>
+      <c r="AK5" t="n">
+        <v>6</v>
       </c>
       <c r="AL5" t="s">
         <v>45</v>
@@ -1903,25 +1785,23 @@
       <c r="AM5" t="s">
         <v>45</v>
       </c>
-      <c r="AN5" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN5"/>
       <c r="AO5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -1945,25 +1825,25 @@
         <v>48</v>
       </c>
       <c r="L6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M6" t="s">
         <v>45</v>
       </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P6" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R6" t="s">
         <v>80</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>53</v>
-      </c>
-      <c r="R6" t="s">
-        <v>87</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1975,50 +1855,46 @@
         <v>45</v>
       </c>
       <c r="V6"/>
-      <c r="W6" t="s">
-        <v>61</v>
-      </c>
+      <c r="W6"/>
       <c r="X6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD6" t="s">
         <v>56</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="s">
         <v>57</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="s">
+      <c r="AH6" t="s">
         <v>58</v>
       </c>
-      <c r="AH6" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI6" t="s">
+      <c r="AI6"/>
+      <c r="AJ6" t="s">
         <v>50</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>88</v>
+      <c r="AK6" t="n">
+        <v>5</v>
       </c>
       <c r="AL6" t="s">
         <v>45</v>
@@ -2026,28 +1902,26 @@
       <c r="AM6" t="s">
         <v>45</v>
       </c>
-      <c r="AN6" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN6"/>
       <c r="AO6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
         <v>410</v>
@@ -2055,12 +1929,8 @@
       <c r="G7" t="n">
         <v>0.0833333333333333</v>
       </c>
-      <c r="H7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" t="s">
-        <v>68</v>
-      </c>
+      <c r="H7"/>
+      <c r="I7"/>
       <c r="J7" t="s">
         <v>47</v>
       </c>
@@ -2068,25 +1938,25 @@
         <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M7" t="s">
         <v>45</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="Q7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" t="s">
         <v>53</v>
-      </c>
-      <c r="R7" t="s">
-        <v>54</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -2098,11 +1968,9 @@
         <v>45</v>
       </c>
       <c r="V7"/>
-      <c r="W7" t="s">
-        <v>61</v>
-      </c>
+      <c r="W7"/>
       <c r="X7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="Y7" t="n">
         <v>1</v>
@@ -2117,31 +1985,29 @@
         <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="s">
         <v>57</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>58</v>
-      </c>
       <c r="AH7" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI7"/>
+      <c r="AJ7" t="s">
         <v>50</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>96</v>
+      <c r="AK7" t="n">
+        <v>0.5</v>
       </c>
       <c r="AL7" t="s">
         <v>45</v>
@@ -2149,25 +2015,23 @@
       <c r="AM7" t="s">
         <v>45</v>
       </c>
-      <c r="AN7" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN7"/>
       <c r="AO7" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
         <v>44</v>
@@ -2191,25 +2055,25 @@
         <v>48</v>
       </c>
       <c r="L8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M8" t="s">
         <v>45</v>
       </c>
       <c r="N8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="Q8" t="s">
+        <v>52</v>
+      </c>
+      <c r="R8" t="s">
         <v>53</v>
-      </c>
-      <c r="R8" t="s">
-        <v>54</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -2221,50 +2085,48 @@
         <v>45</v>
       </c>
       <c r="V8"/>
-      <c r="W8" t="s">
-        <v>61</v>
-      </c>
+      <c r="W8"/>
       <c r="X8" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD8" t="s">
         <v>56</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="s">
         <v>57</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="s">
+      <c r="AH8" t="s">
         <v>58</v>
       </c>
-      <c r="AH8" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>101</v>
+      <c r="AI8" t="n">
+        <v>4.5</v>
       </c>
       <c r="AJ8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>102</v>
+        <v>50</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>10</v>
       </c>
       <c r="AL8" t="s">
         <v>45</v>
@@ -2272,25 +2134,23 @@
       <c r="AM8" t="s">
         <v>45</v>
       </c>
-      <c r="AN8" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN8"/>
       <c r="AO8" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>44</v>
@@ -2320,19 +2180,19 @@
         <v>45</v>
       </c>
       <c r="N9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P9" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="Q9" t="s">
+        <v>52</v>
+      </c>
+      <c r="R9" t="s">
         <v>53</v>
-      </c>
-      <c r="R9" t="s">
-        <v>54</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -2344,30 +2204,28 @@
         <v>45</v>
       </c>
       <c r="V9"/>
-      <c r="W9" t="s">
-        <v>61</v>
-      </c>
+      <c r="W9"/>
       <c r="X9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD9" t="s">
         <v>56</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>57</v>
-      </c>
       <c r="AE9" t="n">
         <v>1</v>
       </c>
@@ -2375,48 +2233,40 @@
         <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="AH9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI9"/>
+      <c r="AJ9"/>
+      <c r="AK9"/>
       <c r="AL9" t="s">
         <v>45</v>
       </c>
       <c r="AM9" t="s">
         <v>45</v>
       </c>
-      <c r="AN9" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN9"/>
       <c r="AO9" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F10" t="n">
         <v>304</v>
@@ -2424,38 +2274,34 @@
       <c r="G10" t="n">
         <v>2.5</v>
       </c>
-      <c r="H10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I10" t="s">
-        <v>68</v>
-      </c>
+      <c r="H10"/>
+      <c r="I10"/>
       <c r="J10" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="K10" t="s">
         <v>48</v>
       </c>
       <c r="L10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M10" t="s">
         <v>45</v>
       </c>
       <c r="N10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P10" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" t="s">
         <v>53</v>
-      </c>
-      <c r="R10" t="s">
-        <v>54</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -2467,79 +2313,69 @@
         <v>45</v>
       </c>
       <c r="V10"/>
-      <c r="W10" t="s">
-        <v>61</v>
-      </c>
+      <c r="W10"/>
       <c r="X10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD10" t="s">
         <v>56</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD10" t="s">
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="s">
         <v>57</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>58</v>
-      </c>
       <c r="AH10" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI10"/>
+      <c r="AJ10"/>
+      <c r="AK10"/>
       <c r="AL10" t="s">
         <v>45</v>
       </c>
       <c r="AM10" t="s">
         <v>45</v>
       </c>
-      <c r="AN10" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN10"/>
       <c r="AO10" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F11" t="n">
         <v>368</v>
@@ -2547,38 +2383,34 @@
       <c r="G11" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>68</v>
-      </c>
+      <c r="H11"/>
+      <c r="I11"/>
       <c r="J11" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="K11" t="s">
         <v>48</v>
       </c>
       <c r="L11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M11" t="s">
         <v>45</v>
       </c>
       <c r="N11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="s">
+        <v>52</v>
+      </c>
+      <c r="R11" t="s">
         <v>53</v>
-      </c>
-      <c r="R11" t="s">
-        <v>54</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -2590,76 +2422,66 @@
         <v>45</v>
       </c>
       <c r="V11"/>
-      <c r="W11" t="s">
-        <v>61</v>
-      </c>
+      <c r="W11"/>
       <c r="X11" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD11" t="s">
         <v>56</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD11" t="s">
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="s">
         <v>57</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>58</v>
-      </c>
       <c r="AH11" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI11"/>
+      <c r="AJ11"/>
+      <c r="AK11"/>
       <c r="AL11" t="s">
         <v>45</v>
       </c>
       <c r="AM11" t="s">
         <v>45</v>
       </c>
-      <c r="AN11" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN11"/>
       <c r="AO11" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>44</v>
@@ -2683,26 +2505,26 @@
         <v>48</v>
       </c>
       <c r="L12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M12" t="s">
         <v>45</v>
       </c>
       <c r="N12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P12" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>52</v>
+      </c>
+      <c r="R12" t="s">
         <v>80</v>
       </c>
-      <c r="Q12" t="s">
-        <v>53</v>
-      </c>
-      <c r="R12" t="s">
-        <v>87</v>
-      </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
@@ -2710,55 +2532,55 @@
         <v>1</v>
       </c>
       <c r="U12" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="V12" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="W12" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="X12" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD12" t="s">
         <v>56</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD12" t="s">
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="s">
         <v>57</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="s">
+      <c r="AH12" t="s">
         <v>58</v>
       </c>
-      <c r="AH12" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>122</v>
+      <c r="AI12" t="n">
+        <v>2.2</v>
       </c>
       <c r="AJ12" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>123</v>
+        <v>50</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>5.5</v>
       </c>
       <c r="AL12" t="s">
         <v>45</v>
@@ -2766,25 +2588,23 @@
       <c r="AM12" t="s">
         <v>45</v>
       </c>
-      <c r="AN12" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN12"/>
       <c r="AO12" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>44</v>
@@ -2804,30 +2624,28 @@
       <c r="J13" t="s">
         <v>47</v>
       </c>
-      <c r="K13" t="s">
-        <v>50</v>
-      </c>
+      <c r="K13"/>
       <c r="L13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M13" t="s">
         <v>45</v>
       </c>
       <c r="N13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q13" t="s">
+        <v>52</v>
+      </c>
+      <c r="R13" t="s">
         <v>53</v>
       </c>
-      <c r="R13" t="s">
-        <v>54</v>
-      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
@@ -2835,55 +2653,51 @@
         <v>0</v>
       </c>
       <c r="U13" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="V13" t="s">
-        <v>127</v>
-      </c>
-      <c r="W13" t="s">
-        <v>61</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="W13"/>
       <c r="X13" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD13" t="s">
         <v>56</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD13" t="s">
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="s">
         <v>57</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>58</v>
-      </c>
       <c r="AH13" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI13"/>
+      <c r="AJ13" t="s">
         <v>50</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>75</v>
+      <c r="AK13" t="n">
+        <v>5</v>
       </c>
       <c r="AL13" t="s">
         <v>45</v>
@@ -2891,19 +2705,17 @@
       <c r="AM13" t="s">
         <v>45</v>
       </c>
-      <c r="AN13" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN13"/>
       <c r="AO13" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -2912,7 +2724,7 @@
         <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -2920,12 +2732,8 @@
       <c r="G14" t="n">
         <v>5</v>
       </c>
-      <c r="H14" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" t="s">
-        <v>68</v>
-      </c>
+      <c r="H14"/>
+      <c r="I14"/>
       <c r="J14" t="s">
         <v>47</v>
       </c>
@@ -2933,25 +2741,25 @@
         <v>48</v>
       </c>
       <c r="L14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M14" t="s">
         <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q14" t="s">
+        <v>52</v>
+      </c>
+      <c r="R14" t="s">
         <v>53</v>
-      </c>
-      <c r="R14" t="s">
-        <v>54</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2963,11 +2771,9 @@
         <v>45</v>
       </c>
       <c r="V14"/>
-      <c r="W14" t="s">
-        <v>61</v>
-      </c>
+      <c r="W14"/>
       <c r="X14" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="Y14" t="n">
         <v>1</v>
@@ -2982,31 +2788,31 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="s">
         <v>57</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="s">
+      <c r="AH14" t="s">
         <v>58</v>
       </c>
-      <c r="AH14" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>133</v>
+      <c r="AI14" t="n">
+        <v>8</v>
       </c>
       <c r="AJ14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>134</v>
+        <v>50</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>6</v>
       </c>
       <c r="AL14" t="s">
         <v>45</v>
@@ -3014,19 +2820,17 @@
       <c r="AM14" t="s">
         <v>45</v>
       </c>
-      <c r="AN14" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN14"/>
       <c r="AO14" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -3044,7 +2848,7 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
         <v>46</v>
@@ -3056,25 +2860,25 @@
         <v>48</v>
       </c>
       <c r="L15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M15" t="s">
         <v>45</v>
       </c>
       <c r="N15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P15" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="Q15" t="s">
+        <v>52</v>
+      </c>
+      <c r="R15" t="s">
         <v>53</v>
-      </c>
-      <c r="R15" t="s">
-        <v>54</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -3087,49 +2891,47 @@
       </c>
       <c r="V15"/>
       <c r="W15" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="X15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD15" t="s">
         <v>56</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD15" t="s">
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="s">
         <v>57</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="s">
+      <c r="AH15" t="s">
         <v>58</v>
       </c>
-      <c r="AH15" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI15" t="s">
+      <c r="AI15"/>
+      <c r="AJ15" t="s">
         <v>50</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>123</v>
+      <c r="AK15" t="n">
+        <v>5.5</v>
       </c>
       <c r="AL15" t="s">
         <v>45</v>
@@ -3137,19 +2939,17 @@
       <c r="AM15" t="s">
         <v>45</v>
       </c>
-      <c r="AN15" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN15"/>
       <c r="AO15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -3158,7 +2958,7 @@
         <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -3166,12 +2966,8 @@
       <c r="G16" t="n">
         <v>0.5</v>
       </c>
-      <c r="H16" t="s">
-        <v>68</v>
-      </c>
-      <c r="I16" t="s">
-        <v>68</v>
-      </c>
+      <c r="H16"/>
+      <c r="I16"/>
       <c r="J16" t="s">
         <v>47</v>
       </c>
@@ -3179,25 +2975,23 @@
         <v>48</v>
       </c>
       <c r="L16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M16" t="s">
         <v>45</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16"/>
+      <c r="O16" t="s">
         <v>50</v>
       </c>
-      <c r="O16" t="s">
-        <v>51</v>
-      </c>
       <c r="P16" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>52</v>
+      </c>
+      <c r="R16" t="s">
         <v>80</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" t="s">
-        <v>87</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -3209,11 +3003,9 @@
         <v>45</v>
       </c>
       <c r="V16"/>
-      <c r="W16" t="s">
-        <v>61</v>
-      </c>
+      <c r="W16"/>
       <c r="X16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="Y16" t="n">
         <v>1</v>
@@ -3228,57 +3020,51 @@
         <v>0</v>
       </c>
       <c r="AC16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="s">
         <v>57</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="s">
+      <c r="AH16" t="s">
         <v>58</v>
       </c>
-      <c r="AH16" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI16" t="s">
+      <c r="AI16"/>
+      <c r="AJ16" t="s">
         <v>50</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>50</v>
-      </c>
+      <c r="AK16"/>
       <c r="AL16" t="s">
         <v>45</v>
       </c>
       <c r="AM16" t="s">
         <v>45</v>
       </c>
-      <c r="AN16" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN16"/>
       <c r="AO16" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>44</v>
@@ -3302,25 +3088,25 @@
         <v>48</v>
       </c>
       <c r="L17" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="M17" t="s">
         <v>45</v>
       </c>
       <c r="N17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P17" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q17" t="s">
+        <v>52</v>
+      </c>
+      <c r="R17" t="s">
         <v>53</v>
-      </c>
-      <c r="R17" t="s">
-        <v>54</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -3332,50 +3118,46 @@
         <v>45</v>
       </c>
       <c r="V17"/>
-      <c r="W17" t="s">
-        <v>61</v>
-      </c>
+      <c r="W17"/>
       <c r="X17" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD17" t="s">
         <v>56</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD17" t="s">
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="s">
         <v>57</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="s">
+      <c r="AH17" t="s">
         <v>58</v>
       </c>
-      <c r="AH17" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI17" t="s">
+      <c r="AI17"/>
+      <c r="AJ17" t="s">
         <v>50</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>147</v>
+      <c r="AK17" t="n">
+        <v>4</v>
       </c>
       <c r="AL17" t="s">
         <v>45</v>
@@ -3383,25 +3165,23 @@
       <c r="AM17" t="s">
         <v>45</v>
       </c>
-      <c r="AN17" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN17"/>
       <c r="AO17" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>44</v>
@@ -3425,25 +3205,25 @@
         <v>48</v>
       </c>
       <c r="L18" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M18" t="s">
         <v>45</v>
       </c>
       <c r="N18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P18" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q18" t="s">
+        <v>52</v>
+      </c>
+      <c r="R18" t="s">
         <v>53</v>
-      </c>
-      <c r="R18" t="s">
-        <v>54</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -3455,50 +3235,46 @@
         <v>45</v>
       </c>
       <c r="V18"/>
-      <c r="W18" t="s">
-        <v>61</v>
-      </c>
+      <c r="W18"/>
       <c r="X18" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD18" t="s">
         <v>56</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD18" t="s">
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="s">
         <v>57</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="s">
+      <c r="AH18" t="s">
         <v>58</v>
       </c>
-      <c r="AH18" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI18" t="s">
+      <c r="AI18"/>
+      <c r="AJ18" t="s">
         <v>50</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>88</v>
+      <c r="AK18" t="n">
+        <v>5</v>
       </c>
       <c r="AL18" t="s">
         <v>45</v>
@@ -3506,19 +3282,17 @@
       <c r="AM18" t="s">
         <v>45</v>
       </c>
-      <c r="AN18" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN18"/>
       <c r="AO18" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -3548,26 +3322,26 @@
         <v>48</v>
       </c>
       <c r="L19" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M19" t="s">
         <v>45</v>
       </c>
       <c r="N19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q19" t="s">
+        <v>52</v>
+      </c>
+      <c r="R19" t="s">
         <v>53</v>
       </c>
-      <c r="R19" t="s">
-        <v>54</v>
-      </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
@@ -3575,55 +3349,51 @@
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>119</v>
-      </c>
-      <c r="V19" t="s">
+        <v>108</v>
+      </c>
+      <c r="V19"/>
+      <c r="W19" t="s">
+        <v>138</v>
+      </c>
+      <c r="X19" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="s">
         <v>50</v>
       </c>
-      <c r="W19" t="s">
-        <v>154</v>
-      </c>
-      <c r="X19" t="s">
+      <c r="AD19" t="s">
         <v>56</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD19" t="s">
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="s">
         <v>57</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="s">
+      <c r="AH19" t="s">
         <v>58</v>
       </c>
-      <c r="AH19" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI19" t="s">
+      <c r="AI19"/>
+      <c r="AJ19" t="s">
         <v>50</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>155</v>
+      <c r="AK19" t="n">
+        <v>2.5</v>
       </c>
       <c r="AL19" t="s">
         <v>45</v>
@@ -3631,19 +3401,17 @@
       <c r="AM19" t="s">
         <v>45</v>
       </c>
-      <c r="AN19" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN19"/>
       <c r="AO19" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -3661,10 +3429,10 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J20" t="s">
         <v>47</v>
@@ -3673,25 +3441,25 @@
         <v>48</v>
       </c>
       <c r="L20" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M20" t="s">
         <v>45</v>
       </c>
       <c r="N20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P20" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R20" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -3703,50 +3471,48 @@
         <v>45</v>
       </c>
       <c r="V20"/>
-      <c r="W20" t="s">
-        <v>61</v>
-      </c>
+      <c r="W20"/>
       <c r="X20" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD20" t="s">
         <v>56</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD20" t="s">
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="s">
         <v>57</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="s">
+      <c r="AH20" t="s">
         <v>58</v>
       </c>
-      <c r="AH20" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>161</v>
+      <c r="AI20" t="n">
+        <v>2.4</v>
       </c>
       <c r="AJ20" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>162</v>
+        <v>50</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>9.5</v>
       </c>
       <c r="AL20" t="s">
         <v>45</v>
@@ -3754,19 +3520,17 @@
       <c r="AM20" t="s">
         <v>45</v>
       </c>
-      <c r="AN20" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN20"/>
       <c r="AO20" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -3796,25 +3560,25 @@
         <v>48</v>
       </c>
       <c r="L21" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M21" t="s">
         <v>45</v>
       </c>
       <c r="N21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P21" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q21" t="s">
+        <v>52</v>
+      </c>
+      <c r="R21" t="s">
         <v>53</v>
-      </c>
-      <c r="R21" t="s">
-        <v>54</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3826,50 +3590,48 @@
         <v>45</v>
       </c>
       <c r="V21"/>
-      <c r="W21" t="s">
-        <v>61</v>
-      </c>
+      <c r="W21"/>
       <c r="X21" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD21" t="s">
         <v>56</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD21" t="s">
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="s">
         <v>57</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="s">
+      <c r="AH21" t="s">
         <v>58</v>
       </c>
-      <c r="AH21" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>161</v>
+      <c r="AI21" t="n">
+        <v>2.4</v>
       </c>
       <c r="AJ21" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>88</v>
+        <v>50</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>5</v>
       </c>
       <c r="AL21" t="s">
         <v>45</v>
@@ -3877,19 +3639,17 @@
       <c r="AM21" t="s">
         <v>45</v>
       </c>
-      <c r="AN21" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN21"/>
       <c r="AO21" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -3898,7 +3658,7 @@
         <v>43</v>
       </c>
       <c r="E22" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
         <v>200</v>
@@ -3906,12 +3666,8 @@
       <c r="G22" t="n">
         <v>0.25</v>
       </c>
-      <c r="H22" t="s">
-        <v>68</v>
-      </c>
-      <c r="I22" t="s">
-        <v>68</v>
-      </c>
+      <c r="H22"/>
+      <c r="I22"/>
       <c r="J22" t="s">
         <v>47</v>
       </c>
@@ -3919,25 +3675,25 @@
         <v>48</v>
       </c>
       <c r="L22" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M22" t="s">
         <v>45</v>
       </c>
       <c r="N22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P22" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q22" t="s">
+        <v>52</v>
+      </c>
+      <c r="R22" t="s">
         <v>53</v>
-      </c>
-      <c r="R22" t="s">
-        <v>54</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3949,11 +3705,9 @@
         <v>45</v>
       </c>
       <c r="V22"/>
-      <c r="W22" t="s">
-        <v>61</v>
-      </c>
+      <c r="W22"/>
       <c r="X22" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="Y22" t="n">
         <v>1</v>
@@ -3968,31 +3722,31 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD22" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="s">
         <v>57</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="s">
+      <c r="AH22" t="s">
         <v>58</v>
       </c>
-      <c r="AH22" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>168</v>
+      <c r="AI22" t="n">
+        <v>5</v>
       </c>
       <c r="AJ22" t="s">
         <v>45</v>
       </c>
-      <c r="AK22" t="s">
-        <v>123</v>
+      <c r="AK22" t="n">
+        <v>5.5</v>
       </c>
       <c r="AL22" t="s">
         <v>45</v>
@@ -4000,25 +3754,23 @@
       <c r="AM22" t="s">
         <v>45</v>
       </c>
-      <c r="AN22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN22"/>
       <c r="AO22" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="E23" t="s">
         <v>44</v>
@@ -4042,25 +3794,25 @@
         <v>48</v>
       </c>
       <c r="L23" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M23" t="s">
         <v>45</v>
       </c>
       <c r="N23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P23" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q23" t="s">
+        <v>52</v>
+      </c>
+      <c r="R23" t="s">
         <v>53</v>
-      </c>
-      <c r="R23" t="s">
-        <v>54</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -4072,11 +3824,9 @@
         <v>45</v>
       </c>
       <c r="V23"/>
-      <c r="W23" t="s">
-        <v>61</v>
-      </c>
+      <c r="W23"/>
       <c r="X23" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="Y23" t="n">
         <v>1</v>
@@ -4091,60 +3841,54 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="s">
         <v>57</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="s">
+      <c r="AH23" t="s">
         <v>58</v>
       </c>
-      <c r="AH23" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI23" t="s">
+      <c r="AI23"/>
+      <c r="AJ23" t="s">
         <v>50</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK23" t="s">
-        <v>50</v>
-      </c>
+      <c r="AK23"/>
       <c r="AL23" t="s">
         <v>45</v>
       </c>
       <c r="AM23" t="s">
         <v>45</v>
       </c>
-      <c r="AN23" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN23"/>
       <c r="AO23" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D24" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F24" t="n">
         <v>23</v>
@@ -4155,9 +3899,7 @@
       <c r="H24" t="s">
         <v>45</v>
       </c>
-      <c r="I24" t="s">
-        <v>68</v>
-      </c>
+      <c r="I24"/>
       <c r="J24" t="s">
         <v>47</v>
       </c>
@@ -4165,7 +3907,7 @@
         <v>48</v>
       </c>
       <c r="L24" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M24" t="s">
         <v>45</v>
@@ -4174,16 +3916,16 @@
         <v>45</v>
       </c>
       <c r="O24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P24" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R24" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -4196,10 +3938,10 @@
       </c>
       <c r="V24"/>
       <c r="W24" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X24" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="Y24" t="n">
         <v>1</v>
@@ -4214,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD24" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4226,45 +3968,39 @@
         <v>1</v>
       </c>
       <c r="AG24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI24"/>
+      <c r="AJ24"/>
+      <c r="AK24"/>
       <c r="AL24" t="s">
         <v>45</v>
       </c>
       <c r="AM24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN24" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="AO24" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D25" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E25" t="s">
         <v>44</v>
@@ -4276,10 +4012,10 @@
         <v>3</v>
       </c>
       <c r="H25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I25" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J25" t="s">
         <v>47</v>
@@ -4288,7 +4024,7 @@
         <v>48</v>
       </c>
       <c r="L25" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M25" t="s">
         <v>45</v>
@@ -4297,16 +4033,16 @@
         <v>45</v>
       </c>
       <c r="O25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P25" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R25" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -4319,10 +4055,10 @@
       </c>
       <c r="V25"/>
       <c r="W25" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X25" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
@@ -4337,10 +4073,10 @@
         <v>1</v>
       </c>
       <c r="AC25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD25" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4349,45 +4085,43 @@
         <v>1</v>
       </c>
       <c r="AG25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH25" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI25"/>
       <c r="AJ25" t="s">
         <v>45</v>
       </c>
-      <c r="AK25" t="s">
-        <v>187</v>
+      <c r="AK25" t="n">
+        <v>2</v>
       </c>
       <c r="AL25" t="s">
         <v>45</v>
       </c>
       <c r="AM25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN25" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="AO25" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
@@ -4399,10 +4133,10 @@
         <v>3</v>
       </c>
       <c r="H26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I26" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J26" t="s">
         <v>47</v>
@@ -4411,7 +4145,7 @@
         <v>48</v>
       </c>
       <c r="L26" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M26" t="s">
         <v>45</v>
@@ -4420,16 +4154,16 @@
         <v>45</v>
       </c>
       <c r="O26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R26" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -4442,10 +4176,10 @@
       </c>
       <c r="V26"/>
       <c r="W26" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X26" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="Y26" t="n">
         <v>1</v>
@@ -4460,10 +4194,10 @@
         <v>1</v>
       </c>
       <c r="AC26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD26" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4472,45 +4206,43 @@
         <v>1</v>
       </c>
       <c r="AG26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH26" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI26"/>
       <c r="AJ26" t="s">
         <v>45</v>
       </c>
-      <c r="AK26" t="s">
-        <v>192</v>
+      <c r="AK26" t="n">
+        <v>2</v>
       </c>
       <c r="AL26" t="s">
         <v>45</v>
       </c>
       <c r="AM26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN26" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="AO26" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D27" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
         <v>44</v>
@@ -4522,10 +4254,10 @@
         <v>3</v>
       </c>
       <c r="H27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I27" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J27" t="s">
         <v>47</v>
@@ -4534,7 +4266,7 @@
         <v>48</v>
       </c>
       <c r="L27" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M27" t="s">
         <v>45</v>
@@ -4543,16 +4275,16 @@
         <v>45</v>
       </c>
       <c r="O27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R27" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -4565,10 +4297,10 @@
       </c>
       <c r="V27"/>
       <c r="W27" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X27" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="Y27" t="n">
         <v>1</v>
@@ -4583,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="AC27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD27" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4595,45 +4327,43 @@
         <v>1</v>
       </c>
       <c r="AG27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH27" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI27"/>
       <c r="AJ27" t="s">
         <v>45</v>
       </c>
-      <c r="AK27" t="s">
-        <v>192</v>
+      <c r="AK27" t="n">
+        <v>2</v>
       </c>
       <c r="AL27" t="s">
         <v>45</v>
       </c>
       <c r="AM27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN27" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="AO27" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E28" t="s">
         <v>44</v>
@@ -4645,10 +4375,10 @@
         <v>3</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I28" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J28" t="s">
         <v>47</v>
@@ -4657,7 +4387,7 @@
         <v>48</v>
       </c>
       <c r="L28" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M28" t="s">
         <v>45</v>
@@ -4666,16 +4396,16 @@
         <v>45</v>
       </c>
       <c r="O28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R28" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -4688,10 +4418,10 @@
       </c>
       <c r="V28"/>
       <c r="W28" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X28" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="Y28" t="n">
         <v>1</v>
@@ -4706,10 +4436,10 @@
         <v>1</v>
       </c>
       <c r="AC28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD28" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4718,45 +4448,43 @@
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH28" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI28" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI28"/>
       <c r="AJ28" t="s">
         <v>45</v>
       </c>
-      <c r="AK28" t="s">
-        <v>192</v>
+      <c r="AK28" t="n">
+        <v>2</v>
       </c>
       <c r="AL28" t="s">
         <v>45</v>
       </c>
       <c r="AM28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN28" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="AO28" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="E29" t="s">
         <v>44</v>
@@ -4768,10 +4496,10 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I29" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J29" t="s">
         <v>47</v>
@@ -4780,25 +4508,25 @@
         <v>48</v>
       </c>
       <c r="L29" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N29" t="s">
         <v>45</v>
       </c>
       <c r="O29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P29" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R29" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4811,10 +4539,10 @@
       </c>
       <c r="V29"/>
       <c r="W29" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X29" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="Y29" t="n">
         <v>1</v>
@@ -4829,10 +4557,10 @@
         <v>1</v>
       </c>
       <c r="AC29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD29" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4841,19 +4569,17 @@
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH29" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI29" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI29"/>
+      <c r="AJ29" t="s">
         <v>50</v>
       </c>
-      <c r="AJ29" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK29" t="s">
-        <v>205</v>
+      <c r="AK29" t="n">
+        <v>1</v>
       </c>
       <c r="AL29" t="s">
         <v>45</v>
@@ -4861,25 +4587,23 @@
       <c r="AM29" t="s">
         <v>45</v>
       </c>
-      <c r="AN29" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN29"/>
       <c r="AO29" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D30" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
         <v>44</v>
@@ -4891,10 +4615,10 @@
         <v>10</v>
       </c>
       <c r="H30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I30" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J30" t="s">
         <v>47</v>
@@ -4903,7 +4627,7 @@
         <v>48</v>
       </c>
       <c r="L30" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M30" t="s">
         <v>45</v>
@@ -4912,16 +4636,16 @@
         <v>45</v>
       </c>
       <c r="O30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P30" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R30" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4930,16 +4654,14 @@
         <v>1</v>
       </c>
       <c r="U30" t="s">
-        <v>51</v>
-      </c>
-      <c r="V30" t="s">
         <v>50</v>
       </c>
+      <c r="V30"/>
       <c r="W30" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="X30" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="Y30" t="n">
         <v>1</v>
@@ -4954,10 +4676,10 @@
         <v>1</v>
       </c>
       <c r="AC30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD30" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -4966,45 +4688,41 @@
         <v>1</v>
       </c>
       <c r="AG30" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="AH30" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>50</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="AI30"/>
       <c r="AJ30" t="s">
-        <v>212</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>213</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="AK30"/>
       <c r="AL30" t="s">
         <v>45</v>
       </c>
       <c r="AM30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN30" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="AO30" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D31" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E31" t="s">
         <v>44</v>
@@ -5016,10 +4734,10 @@
         <v>10</v>
       </c>
       <c r="H31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I31" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J31" t="s">
         <v>47</v>
@@ -5028,7 +4746,7 @@
         <v>48</v>
       </c>
       <c r="L31" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M31" t="s">
         <v>45</v>
@@ -5037,16 +4755,16 @@
         <v>45</v>
       </c>
       <c r="O31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P31" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R31" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -5058,11 +4776,9 @@
         <v>45</v>
       </c>
       <c r="V31"/>
-      <c r="W31" t="s">
-        <v>61</v>
-      </c>
+      <c r="W31"/>
       <c r="X31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y31" t="n">
         <v>1</v>
@@ -5077,10 +4793,10 @@
         <v>1</v>
       </c>
       <c r="AC31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD31" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5089,48 +4805,44 @@
         <v>1</v>
       </c>
       <c r="AG31" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="AH31" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI31"/>
       <c r="AJ31" t="s">
-        <v>212</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>68</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="AK31"/>
       <c r="AL31" t="s">
         <v>45</v>
       </c>
       <c r="AM31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN31" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="AO31" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D32" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F32" t="n">
         <v>35</v>
@@ -5141,17 +4853,15 @@
       <c r="H32" t="s">
         <v>45</v>
       </c>
-      <c r="I32" t="s">
-        <v>68</v>
-      </c>
+      <c r="I32"/>
       <c r="J32" t="s">
         <v>47</v>
       </c>
       <c r="K32" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="L32" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="M32" t="s">
         <v>45</v>
@@ -5160,16 +4870,16 @@
         <v>45</v>
       </c>
       <c r="O32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P32" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R32" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -5177,15 +4887,13 @@
       <c r="T32" t="n">
         <v>1</v>
       </c>
-      <c r="U32" t="s">
-        <v>50</v>
-      </c>
+      <c r="U32"/>
       <c r="V32"/>
       <c r="W32" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X32" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="Y32" t="n">
         <v>1</v>
@@ -5200,10 +4908,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD32" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5212,45 +4920,39 @@
         <v>1</v>
       </c>
       <c r="AG32" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI32" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="AH32"/>
+      <c r="AI32"/>
+      <c r="AJ32"/>
+      <c r="AK32" t="n">
+        <v>5</v>
       </c>
       <c r="AL32" t="s">
         <v>45</v>
       </c>
       <c r="AM32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN32" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="AO32" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D33" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E33" t="s">
         <v>44</v>
@@ -5262,10 +4964,10 @@
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I33" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J33" t="s">
         <v>47</v>
@@ -5274,7 +4976,7 @@
         <v>48</v>
       </c>
       <c r="L33" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M33" t="s">
         <v>45</v>
@@ -5283,16 +4985,16 @@
         <v>45</v>
       </c>
       <c r="O33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P33" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R33" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -5305,10 +5007,10 @@
       </c>
       <c r="V33"/>
       <c r="W33" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X33" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -5323,10 +5025,10 @@
         <v>1</v>
       </c>
       <c r="AC33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD33" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5335,19 +5037,19 @@
         <v>1</v>
       </c>
       <c r="AG33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH33" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI33" t="s">
-        <v>230</v>
+        <v>87</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>20</v>
       </c>
       <c r="AJ33" t="s">
         <v>45</v>
       </c>
-      <c r="AK33" t="s">
-        <v>187</v>
+      <c r="AK33" t="n">
+        <v>2</v>
       </c>
       <c r="AL33" t="s">
         <v>45</v>
@@ -5355,25 +5057,23 @@
       <c r="AM33" t="s">
         <v>45</v>
       </c>
-      <c r="AN33" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN33"/>
       <c r="AO33" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D34" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E34" t="s">
         <v>44</v>
@@ -5385,10 +5085,10 @@
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I34" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J34" t="s">
         <v>47</v>
@@ -5397,7 +5097,7 @@
         <v>48</v>
       </c>
       <c r="L34" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M34" t="s">
         <v>45</v>
@@ -5406,16 +5106,16 @@
         <v>45</v>
       </c>
       <c r="O34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R34" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -5428,10 +5128,10 @@
       </c>
       <c r="V34"/>
       <c r="W34" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X34" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="Y34" t="n">
         <v>1</v>
@@ -5446,10 +5146,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD34" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5458,48 +5158,46 @@
         <v>1</v>
       </c>
       <c r="AG34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>50</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="AI34"/>
       <c r="AJ34" t="s">
         <v>45</v>
       </c>
-      <c r="AK34" t="s">
-        <v>187</v>
+      <c r="AK34" t="n">
+        <v>2</v>
       </c>
       <c r="AL34" t="s">
         <v>45</v>
       </c>
       <c r="AM34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN34" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="AO34" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D35" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F35" t="n">
         <v>88</v>
@@ -5510,9 +5208,7 @@
       <c r="H35" t="s">
         <v>45</v>
       </c>
-      <c r="I35" t="s">
-        <v>68</v>
-      </c>
+      <c r="I35"/>
       <c r="J35" t="s">
         <v>47</v>
       </c>
@@ -5520,7 +5216,7 @@
         <v>48</v>
       </c>
       <c r="L35" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M35" t="s">
         <v>45</v>
@@ -5531,14 +5227,12 @@
       <c r="O35" t="s">
         <v>45</v>
       </c>
-      <c r="P35" t="s">
-        <v>68</v>
-      </c>
+      <c r="P35"/>
       <c r="Q35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R35" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -5551,10 +5245,10 @@
       </c>
       <c r="V35"/>
       <c r="W35" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X35" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="Y35" t="n">
         <v>1</v>
@@ -5569,10 +5263,10 @@
         <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD35" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5581,45 +5275,43 @@
         <v>1</v>
       </c>
       <c r="AG35" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH35" t="s">
         <v>58</v>
       </c>
-      <c r="AH35" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI35" t="s">
-        <v>50</v>
-      </c>
+      <c r="AI35"/>
       <c r="AJ35" t="s">
         <v>45</v>
       </c>
-      <c r="AK35" t="s">
-        <v>238</v>
+      <c r="AK35" t="n">
+        <v>0.33</v>
       </c>
       <c r="AL35" t="s">
         <v>45</v>
       </c>
       <c r="AM35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN35" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="AO35" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D36" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
@@ -5631,10 +5323,10 @@
         <v>3</v>
       </c>
       <c r="H36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I36" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J36" t="s">
         <v>47</v>
@@ -5643,7 +5335,7 @@
         <v>48</v>
       </c>
       <c r="L36" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M36" t="s">
         <v>45</v>
@@ -5652,16 +5344,16 @@
         <v>45</v>
       </c>
       <c r="O36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P36" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q36" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="R36" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -5674,10 +5366,10 @@
       </c>
       <c r="V36"/>
       <c r="W36" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X36" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="Y36" t="n">
         <v>1</v>
@@ -5692,10 +5384,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD36" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -5704,45 +5396,43 @@
         <v>1</v>
       </c>
       <c r="AG36" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="AH36" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>50</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="AI36"/>
       <c r="AJ36" t="s">
         <v>45</v>
       </c>
-      <c r="AK36" t="s">
-        <v>245</v>
+      <c r="AK36" t="n">
+        <v>6</v>
       </c>
       <c r="AL36" t="s">
         <v>45</v>
       </c>
       <c r="AM36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN36" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="AO36" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D37" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="E37" t="s">
         <v>44</v>
@@ -5754,10 +5444,10 @@
         <v>3</v>
       </c>
       <c r="H37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I37" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J37" t="s">
         <v>47</v>
@@ -5766,25 +5456,25 @@
         <v>48</v>
       </c>
       <c r="L37" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N37" t="s">
         <v>45</v>
       </c>
       <c r="O37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P37" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R37" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -5793,16 +5483,14 @@
         <v>1</v>
       </c>
       <c r="U37" t="s">
-        <v>51</v>
-      </c>
-      <c r="V37" t="s">
         <v>50</v>
       </c>
+      <c r="V37"/>
       <c r="W37" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y37" t="n">
         <v>1</v>
@@ -5817,10 +5505,10 @@
         <v>1</v>
       </c>
       <c r="AC37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD37" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -5829,19 +5517,17 @@
         <v>1</v>
       </c>
       <c r="AG37" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH37" t="s">
         <v>58</v>
       </c>
-      <c r="AH37" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI37" t="s">
+      <c r="AI37"/>
+      <c r="AJ37" t="s">
         <v>50</v>
       </c>
-      <c r="AJ37" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>75</v>
+      <c r="AK37" t="n">
+        <v>5</v>
       </c>
       <c r="AL37" t="s">
         <v>45</v>
@@ -5849,25 +5535,23 @@
       <c r="AM37" t="s">
         <v>45</v>
       </c>
-      <c r="AN37" t="s">
-        <v>61</v>
-      </c>
+      <c r="AN37"/>
       <c r="AO37" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D38" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
         <v>44</v>
@@ -5879,10 +5563,10 @@
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I38" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J38" t="s">
         <v>47</v>
@@ -5891,7 +5575,7 @@
         <v>48</v>
       </c>
       <c r="L38" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M38" t="s">
         <v>45</v>
@@ -5900,16 +5584,16 @@
         <v>45</v>
       </c>
       <c r="O38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q38" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="R38" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5917,15 +5601,13 @@
       <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="U38" t="s">
-        <v>50</v>
-      </c>
+      <c r="U38"/>
       <c r="V38"/>
       <c r="W38" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X38" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="Y38" t="n">
         <v>1</v>
@@ -5940,10 +5622,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD38" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5952,48 +5634,42 @@
         <v>1</v>
       </c>
       <c r="AG38" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH38" t="s">
         <v>58</v>
       </c>
-      <c r="AH38" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI38" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK38" t="s">
-        <v>50</v>
-      </c>
+      <c r="AI38"/>
+      <c r="AJ38"/>
+      <c r="AK38"/>
       <c r="AL38" t="s">
         <v>45</v>
       </c>
       <c r="AM38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN38" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="AO38" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D39" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="E39" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F39" t="n">
         <v>10</v>
@@ -6004,9 +5680,7 @@
       <c r="H39" t="s">
         <v>45</v>
       </c>
-      <c r="I39" t="s">
-        <v>68</v>
-      </c>
+      <c r="I39"/>
       <c r="J39" t="s">
         <v>47</v>
       </c>
@@ -6014,25 +5688,25 @@
         <v>48</v>
       </c>
       <c r="L39" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N39" t="s">
         <v>45</v>
       </c>
       <c r="O39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P39" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R39" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -6040,15 +5714,13 @@
       <c r="T39" t="n">
         <v>1</v>
       </c>
-      <c r="U39" t="s">
-        <v>50</v>
-      </c>
+      <c r="U39"/>
       <c r="V39"/>
       <c r="W39" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X39" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="Y39" t="n">
         <v>1</v>
@@ -6063,10 +5735,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD39" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6075,45 +5747,43 @@
         <v>1</v>
       </c>
       <c r="AG39" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH39" t="s">
         <v>58</v>
       </c>
-      <c r="AH39" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI39" t="s">
+      <c r="AI39"/>
+      <c r="AJ39" t="s">
         <v>50</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK39" t="s">
-        <v>258</v>
+      <c r="AK39" t="n">
+        <v>1</v>
       </c>
       <c r="AL39" t="s">
         <v>45</v>
       </c>
       <c r="AM39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN39" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="AO39" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="B40" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D40" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E40" t="s">
         <v>44</v>
@@ -6125,10 +5795,10 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I40" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J40" t="s">
         <v>47</v>
@@ -6137,7 +5807,7 @@
         <v>48</v>
       </c>
       <c r="L40" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M40" t="s">
         <v>45</v>
@@ -6148,14 +5818,12 @@
       <c r="O40" t="s">
         <v>45</v>
       </c>
-      <c r="P40" t="s">
-        <v>68</v>
-      </c>
+      <c r="P40"/>
       <c r="Q40" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="R40" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -6164,16 +5832,14 @@
         <v>1</v>
       </c>
       <c r="U40" t="s">
-        <v>51</v>
-      </c>
-      <c r="V40" t="s">
         <v>50</v>
       </c>
+      <c r="V40"/>
       <c r="W40" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X40" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="Y40" t="n">
         <v>1</v>
@@ -6188,10 +5854,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD40" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6200,48 +5866,46 @@
         <v>1</v>
       </c>
       <c r="AG40" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH40" t="s">
         <v>58</v>
       </c>
-      <c r="AH40" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI40" t="s">
+      <c r="AI40"/>
+      <c r="AJ40" t="s">
         <v>50</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK40" t="s">
-        <v>258</v>
+      <c r="AK40" t="n">
+        <v>1</v>
       </c>
       <c r="AL40" t="s">
         <v>45</v>
       </c>
       <c r="AM40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN40" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="AO40" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D41" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F41" t="n">
         <v>52</v>
@@ -6252,9 +5916,7 @@
       <c r="H41" t="s">
         <v>45</v>
       </c>
-      <c r="I41" t="s">
-        <v>68</v>
-      </c>
+      <c r="I41"/>
       <c r="J41" t="s">
         <v>47</v>
       </c>
@@ -6262,7 +5924,7 @@
         <v>48</v>
       </c>
       <c r="L41" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M41" t="s">
         <v>45</v>
@@ -6271,16 +5933,16 @@
         <v>45</v>
       </c>
       <c r="O41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q41" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="R41" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -6289,16 +5951,14 @@
         <v>1</v>
       </c>
       <c r="U41" t="s">
-        <v>51</v>
-      </c>
-      <c r="V41" t="s">
         <v>50</v>
       </c>
+      <c r="V41"/>
       <c r="W41" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="X41" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="Y41" t="n">
         <v>1</v>
@@ -6313,10 +5973,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD41" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -6325,45 +5985,43 @@
         <v>1</v>
       </c>
       <c r="AG41" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH41" t="s">
         <v>58</v>
       </c>
-      <c r="AH41" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI41" t="s">
+      <c r="AI41"/>
+      <c r="AJ41" t="s">
         <v>50</v>
       </c>
-      <c r="AJ41" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK41" t="s">
-        <v>267</v>
+      <c r="AK41" t="n">
+        <v>0.5</v>
       </c>
       <c r="AL41" t="s">
         <v>45</v>
       </c>
       <c r="AM41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN41" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="AO41" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="B42" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D42" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E42" t="s">
         <v>44</v>
@@ -6375,10 +6033,10 @@
         <v>0.25</v>
       </c>
       <c r="H42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I42" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J42" t="s">
         <v>47</v>
@@ -6387,7 +6045,7 @@
         <v>48</v>
       </c>
       <c r="L42" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M42" t="s">
         <v>45</v>
@@ -6396,16 +6054,16 @@
         <v>45</v>
       </c>
       <c r="O42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P42" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="Q42" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="R42" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -6413,33 +6071,29 @@
       <c r="T42" t="n">
         <v>1</v>
       </c>
-      <c r="U42" t="s">
+      <c r="U42"/>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="s">
         <v>50</v>
       </c>
-      <c r="V42"/>
-      <c r="W42" t="s">
-        <v>61</v>
-      </c>
-      <c r="X42" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="s">
-        <v>51</v>
-      </c>
       <c r="AD42" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -6448,31 +6102,29 @@
         <v>1</v>
       </c>
       <c r="AG42" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH42" t="s">
         <v>58</v>
       </c>
-      <c r="AH42" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI42" t="s">
-        <v>50</v>
-      </c>
+      <c r="AI42"/>
       <c r="AJ42" t="s">
         <v>45</v>
       </c>
-      <c r="AK42" t="s">
-        <v>272</v>
+      <c r="AK42" t="n">
+        <v>0.33</v>
       </c>
       <c r="AL42" t="s">
         <v>45</v>
       </c>
       <c r="AM42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AN42" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="AO42" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -6497,25 +6149,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="E1" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="F1" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="G1" t="s">
         <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="I1" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="J1" t="s">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
@@ -6552,10 +6204,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>45022</v>
@@ -6584,10 +6236,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>45028</v>
@@ -6616,10 +6268,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>45028</v>
@@ -6648,10 +6300,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>45035</v>
@@ -6680,10 +6332,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>45035</v>
@@ -6712,10 +6364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>45042</v>
@@ -6744,10 +6396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>45042</v>
@@ -6776,10 +6428,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>45055</v>
@@ -6808,10 +6460,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45055</v>
@@ -6840,10 +6492,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
@@ -6872,10 +6524,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
@@ -6904,10 +6556,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -6936,10 +6588,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -6968,10 +6620,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -7000,10 +6652,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -7032,10 +6684,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -7064,10 +6716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -7096,10 +6748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -7128,10 +6780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -7160,10 +6812,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -7192,10 +6844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
@@ -7224,10 +6876,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
@@ -7256,10 +6908,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
@@ -7288,10 +6940,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
@@ -7320,10 +6972,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
@@ -7352,10 +7004,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
@@ -7384,10 +7036,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
@@ -7416,10 +7068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
@@ -7448,10 +7100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
@@ -7480,10 +7132,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
@@ -7512,10 +7164,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
@@ -7544,10 +7196,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
@@ -7576,10 +7228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
@@ -7608,10 +7260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
@@ -7640,10 +7292,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
@@ -7672,10 +7324,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
@@ -7704,10 +7356,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
@@ -7736,10 +7388,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="B40" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
@@ -7768,10 +7420,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
@@ -7800,10 +7452,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="B42" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
@@ -7855,13 +7507,13 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="F1" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="G1" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2">
@@ -7889,10 +7541,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>45022</v>
@@ -7912,10 +7564,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>45028</v>
@@ -7935,10 +7587,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>45028</v>
@@ -7958,10 +7610,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>45035</v>
@@ -7981,10 +7633,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>45035</v>
@@ -8004,10 +7656,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>45042</v>
@@ -8027,10 +7679,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>45042</v>
@@ -8050,10 +7702,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>45055</v>
@@ -8073,10 +7725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45055</v>
@@ -8096,10 +7748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
@@ -8119,10 +7771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
@@ -8142,10 +7794,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -8165,10 +7817,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -8188,10 +7840,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -8211,10 +7863,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -8234,10 +7886,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -8257,10 +7909,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -8280,10 +7932,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -8303,10 +7955,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -8326,10 +7978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -8349,10 +8001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
@@ -8372,10 +8024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
@@ -8395,10 +8047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
@@ -8418,10 +8070,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
@@ -8441,10 +8093,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
@@ -8464,10 +8116,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
@@ -8487,10 +8139,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
@@ -8510,10 +8162,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
@@ -8533,10 +8185,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
@@ -8556,10 +8208,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
@@ -8579,10 +8231,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
@@ -8602,10 +8254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
@@ -8625,10 +8277,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
@@ -8648,10 +8300,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
@@ -8671,10 +8323,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
@@ -8694,10 +8346,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
@@ -8717,10 +8369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
@@ -8740,10 +8392,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="B40" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
@@ -8763,10 +8415,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
@@ -8786,10 +8438,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="B42" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
@@ -8829,82 +8481,82 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1" t="s">
+        <v>259</v>
+      </c>
+      <c r="K1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L1" t="s">
+        <v>261</v>
+      </c>
+      <c r="M1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N1" t="s">
+        <v>263</v>
+      </c>
+      <c r="O1" t="s">
+        <v>264</v>
+      </c>
+      <c r="P1" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>266</v>
+      </c>
+      <c r="R1" t="s">
+        <v>267</v>
+      </c>
+      <c r="S1" t="s">
+        <v>268</v>
+      </c>
+      <c r="T1" t="s">
+        <v>269</v>
+      </c>
+      <c r="U1" t="s">
+        <v>270</v>
+      </c>
+      <c r="V1" t="s">
+        <v>271</v>
+      </c>
+      <c r="W1" t="s">
+        <v>272</v>
+      </c>
+      <c r="X1" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA1" t="s">
         <v>276</v>
       </c>
-      <c r="F1" t="s">
-        <v>285</v>
-      </c>
-      <c r="G1" t="s">
-        <v>286</v>
-      </c>
-      <c r="H1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I1" t="s">
-        <v>288</v>
-      </c>
-      <c r="J1" t="s">
-        <v>289</v>
-      </c>
-      <c r="K1" t="s">
-        <v>290</v>
-      </c>
-      <c r="L1" t="s">
-        <v>291</v>
-      </c>
-      <c r="M1" t="s">
-        <v>292</v>
-      </c>
-      <c r="N1" t="s">
-        <v>293</v>
-      </c>
-      <c r="O1" t="s">
-        <v>294</v>
-      </c>
-      <c r="P1" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>296</v>
-      </c>
-      <c r="R1" t="s">
-        <v>297</v>
-      </c>
-      <c r="S1" t="s">
-        <v>298</v>
-      </c>
-      <c r="T1" t="s">
-        <v>299</v>
-      </c>
-      <c r="U1" t="s">
-        <v>300</v>
-      </c>
-      <c r="V1" t="s">
-        <v>301</v>
-      </c>
-      <c r="W1" t="s">
-        <v>302</v>
-      </c>
-      <c r="X1" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>305</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>306</v>
-      </c>
       <c r="AB1" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="AC1" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2">
@@ -8918,7 +8570,7 @@
         <v>45022</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9007,7 +8659,7 @@
         <v>45022</v>
       </c>
       <c r="D3" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E3" t="n">
         <v>0.65</v>
@@ -9096,7 +8748,7 @@
         <v>45022</v>
       </c>
       <c r="D4" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E4" t="n">
         <v>1.31</v>
@@ -9176,16 +8828,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>45022</v>
       </c>
       <c r="D5" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -9265,16 +8917,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>45022</v>
       </c>
       <c r="D6" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
@@ -9354,16 +9006,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>45022</v>
       </c>
       <c r="D7" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E7" t="n">
         <v>1.82</v>
@@ -9443,16 +9095,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D8" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9532,16 +9184,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D9" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
@@ -9621,16 +9273,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D10" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E10" t="n">
         <v>1.85</v>
@@ -9710,16 +9362,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D11" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -9799,16 +9451,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D12" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -9888,16 +9540,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D13" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E13" t="n">
         <v>1.05</v>
@@ -9977,16 +9629,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D14" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -10066,16 +9718,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D15" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E15" t="n">
         <v>0.46</v>
@@ -10155,16 +9807,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D16" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E16" t="n">
         <v>0.92</v>
@@ -10244,16 +9896,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D17" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10333,16 +9985,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D18" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E18" t="n">
         <v>0.7</v>
@@ -10422,16 +10074,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D19" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E19" t="n">
         <v>1.39</v>
@@ -10511,16 +10163,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D20" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10600,16 +10252,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D21" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E21" t="n">
         <v>0.7</v>
@@ -10689,16 +10341,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D22" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E22" t="n">
         <v>1.41</v>
@@ -10778,16 +10430,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D23" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10867,16 +10519,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D24" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E24" t="n">
         <v>0.52</v>
@@ -10956,16 +10608,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D25" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E25" t="n">
         <v>1.04</v>
@@ -11045,16 +10697,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D26" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -11134,16 +10786,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D27" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E27" t="n">
         <v>1.055</v>
@@ -11223,16 +10875,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D28" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E28" t="n">
         <v>2.11</v>
@@ -11312,16 +10964,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D29" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -11401,16 +11053,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D30" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E30" t="n">
         <v>0.45</v>
@@ -11490,16 +11142,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D31" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E31" t="n">
         <v>1.92</v>
@@ -11579,16 +11231,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D32" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -11668,16 +11320,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D33" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -11757,16 +11409,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D34" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E34" t="n">
         <v>0.55</v>
@@ -11846,16 +11498,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D35" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E35" t="n">
         <v>1.15</v>
@@ -11935,16 +11587,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D36" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -12024,16 +11676,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D37" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E37" t="n">
         <v>0.94</v>
@@ -12113,16 +11765,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B38" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D38" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E38" t="n">
         <v>1.88</v>
@@ -12202,16 +11854,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D39" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -12291,16 +11943,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D40" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E40" t="n">
         <v>0.52</v>
@@ -12380,16 +12032,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D41" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E41" t="n">
         <v>1.04</v>
@@ -12469,16 +12121,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -12558,16 +12210,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E43" t="n">
         <v>0.55</v>
@@ -12647,16 +12299,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E44" t="n">
         <v>1.11</v>
@@ -12736,16 +12388,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B45" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -12825,16 +12477,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E46" t="n">
         <v>0.42</v>
@@ -12914,16 +12566,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E47" t="n">
         <v>0.95</v>
@@ -13003,16 +12655,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B48" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -13092,16 +12744,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B49" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E49" t="n">
         <v>0.67</v>
@@ -13181,16 +12833,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E50" t="n">
         <v>1.34</v>
@@ -13270,16 +12922,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B51" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -13359,16 +13011,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E52" t="n">
         <v>0.505</v>
@@ -13448,16 +13100,16 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B53" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E53" t="n">
         <v>1.01</v>
@@ -13537,16 +13189,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="B54" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D54" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -13626,16 +13278,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B55" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D55" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -13715,16 +13367,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B56" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D56" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E56" t="n">
         <v>0.61</v>
@@ -13804,16 +13456,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D57" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E57" t="n">
         <v>1.22</v>
@@ -13893,16 +13545,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B58" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D58" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -13982,16 +13634,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B59" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C59" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D59" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E59" t="n">
         <v>0.735</v>
@@ -14071,16 +13723,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B60" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D60" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E60" t="n">
         <v>1.47</v>
@@ -14160,16 +13812,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B61" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D61" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -14249,16 +13901,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D62" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E62" t="n">
         <v>0.575</v>
@@ -14338,16 +13990,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B63" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D63" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E63" t="n">
         <v>1.15</v>
@@ -14427,16 +14079,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B64" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D64" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -14514,16 +14166,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B65" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D65" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E65" t="n">
         <v>1.05</v>
@@ -14601,16 +14253,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B66" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D66" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E66" t="n">
         <v>2.1</v>
@@ -14688,16 +14340,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D67" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -14775,16 +14427,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B68" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D68" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E68" t="n">
         <v>1.75</v>
@@ -14864,16 +14516,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B69" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C69" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D69" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E69" t="n">
         <v>3.5</v>
@@ -14953,16 +14605,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B70" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C70" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D70" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -15040,16 +14692,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B71" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C71" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D71" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -15127,16 +14779,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B72" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C72" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D72" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E72" t="n">
         <v>2.05</v>
@@ -15214,16 +14866,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B73" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D73" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -15301,16 +14953,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B74" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D74" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -15388,16 +15040,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B75" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D75" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E75" t="n">
         <v>2.05</v>
@@ -15477,16 +15129,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B76" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C76" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D76" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -15564,16 +15216,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B77" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C77" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D77" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -15653,16 +15305,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B78" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C78" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D78" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E78" t="n">
         <v>2.05</v>
@@ -15742,16 +15394,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B79" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C79" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D79" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -15831,16 +15483,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C80" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D80" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E80" t="n">
         <v>1.35</v>
@@ -15920,16 +15572,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B81" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D81" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E81" t="n">
         <v>2.7</v>
@@ -16009,16 +15661,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B82" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="C82" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D82" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -16098,16 +15750,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B83" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="C83" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D83" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E83" t="n">
         <v>0.7</v>
@@ -16187,16 +15839,16 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="C84" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D84" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E84" t="n">
         <v>1.85</v>
@@ -16276,16 +15928,16 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B85" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C85" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D85" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -16365,16 +16017,16 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B86" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C86" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D86" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E86" t="n">
         <v>0.5</v>
@@ -16454,16 +16106,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B87" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C87" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D87" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E87" t="n">
         <v>1.05</v>
@@ -16505,16 +16157,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B88" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C88" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D88" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -16594,16 +16246,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B89" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C89" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D89" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E89" t="n">
         <v>0.5</v>
@@ -16683,16 +16335,16 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B90" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D90" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -16734,16 +16386,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B91" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C91" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D91" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -16823,16 +16475,16 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B92" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C92" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D92" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E92" t="n">
         <v>1.18</v>
@@ -16912,16 +16564,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B93" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C93" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D93" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E93" t="n">
         <v>2.34</v>
@@ -17001,16 +16653,16 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="B94" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D94" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -17090,16 +16742,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="B95" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C95" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D95" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E95" t="n">
         <v>1.08</v>
@@ -17179,16 +16831,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="B96" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="C96" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D96" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E96" t="n">
         <v>2.15</v>
@@ -17268,16 +16920,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="B97" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="C97" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D97" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -17357,16 +17009,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="B98" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="C98" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D98" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E98" t="n">
         <v>1.5</v>
@@ -17446,16 +17098,16 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="B99" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="C99" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D99" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E99" t="n">
         <v>3</v>
@@ -17535,16 +17187,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B100" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C100" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D100" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -17624,16 +17276,16 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B101" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C101" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D101" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E101" t="n">
         <v>0.9</v>
@@ -17711,16 +17363,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B102" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C102" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D102" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E102" t="n">
         <v>1.8</v>
@@ -17762,16 +17414,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="B103" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C103" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D103" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -17851,16 +17503,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="B104" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C104" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D104" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E104" t="n">
         <v>0.9</v>
@@ -17940,16 +17592,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="B105" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D105" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E105" t="n">
         <v>1.8</v>
@@ -18029,16 +17681,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B106" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D106" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -18118,16 +17770,16 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B107" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D107" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E107" t="n">
         <v>0.8</v>
@@ -18207,16 +17859,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B108" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D108" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E108" t="n">
         <v>1.65</v>
@@ -18258,16 +17910,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B109" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D109" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -18347,16 +17999,16 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B110" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D110" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E110" t="n">
         <v>0.7</v>
@@ -18436,16 +18088,16 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B111" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C111" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D111" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E111" t="n">
         <v>1.35</v>
@@ -18525,16 +18177,16 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="B112" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C112" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D112" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -18614,16 +18266,16 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="B113" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C113" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D113" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -18703,16 +18355,16 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="B114" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C114" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D114" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E114" t="n">
         <v>4</v>
@@ -18792,16 +18444,16 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="B115" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C115" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D115" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -18881,16 +18533,16 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="B116" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C116" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D116" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E116" t="n">
         <v>0.9</v>
@@ -18970,16 +18622,16 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="B117" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C117" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D117" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E117" t="n">
         <v>1.8</v>
@@ -19059,16 +18711,16 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="B118" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="C118" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D118" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -19148,16 +18800,16 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="B119" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="C119" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D119" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="E119" t="n">
         <v>1.05</v>
@@ -19237,16 +18889,16 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="B120" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="C120" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D120" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="E120" t="n">
         <v>2.15</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -7156,7 +7156,7 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>2.63615890590452</v>
+        <v>27.2560329603118</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -7179,10 +7179,10 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.603733040872141</v>
+        <v>31.6839087476299</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>87.4345981301277</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7202,10 +7202,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1.62199448988941</v>
+        <v>7.05696469602596</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>63.1432744737226</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -7225,10 +7225,10 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1.30107457811649</v>
+        <v>40.083047620108</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>19.3254504152049</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7248,10 +7248,10 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>6.24429282617261</v>
+        <v>85.6196766726526</v>
       </c>
       <c r="F6" t="n">
-        <v>49.4296557126272</v>
+        <v>161.516002704894</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>410</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0698748567203347</v>
+        <v>0.418042154143449</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1.75475744741278</v>
+        <v>41.5812684610042</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7317,10 +7317,10 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>6.9684218922271</v>
+        <v>116.931953337674</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>179.60486212834</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -7363,10 +7363,10 @@
         <v>368</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0632422299953523</v>
+        <v>1.12880556599633</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.398772880015029</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0371138101410104</v>
+        <v>0.167779417271585</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3.49669944063345</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7409,10 +7409,10 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>3.04774084852544</v>
+        <v>14.5719489770412</v>
       </c>
       <c r="F13" t="n">
-        <v>2.20329085265111</v>
+        <v>19.8036293337893</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0387368630756498</v>
+        <v>3.47199432365575</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7455,10 +7455,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>14.2412941161905</v>
+        <v>153.242356075774</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>176.11862559466</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -7501,10 +7501,10 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>3.69791088127849</v>
+        <v>28.4853414538738</v>
       </c>
       <c r="F17" t="n">
-        <v>15.9136423321382</v>
+        <v>81.1197413616831</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -7524,7 +7524,7 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.54692900155373</v>
+        <v>30.7601642715924</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>10.3704160596052</v>
+        <v>15.2095004951554</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -7570,10 +7570,10 @@
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.97299809427969</v>
+        <v>36.1174196010493</v>
       </c>
       <c r="F20" t="n">
-        <v>6.82470441922309</v>
+        <v>59.7184067673525</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -7593,7 +7593,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.92812403830783</v>
+        <v>13.6916997203912</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -7616,10 +7616,10 @@
         <v>200</v>
       </c>
       <c r="E22" t="n">
-        <v>0.165981089038274</v>
+        <v>0.784252236544445</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.32788011504695</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -7662,10 +7662,10 @@
         <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>4.46</v>
+        <v>40.7605297469947</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>77.8379282927321</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -7685,10 +7685,10 @@
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>2.15</v>
+        <v>13.7818968442006</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>489.551167461809</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -7708,10 +7708,10 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>4.28</v>
+        <v>13.92256539862</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>142.941859135691</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -7731,7 +7731,7 @@
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>10.96</v>
+        <v>37.8630425374192</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>4.69</v>
+        <v>21.6094847868012</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -7777,10 +7777,10 @@
         <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1</v>
+        <v>16.9404675162311</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>16.2509044834474</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -7800,10 +7800,10 @@
         <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>1.87</v>
+        <v>6.90140153131008</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>23.3603081609197</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
         <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>0.46</v>
+        <v>0.682280530392119</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>35</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2</v>
+        <v>0.76502851822708</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>7.73917745909456</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -7869,10 +7869,10 @@
         <v>30</v>
       </c>
       <c r="E33" t="n">
-        <v>3.4</v>
+        <v>18.9946622972448</v>
       </c>
       <c r="F33" t="n">
-        <v>32.2</v>
+        <v>160.385524565915</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -7892,10 +7892,10 @@
         <v>30</v>
       </c>
       <c r="E34" t="n">
-        <v>1.19</v>
+        <v>10.9054868168041</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1</v>
+        <v>31.7640581080592</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -7915,10 +7915,10 @@
         <v>88</v>
       </c>
       <c r="E35" t="n">
-        <v>7.98</v>
+        <v>25.1839141857233</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9</v>
+        <v>39.861061346201</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>35</v>
       </c>
       <c r="E36" t="n">
-        <v>1.44</v>
+        <v>12.5601837915343</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>33.0356504245321</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -7961,10 +7961,10 @@
         <v>43</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9</v>
+        <v>3.25216968243562</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>15.0464351300317</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -7984,10 +7984,10 @@
         <v>29</v>
       </c>
       <c r="E38" t="n">
-        <v>1.45</v>
+        <v>5.29238719834521</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>9.68965819806905</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -8010,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.6</v>
+        <v>19.447947290656</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -8030,10 +8030,10 @@
         <v>16</v>
       </c>
       <c r="E40" t="n">
-        <v>3.04</v>
+        <v>41.4873367008572</v>
       </c>
       <c r="F40" t="n">
-        <v>1.8</v>
+        <v>71.6871984130468</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -8053,10 +8053,10 @@
         <v>52</v>
       </c>
       <c r="E41" t="n">
-        <v>1.41</v>
+        <v>4.60436461329772</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1</v>
+        <v>8.85828755155557</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -8076,10 +8076,10 @@
         <v>14</v>
       </c>
       <c r="E42" t="n">
-        <v>0.49</v>
+        <v>3.56663954822773</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>25.9659080323872</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -6351,16 +6351,16 @@
         <v>45085</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
         <v>2.7</v>
@@ -6383,16 +6383,16 @@
         <v>45085</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="H20" t="n">
         <v>2.7</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="230">
   <si>
     <t xml:space="preserve">sample_id</t>
   </si>
@@ -308,9 +308,6 @@
     <t xml:space="preserve">7a</t>
   </si>
   <si>
-    <t xml:space="preserve">Office building</t>
-  </si>
-  <si>
     <t xml:space="preserve">Toilet Kitchen</t>
   </si>
   <si>
@@ -327,9 +324,6 @@
   </si>
   <si>
     <t xml:space="preserve">7c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
   </si>
   <si>
     <t xml:space="preserve">16-DC-07062023</t>
@@ -2508,7 +2502,7 @@
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -2559,7 +2553,7 @@
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
@@ -2607,10 +2601,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
         <v>99</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -2671,7 +2665,7 @@
       </c>
       <c r="V15"/>
       <c r="W15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="X15" t="s">
         <v>51</v>
@@ -2720,10 +2714,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
         <v>102</v>
-      </c>
-      <c r="B16" t="s">
-        <v>103</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -2732,7 +2726,7 @@
         <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -2827,10 +2821,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -2860,7 +2854,7 @@
         <v>45</v>
       </c>
       <c r="L17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
@@ -2938,10 +2932,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -3049,10 +3043,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -3111,7 +3105,7 @@
       <c r="U19"/>
       <c r="V19"/>
       <c r="W19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="X19" t="s">
         <v>51</v>
@@ -3160,10 +3154,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -3184,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J20" t="s">
         <v>44</v>
@@ -3211,7 +3205,7 @@
         <v>48</v>
       </c>
       <c r="R20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -3273,10 +3267,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -3386,10 +3380,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -3449,7 +3443,7 @@
       <c r="V22"/>
       <c r="W22"/>
       <c r="X22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
@@ -3497,16 +3491,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -3562,7 +3556,7 @@
       <c r="V23"/>
       <c r="W23"/>
       <c r="X23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
@@ -3606,16 +3600,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
         <v>72</v>
@@ -3649,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q24" t="s">
         <v>48</v>
@@ -3668,10 +3662,10 @@
       </c>
       <c r="V24"/>
       <c r="W24" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
@@ -3712,21 +3706,21 @@
         <v>1</v>
       </c>
       <c r="AM24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
         <v>42</v>
@@ -3741,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J25" t="s">
         <v>44</v>
@@ -3762,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q25" t="s">
         <v>48</v>
@@ -3781,10 +3775,10 @@
       </c>
       <c r="V25"/>
       <c r="W25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X25" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
@@ -3827,21 +3821,21 @@
         <v>1</v>
       </c>
       <c r="AM25" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
         <v>42</v>
@@ -3856,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J26" t="s">
         <v>44</v>
@@ -3877,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q26" t="s">
         <v>48</v>
@@ -3896,10 +3890,10 @@
       </c>
       <c r="V26"/>
       <c r="W26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
@@ -3942,21 +3936,21 @@
         <v>1</v>
       </c>
       <c r="AM26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
         <v>42</v>
@@ -3971,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J27" t="s">
         <v>44</v>
@@ -3992,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q27" t="s">
         <v>48</v>
@@ -4011,10 +4005,10 @@
       </c>
       <c r="V27"/>
       <c r="W27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -4057,21 +4051,21 @@
         <v>1</v>
       </c>
       <c r="AM27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E28" t="s">
         <v>42</v>
@@ -4086,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J28" t="s">
         <v>44</v>
@@ -4107,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q28" t="s">
         <v>48</v>
@@ -4126,10 +4120,10 @@
       </c>
       <c r="V28"/>
       <c r="W28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
@@ -4172,21 +4166,21 @@
         <v>1</v>
       </c>
       <c r="AM28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E29" t="s">
         <v>42</v>
@@ -4201,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J29" t="s">
         <v>44</v>
@@ -4222,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q29" t="s">
         <v>48</v>
@@ -4241,10 +4235,10 @@
       </c>
       <c r="V29"/>
       <c r="W29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
@@ -4290,16 +4284,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E30" t="s">
         <v>42</v>
@@ -4314,7 +4308,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J30" t="s">
         <v>44</v>
@@ -4335,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q30" t="s">
         <v>48</v>
@@ -4354,10 +4348,10 @@
       </c>
       <c r="V30"/>
       <c r="W30" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="X30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
@@ -4381,7 +4375,7 @@
         <v>1</v>
       </c>
       <c r="AF30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG30" t="s">
         <v>53</v>
@@ -4396,21 +4390,21 @@
         <v>1</v>
       </c>
       <c r="AM30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
         <v>42</v>
@@ -4425,7 +4419,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J31" t="s">
         <v>44</v>
@@ -4446,7 +4440,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q31" t="s">
         <v>48</v>
@@ -4490,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="AF31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG31" t="s">
         <v>75</v>
@@ -4505,21 +4499,21 @@
         <v>1</v>
       </c>
       <c r="AM31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D32" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
         <v>72</v>
@@ -4538,10 +4532,10 @@
         <v>44</v>
       </c>
       <c r="K32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="L32" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
@@ -4553,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q32" t="s">
         <v>48</v>
@@ -4572,7 +4566,7 @@
       </c>
       <c r="V32"/>
       <c r="W32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X32" t="s">
         <v>65</v>
@@ -4616,21 +4610,21 @@
         <v>1</v>
       </c>
       <c r="AM32" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
         <v>42</v>
@@ -4645,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J33" t="s">
         <v>44</v>
@@ -4666,7 +4660,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q33" t="s">
         <v>48</v>
@@ -4685,10 +4679,10 @@
       </c>
       <c r="V33"/>
       <c r="W33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X33" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Y33" t="b">
         <v>0</v>
@@ -4736,16 +4730,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E34" t="s">
         <v>42</v>
@@ -4760,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J34" t="s">
         <v>44</v>
@@ -4781,7 +4775,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q34" t="s">
         <v>48</v>
@@ -4800,7 +4794,7 @@
       </c>
       <c r="V34"/>
       <c r="W34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X34" t="s">
         <v>74</v>
@@ -4846,21 +4840,21 @@
         <v>1</v>
       </c>
       <c r="AM34" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
         <v>72</v>
@@ -4911,10 +4905,10 @@
       </c>
       <c r="V35"/>
       <c r="W35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Y35" t="b">
         <v>1</v>
@@ -4957,21 +4951,21 @@
         <v>1</v>
       </c>
       <c r="AM35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E36" t="s">
         <v>42</v>
@@ -4986,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J36" t="s">
         <v>44</v>
@@ -5007,10 +5001,10 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R36" t="s">
         <v>69</v>
@@ -5026,7 +5020,7 @@
       </c>
       <c r="V36"/>
       <c r="W36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X36" t="s">
         <v>74</v>
@@ -5072,21 +5066,21 @@
         <v>1</v>
       </c>
       <c r="AM36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E37" t="s">
         <v>42</v>
@@ -5101,7 +5095,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J37" t="s">
         <v>44</v>
@@ -5122,7 +5116,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q37" t="s">
         <v>48</v>
@@ -5141,7 +5135,7 @@
       </c>
       <c r="V37"/>
       <c r="W37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X37" t="s">
         <v>51</v>
@@ -5190,16 +5184,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D38" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E38" t="s">
         <v>42</v>
@@ -5214,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J38" t="s">
         <v>44</v>
@@ -5235,10 +5229,10 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R38" t="s">
         <v>69</v>
@@ -5254,7 +5248,7 @@
       </c>
       <c r="V38"/>
       <c r="W38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X38" t="s">
         <v>65</v>
@@ -5298,21 +5292,21 @@
         <v>1</v>
       </c>
       <c r="AM38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E39" t="s">
         <v>72</v>
@@ -5346,7 +5340,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q39" t="s">
         <v>48</v>
@@ -5365,7 +5359,7 @@
       </c>
       <c r="V39"/>
       <c r="W39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X39" t="s">
         <v>65</v>
@@ -5411,21 +5405,21 @@
         <v>1</v>
       </c>
       <c r="AM39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
         <v>42</v>
@@ -5440,7 +5434,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J40" t="s">
         <v>44</v>
@@ -5462,7 +5456,7 @@
       </c>
       <c r="P40"/>
       <c r="Q40" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R40" t="s">
         <v>69</v>
@@ -5478,7 +5472,7 @@
       </c>
       <c r="V40"/>
       <c r="W40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X40" t="s">
         <v>74</v>
@@ -5524,21 +5518,21 @@
         <v>1</v>
       </c>
       <c r="AM40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E41" t="s">
         <v>72</v>
@@ -5572,10 +5566,10 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R41" t="s">
         <v>69</v>
@@ -5591,7 +5585,7 @@
       </c>
       <c r="V41"/>
       <c r="W41" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X41" t="s">
         <v>74</v>
@@ -5637,21 +5631,21 @@
         <v>1</v>
       </c>
       <c r="AM41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E42" t="s">
         <v>42</v>
@@ -5666,7 +5660,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J42" t="s">
         <v>44</v>
@@ -5687,10 +5681,10 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q42" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R42" t="s">
         <v>69</v>
@@ -5750,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="AM42" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -5775,25 +5769,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" t="s">
         <v>193</v>
-      </c>
-      <c r="E1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F1" t="s">
-        <v>195</v>
       </c>
       <c r="G1" t="s">
         <v>33</v>
       </c>
       <c r="H1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J1" t="s">
         <v>196</v>
-      </c>
-      <c r="I1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="2">
@@ -6214,10 +6208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
         <v>99</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -6246,10 +6240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
         <v>102</v>
-      </c>
-      <c r="B16" t="s">
-        <v>103</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -6278,10 +6272,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -6310,10 +6304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -6342,10 +6336,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -6374,10 +6368,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -6406,10 +6400,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -6438,10 +6432,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -6470,10 +6464,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
@@ -6502,10 +6496,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
@@ -6534,10 +6528,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
@@ -6566,10 +6560,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
@@ -6598,10 +6592,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
@@ -6630,10 +6624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
@@ -6662,10 +6656,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
@@ -6694,10 +6688,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
@@ -6726,10 +6720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
@@ -6758,10 +6752,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
@@ -6790,10 +6784,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
@@ -6822,10 +6816,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
@@ -6854,10 +6848,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
@@ -6886,10 +6880,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
@@ -6918,10 +6912,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
@@ -6950,10 +6944,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
@@ -6982,10 +6976,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
@@ -7014,10 +7008,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
@@ -7046,10 +7040,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
@@ -7078,10 +7072,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
@@ -7133,13 +7127,13 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" t="s">
         <v>199</v>
-      </c>
-      <c r="F1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="2">
@@ -7443,10 +7437,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
         <v>99</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -7466,10 +7460,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
         <v>102</v>
-      </c>
-      <c r="B16" t="s">
-        <v>103</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -7489,10 +7483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -7512,10 +7506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -7535,10 +7529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -7558,10 +7552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -7581,10 +7575,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -7604,10 +7598,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -7627,10 +7621,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
@@ -7650,10 +7644,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
@@ -7673,10 +7667,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
@@ -7696,10 +7690,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
@@ -7719,10 +7713,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
@@ -7742,10 +7736,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
@@ -7765,10 +7759,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
@@ -7788,10 +7782,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
@@ -7811,10 +7805,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
@@ -7834,10 +7828,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
@@ -7857,10 +7851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
@@ -7880,10 +7874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
@@ -7903,10 +7897,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
@@ -7926,10 +7920,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
@@ -7949,10 +7943,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
@@ -7972,10 +7966,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
@@ -7995,10 +7989,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
@@ -8018,10 +8012,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
@@ -8041,10 +8035,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
@@ -8064,10 +8058,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
@@ -8107,82 +8101,82 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1" t="s">
         <v>202</v>
       </c>
-      <c r="E1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>203</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>204</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>205</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>206</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>207</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>208</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>209</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>210</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>211</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>212</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>213</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>214</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>215</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>216</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>217</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>218</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>219</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>220</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>221</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>222</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>223</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>224</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>225</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="2">
@@ -8196,7 +8190,7 @@
         <v>45022</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -8285,7 +8279,7 @@
         <v>45022</v>
       </c>
       <c r="D3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E3" t="n">
         <v>0.65</v>
@@ -8374,7 +8368,7 @@
         <v>45022</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E4" t="n">
         <v>1.31</v>
@@ -8463,7 +8457,7 @@
         <v>45022</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -8552,7 +8546,7 @@
         <v>45022</v>
       </c>
       <c r="D6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
@@ -8641,7 +8635,7 @@
         <v>45022</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E7" t="n">
         <v>1.82</v>
@@ -8730,7 +8724,7 @@
         <v>45028</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -8819,7 +8813,7 @@
         <v>45028</v>
       </c>
       <c r="D9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
@@ -8908,7 +8902,7 @@
         <v>45028</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E10" t="n">
         <v>1.85</v>
@@ -8997,7 +8991,7 @@
         <v>45028</v>
       </c>
       <c r="D11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -9086,7 +9080,7 @@
         <v>45028</v>
       </c>
       <c r="D12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -9175,7 +9169,7 @@
         <v>45028</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E13" t="n">
         <v>1.05</v>
@@ -9264,7 +9258,7 @@
         <v>45035</v>
       </c>
       <c r="D14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -9353,7 +9347,7 @@
         <v>45035</v>
       </c>
       <c r="D15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E15" t="n">
         <v>0.46</v>
@@ -9442,7 +9436,7 @@
         <v>45035</v>
       </c>
       <c r="D16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E16" t="n">
         <v>0.92</v>
@@ -9531,7 +9525,7 @@
         <v>45035</v>
       </c>
       <c r="D17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -9620,7 +9614,7 @@
         <v>45035</v>
       </c>
       <c r="D18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E18" t="n">
         <v>0.7</v>
@@ -9709,7 +9703,7 @@
         <v>45035</v>
       </c>
       <c r="D19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E19" t="n">
         <v>1.39</v>
@@ -9798,7 +9792,7 @@
         <v>45042</v>
       </c>
       <c r="D20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -9887,7 +9881,7 @@
         <v>45042</v>
       </c>
       <c r="D21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E21" t="n">
         <v>0.7</v>
@@ -9976,7 +9970,7 @@
         <v>45042</v>
       </c>
       <c r="D22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E22" t="n">
         <v>1.41</v>
@@ -10065,7 +10059,7 @@
         <v>45042</v>
       </c>
       <c r="D23" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10154,7 +10148,7 @@
         <v>45042</v>
       </c>
       <c r="D24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E24" t="n">
         <v>0.52</v>
@@ -10243,7 +10237,7 @@
         <v>45042</v>
       </c>
       <c r="D25" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E25" t="n">
         <v>1.04</v>
@@ -10332,7 +10326,7 @@
         <v>45055</v>
       </c>
       <c r="D26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -10421,7 +10415,7 @@
         <v>45055</v>
       </c>
       <c r="D27" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E27" t="n">
         <v>1.055</v>
@@ -10510,7 +10504,7 @@
         <v>45055</v>
       </c>
       <c r="D28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E28" t="n">
         <v>2.11</v>
@@ -10599,7 +10593,7 @@
         <v>45055</v>
       </c>
       <c r="D29" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -10688,7 +10682,7 @@
         <v>45055</v>
       </c>
       <c r="D30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E30" t="n">
         <v>0.45</v>
@@ -10777,7 +10771,7 @@
         <v>45055</v>
       </c>
       <c r="D31" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E31" t="n">
         <v>1.92</v>
@@ -10866,7 +10860,7 @@
         <v>45071</v>
       </c>
       <c r="D32" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -10955,7 +10949,7 @@
         <v>45071</v>
       </c>
       <c r="D33" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -11044,7 +11038,7 @@
         <v>45071</v>
       </c>
       <c r="D34" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E34" t="n">
         <v>0.55</v>
@@ -11133,7 +11127,7 @@
         <v>45071</v>
       </c>
       <c r="D35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E35" t="n">
         <v>1.15</v>
@@ -11222,7 +11216,7 @@
         <v>45077</v>
       </c>
       <c r="D36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -11311,7 +11305,7 @@
         <v>45077</v>
       </c>
       <c r="D37" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E37" t="n">
         <v>0.94</v>
@@ -11400,7 +11394,7 @@
         <v>45077</v>
       </c>
       <c r="D38" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E38" t="n">
         <v>1.88</v>
@@ -11480,16 +11474,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" t="s">
         <v>99</v>
-      </c>
-      <c r="B39" t="s">
-        <v>100</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D39" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -11569,16 +11563,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" t="s">
         <v>99</v>
-      </c>
-      <c r="B40" t="s">
-        <v>100</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D40" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E40" t="n">
         <v>0.52</v>
@@ -11658,16 +11652,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" t="s">
         <v>99</v>
-      </c>
-      <c r="B41" t="s">
-        <v>100</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D41" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E41" t="n">
         <v>1.04</v>
@@ -11747,16 +11741,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
         <v>102</v>
-      </c>
-      <c r="B42" t="s">
-        <v>103</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -11836,16 +11830,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" t="s">
         <v>102</v>
-      </c>
-      <c r="B43" t="s">
-        <v>103</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D43" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E43" t="n">
         <v>0.55</v>
@@ -11925,16 +11919,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" t="s">
         <v>102</v>
-      </c>
-      <c r="B44" t="s">
-        <v>103</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D44" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E44" t="n">
         <v>1.11</v>
@@ -12014,16 +12008,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D45" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -12103,16 +12097,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D46" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E46" t="n">
         <v>0.42</v>
@@ -12192,16 +12186,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D47" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E47" t="n">
         <v>0.95</v>
@@ -12281,16 +12275,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D48" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -12370,16 +12364,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D49" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E49" t="n">
         <v>0.67</v>
@@ -12459,16 +12453,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D50" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E50" t="n">
         <v>1.34</v>
@@ -12548,16 +12542,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D51" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -12637,16 +12631,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D52" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E52" t="n">
         <v>0.505</v>
@@ -12726,16 +12720,16 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D53" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E53" t="n">
         <v>1.01</v>
@@ -12815,16 +12809,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D54" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -12904,16 +12898,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D55" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -12993,16 +12987,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D56" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E56" t="n">
         <v>0.61</v>
@@ -13082,16 +13076,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D57" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E57" t="n">
         <v>1.22</v>
@@ -13171,16 +13165,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B58" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D58" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -13260,16 +13254,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C59" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E59" t="n">
         <v>0.735</v>
@@ -13349,16 +13343,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D60" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E60" t="n">
         <v>1.47</v>
@@ -13438,16 +13432,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D61" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -13527,16 +13521,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D62" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E62" t="n">
         <v>0.575</v>
@@ -13616,16 +13610,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D63" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E63" t="n">
         <v>1.15</v>
@@ -13705,16 +13699,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D64" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -13792,16 +13786,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D65" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E65" t="n">
         <v>1.05</v>
@@ -13879,16 +13873,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D66" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E66" t="n">
         <v>2.1</v>
@@ -13966,16 +13960,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D67" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -14053,16 +14047,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D68" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E68" t="n">
         <v>1.75</v>
@@ -14142,16 +14136,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C69" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D69" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E69" t="n">
         <v>3.5</v>
@@ -14231,16 +14225,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C70" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D70" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -14318,16 +14312,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C71" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D71" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -14405,16 +14399,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C72" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E72" t="n">
         <v>2.05</v>
@@ -14492,16 +14486,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D73" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -14579,16 +14573,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B74" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D74" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -14666,16 +14660,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B75" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D75" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E75" t="n">
         <v>2.05</v>
@@ -14755,16 +14749,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B76" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C76" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D76" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -14842,16 +14836,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C77" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D77" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -14931,16 +14925,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B78" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C78" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D78" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E78" t="n">
         <v>2.05</v>
@@ -15020,16 +15014,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B79" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C79" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D79" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -15109,16 +15103,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C80" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D80" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E80" t="n">
         <v>1.35</v>
@@ -15198,16 +15192,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C81" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D81" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E81" t="n">
         <v>2.7</v>
@@ -15287,16 +15281,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B82" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C82" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D82" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -15376,16 +15370,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B83" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C83" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D83" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E83" t="n">
         <v>0.7</v>
@@ -15465,16 +15459,16 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B84" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C84" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D84" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E84" t="n">
         <v>1.85</v>
@@ -15554,16 +15548,16 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B85" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C85" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D85" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -15643,16 +15637,16 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B86" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C86" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D86" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E86" t="n">
         <v>0.5</v>
@@ -15732,16 +15726,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B87" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C87" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D87" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E87" t="n">
         <v>1.05</v>
@@ -15783,16 +15777,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B88" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C88" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D88" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -15872,16 +15866,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B89" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C89" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D89" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E89" t="n">
         <v>0.5</v>
@@ -15961,16 +15955,16 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B90" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C90" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D90" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -16012,16 +16006,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B91" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C91" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -16101,16 +16095,16 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B92" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C92" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D92" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E92" t="n">
         <v>1.18</v>
@@ -16190,16 +16184,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B93" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C93" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D93" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E93" t="n">
         <v>2.34</v>
@@ -16279,16 +16273,16 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B94" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C94" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D94" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -16368,16 +16362,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B95" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C95" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D95" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E95" t="n">
         <v>1.08</v>
@@ -16457,16 +16451,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B96" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C96" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D96" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E96" t="n">
         <v>2.15</v>
@@ -16546,16 +16540,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B97" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C97" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D97" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -16635,16 +16629,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C98" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D98" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E98" t="n">
         <v>1.5</v>
@@ -16724,16 +16718,16 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B99" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C99" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D99" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E99" t="n">
         <v>3</v>
@@ -16813,16 +16807,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B100" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C100" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D100" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -16902,16 +16896,16 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B101" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C101" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D101" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E101" t="n">
         <v>0.9</v>
@@ -16989,16 +16983,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B102" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C102" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D102" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E102" t="n">
         <v>1.8</v>
@@ -17040,16 +17034,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B103" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C103" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D103" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -17129,16 +17123,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B104" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C104" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D104" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E104" t="n">
         <v>0.9</v>
@@ -17218,16 +17212,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B105" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D105" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E105" t="n">
         <v>1.8</v>
@@ -17307,16 +17301,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B106" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D106" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -17396,16 +17390,16 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B107" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E107" t="n">
         <v>0.8</v>
@@ -17485,16 +17479,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B108" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D108" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E108" t="n">
         <v>1.65</v>
@@ -17536,16 +17530,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B109" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D109" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -17625,16 +17619,16 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B110" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D110" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E110" t="n">
         <v>0.7</v>
@@ -17714,16 +17708,16 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B111" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C111" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D111" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E111" t="n">
         <v>1.35</v>
@@ -17803,16 +17797,16 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B112" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C112" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D112" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -17892,16 +17886,16 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B113" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C113" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D113" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -17981,16 +17975,16 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B114" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C114" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D114" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E114" t="n">
         <v>4</v>
@@ -18070,16 +18064,16 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C115" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D115" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -18159,16 +18153,16 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C116" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D116" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E116" t="n">
         <v>0.9</v>
@@ -18248,16 +18242,16 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B117" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C117" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D117" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E117" t="n">
         <v>1.8</v>
@@ -18337,16 +18331,16 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B118" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C118" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D118" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -18426,16 +18420,16 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B119" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C119" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D119" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E119" t="n">
         <v>1.05</v>
@@ -18515,16 +18509,16 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B120" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C120" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D120" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E120" t="n">
         <v>2.15</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <si>
     <t xml:space="preserve">sample_id</t>
   </si>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">Feminine products, condoms, plastic</t>
   </si>
   <si>
-    <t xml:space="preserve">19-KK13022024</t>
+    <t xml:space="preserve">19-KK-13022024</t>
   </si>
   <si>
     <t xml:space="preserve">20b</t>
@@ -699,12 +699,6 @@
   </si>
   <si>
     <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-KK130202024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19-K-13022024</t>
   </si>
 </sst>
 </file>
@@ -18064,7 +18058,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="B115" t="s">
         <v>186</v>
@@ -18153,7 +18147,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="B116" t="s">
         <v>186</v>
@@ -18242,7 +18236,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="B117" t="s">
         <v>186</v>
@@ -18331,7 +18325,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="B118" t="s">
         <v>189</v>
@@ -18420,7 +18414,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="B119" t="s">
         <v>189</v>
@@ -18509,7 +18503,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="B120" t="s">
         <v>189</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -13713,9 +13713,7 @@
       <c r="G64" t="n">
         <v>0.296</v>
       </c>
-      <c r="H64" t="n">
-        <v>2.93</v>
-      </c>
+      <c r="H64"/>
       <c r="I64" t="n">
         <v>-216</v>
       </c>
@@ -13800,9 +13798,7 @@
       <c r="G65" t="n">
         <v>0.062</v>
       </c>
-      <c r="H65" t="n">
-        <v>2.88</v>
-      </c>
+      <c r="H65"/>
       <c r="I65" t="n">
         <v>-260</v>
       </c>
@@ -13887,9 +13883,7 @@
       <c r="G66" t="n">
         <v>0.057</v>
       </c>
-      <c r="H66" t="n">
-        <v>3.9</v>
-      </c>
+      <c r="H66"/>
       <c r="I66" t="n">
         <v>-276</v>
       </c>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -4510,7 +4510,7 @@
         <v>153</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
         <v>35</v>
@@ -4851,7 +4851,7 @@
         <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="F35" t="n">
         <v>88</v>
@@ -5529,7 +5529,7 @@
         <v>153</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="F41" t="n">
         <v>52</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t xml:space="preserve">sample_id</t>
   </si>
@@ -197,9 +197,6 @@
     <t xml:space="preserve">Saanich</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitchen Laundry Bathing Toilet</t>
-  </si>
-  <si>
     <t xml:space="preserve">04-Saanich-12042023</t>
   </si>
   <si>
@@ -413,9 +410,6 @@
     <t xml:space="preserve">12a</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitchen Toilet Bathing Laundry</t>
-  </si>
-  <si>
     <t xml:space="preserve">Feminine products, plastic</t>
   </si>
   <si>
@@ -501,9 +495,6 @@
   </si>
   <si>
     <t xml:space="preserve">16a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitchen Bathing Laundry</t>
   </si>
   <si>
     <t xml:space="preserve">11-KK-30012024</t>
@@ -1445,7 +1436,7 @@
       <c r="V4"/>
       <c r="W4"/>
       <c r="X4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
@@ -1491,10 +1482,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>45028</v>
@@ -1524,19 +1515,19 @@
         <v>45</v>
       </c>
       <c r="L5" t="s">
+        <v>62</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
         <v>63</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" t="s">
-        <v>64</v>
       </c>
       <c r="Q5" t="s">
         <v>48</v>
@@ -1556,7 +1547,7 @@
       <c r="V5"/>
       <c r="W5"/>
       <c r="X5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
@@ -1602,16 +1593,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
         <v>66</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>
@@ -1635,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="L6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
         <v>63</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" t="s">
-        <v>64</v>
       </c>
       <c r="Q6" t="s">
         <v>48</v>
       </c>
       <c r="R6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S6" t="b">
         <v>1</v>
@@ -1713,19 +1704,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
         <v>410</v>
@@ -1744,7 +1735,7 @@
         <v>45</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
@@ -1756,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q7" t="s">
         <v>48</v>
@@ -1776,7 +1767,7 @@
       <c r="V7"/>
       <c r="W7"/>
       <c r="X7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
@@ -1803,7 +1794,7 @@
         <v>52</v>
       </c>
       <c r="AG7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH7"/>
       <c r="AI7" t="b">
@@ -1822,10 +1813,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>45042</v>
@@ -1855,7 +1846,7 @@
         <v>45</v>
       </c>
       <c r="L8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -1935,10 +1926,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
         <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>45042</v>
@@ -2024,10 +2015,10 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH9"/>
       <c r="AI9" t="b">
@@ -2044,10 +2035,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
         <v>81</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>45055</v>
@@ -2056,7 +2047,7 @@
         <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
         <v>304</v>
@@ -2069,25 +2060,25 @@
       </c>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K10" t="s">
         <v>45</v>
       </c>
       <c r="L10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
         <v>63</v>
-      </c>
-      <c r="M10" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" t="b">
-        <v>1</v>
-      </c>
-      <c r="P10" t="s">
-        <v>64</v>
       </c>
       <c r="Q10" t="s">
         <v>48</v>
@@ -2134,7 +2125,7 @@
         <v>52</v>
       </c>
       <c r="AG10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH10"/>
       <c r="AI10" t="b">
@@ -2151,10 +2142,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
         <v>85</v>
-      </c>
-      <c r="B11" t="s">
-        <v>86</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45055</v>
@@ -2163,7 +2154,7 @@
         <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
         <v>368</v>
@@ -2176,25 +2167,25 @@
       </c>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K11" t="s">
         <v>45</v>
       </c>
       <c r="L11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
         <v>63</v>
-      </c>
-      <c r="M11" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" t="b">
-        <v>1</v>
-      </c>
-      <c r="P11" t="s">
-        <v>64</v>
       </c>
       <c r="Q11" t="s">
         <v>48</v>
@@ -2241,7 +2232,7 @@
         <v>52</v>
       </c>
       <c r="AG11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH11"/>
       <c r="AI11" t="b">
@@ -2258,10 +2249,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
         <v>88</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
@@ -2291,25 +2282,25 @@
         <v>45</v>
       </c>
       <c r="L12" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="s">
         <v>63</v>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" t="s">
-        <v>64</v>
       </c>
       <c r="Q12" t="s">
         <v>48</v>
       </c>
       <c r="R12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S12" t="b">
         <v>1</v>
@@ -2319,10 +2310,10 @@
       </c>
       <c r="U12"/>
       <c r="V12" t="s">
+        <v>89</v>
+      </c>
+      <c r="W12" t="s">
         <v>90</v>
-      </c>
-      <c r="W12" t="s">
-        <v>91</v>
       </c>
       <c r="X12" t="s">
         <v>51</v>
@@ -2373,10 +2364,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" t="s">
         <v>92</v>
-      </c>
-      <c r="B13" t="s">
-        <v>93</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
@@ -2406,19 +2397,19 @@
         <v>45</v>
       </c>
       <c r="L13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
         <v>63</v>
-      </c>
-      <c r="M13" t="b">
-        <v>0</v>
-      </c>
-      <c r="N13" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" t="s">
-        <v>64</v>
       </c>
       <c r="Q13" t="s">
         <v>48</v>
@@ -2434,7 +2425,7 @@
       </c>
       <c r="U13"/>
       <c r="V13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W13"/>
       <c r="X13" t="s">
@@ -2465,7 +2456,7 @@
         <v>52</v>
       </c>
       <c r="AG13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH13"/>
       <c r="AI13" t="b">
@@ -2484,10 +2475,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
         <v>95</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -2496,7 +2487,7 @@
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -2515,19 +2506,19 @@
         <v>45</v>
       </c>
       <c r="L14" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
         <v>63</v>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" t="b">
-        <v>1</v>
-      </c>
-      <c r="P14" t="s">
-        <v>64</v>
       </c>
       <c r="Q14" t="s">
         <v>48</v>
@@ -2547,7 +2538,7 @@
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
@@ -2595,10 +2586,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
         <v>98</v>
-      </c>
-      <c r="B15" t="s">
-        <v>99</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -2628,7 +2619,7 @@
         <v>45</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
@@ -2659,7 +2650,7 @@
       </c>
       <c r="V15"/>
       <c r="W15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X15" t="s">
         <v>51</v>
@@ -2708,10 +2699,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
         <v>101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -2720,7 +2711,7 @@
         <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -2739,25 +2730,25 @@
         <v>45</v>
       </c>
       <c r="L16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="s">
         <v>63</v>
-      </c>
-      <c r="M16" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" t="b">
-        <v>1</v>
-      </c>
-      <c r="P16" t="s">
-        <v>64</v>
       </c>
       <c r="Q16" t="s">
         <v>48</v>
       </c>
       <c r="R16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S16" t="b">
         <v>1</v>
@@ -2771,7 +2762,7 @@
       <c r="V16"/>
       <c r="W16"/>
       <c r="X16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
@@ -2815,10 +2806,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
         <v>103</v>
-      </c>
-      <c r="B17" t="s">
-        <v>104</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -2848,7 +2839,7 @@
         <v>45</v>
       </c>
       <c r="L17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
@@ -2860,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q17" t="s">
         <v>48</v>
@@ -2926,10 +2917,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
         <v>106</v>
-      </c>
-      <c r="B18" t="s">
-        <v>107</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -2959,19 +2950,19 @@
         <v>45</v>
       </c>
       <c r="L18" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="s">
         <v>63</v>
-      </c>
-      <c r="M18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O18" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" t="s">
-        <v>64</v>
       </c>
       <c r="Q18" t="s">
         <v>48</v>
@@ -3037,10 +3028,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
         <v>108</v>
-      </c>
-      <c r="B19" t="s">
-        <v>109</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -3070,19 +3061,19 @@
         <v>45</v>
       </c>
       <c r="L19" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="s">
         <v>63</v>
-      </c>
-      <c r="M19" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" t="b">
-        <v>1</v>
-      </c>
-      <c r="P19" t="s">
-        <v>64</v>
       </c>
       <c r="Q19" t="s">
         <v>48</v>
@@ -3099,7 +3090,7 @@
       <c r="U19"/>
       <c r="V19"/>
       <c r="W19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="X19" t="s">
         <v>51</v>
@@ -3148,10 +3139,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
         <v>111</v>
-      </c>
-      <c r="B20" t="s">
-        <v>112</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -3172,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J20" t="s">
         <v>44</v>
@@ -3181,25 +3172,25 @@
         <v>45</v>
       </c>
       <c r="L20" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="s">
         <v>63</v>
-      </c>
-      <c r="M20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" t="s">
-        <v>64</v>
       </c>
       <c r="Q20" t="s">
         <v>48</v>
       </c>
       <c r="R20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -3261,10 +3252,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
         <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>116</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -3294,19 +3285,19 @@
         <v>45</v>
       </c>
       <c r="L21" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="s">
         <v>63</v>
-      </c>
-      <c r="M21" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21" t="b">
-        <v>1</v>
-      </c>
-      <c r="P21" t="s">
-        <v>64</v>
       </c>
       <c r="Q21" t="s">
         <v>48</v>
@@ -3374,10 +3365,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" t="s">
         <v>117</v>
-      </c>
-      <c r="B22" t="s">
-        <v>118</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -3386,7 +3377,7 @@
         <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
         <v>200</v>
@@ -3405,19 +3396,19 @@
         <v>45</v>
       </c>
       <c r="L22" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="s">
         <v>63</v>
-      </c>
-      <c r="M22" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" t="b">
-        <v>1</v>
-      </c>
-      <c r="P22" t="s">
-        <v>64</v>
       </c>
       <c r="Q22" t="s">
         <v>48</v>
@@ -3437,7 +3428,7 @@
       <c r="V22"/>
       <c r="W22"/>
       <c r="X22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
@@ -3485,16 +3476,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
         <v>119</v>
-      </c>
-      <c r="B23" t="s">
-        <v>120</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -3518,19 +3509,19 @@
         <v>45</v>
       </c>
       <c r="L23" t="s">
+        <v>62</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="s">
         <v>63</v>
-      </c>
-      <c r="M23" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" t="s">
-        <v>64</v>
       </c>
       <c r="Q23" t="s">
         <v>48</v>
@@ -3550,7 +3541,7 @@
       <c r="V23"/>
       <c r="W23"/>
       <c r="X23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
@@ -3594,19 +3585,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" t="s">
         <v>123</v>
-      </c>
-      <c r="B24" t="s">
-        <v>124</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
         <v>23</v>
@@ -3625,7 +3616,7 @@
         <v>45</v>
       </c>
       <c r="L24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
@@ -3637,13 +3628,13 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q24" t="s">
         <v>48</v>
       </c>
       <c r="R24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S24" t="b">
         <v>1</v>
@@ -3656,10 +3647,10 @@
       </c>
       <c r="V24"/>
       <c r="W24" t="s">
+        <v>126</v>
+      </c>
+      <c r="X24" t="s">
         <v>127</v>
-      </c>
-      <c r="X24" t="s">
-        <v>128</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
@@ -3686,7 +3677,7 @@
         <v>52</v>
       </c>
       <c r="AG24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH24"/>
       <c r="AI24" t="b">
@@ -3700,21 +3691,21 @@
         <v>1</v>
       </c>
       <c r="AM24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
         <v>130</v>
-      </c>
-      <c r="B25" t="s">
-        <v>131</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
         <v>42</v>
@@ -3729,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J25" t="s">
         <v>44</v>
@@ -3738,7 +3729,7 @@
         <v>45</v>
       </c>
       <c r="L25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
@@ -3750,13 +3741,13 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q25" t="s">
         <v>48</v>
       </c>
       <c r="R25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S25" t="b">
         <v>1</v>
@@ -3769,10 +3760,10 @@
       </c>
       <c r="V25"/>
       <c r="W25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X25" t="s">
-        <v>132</v>
+        <v>51</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
@@ -3799,7 +3790,7 @@
         <v>52</v>
       </c>
       <c r="AG25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH25"/>
       <c r="AI25" t="b">
@@ -3815,21 +3806,21 @@
         <v>1</v>
       </c>
       <c r="AM25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
         <v>42</v>
@@ -3844,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J26" t="s">
         <v>44</v>
@@ -3853,7 +3844,7 @@
         <v>45</v>
       </c>
       <c r="L26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
@@ -3865,13 +3856,13 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q26" t="s">
         <v>48</v>
       </c>
       <c r="R26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S26" t="b">
         <v>1</v>
@@ -3884,10 +3875,10 @@
       </c>
       <c r="V26"/>
       <c r="W26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
@@ -3914,7 +3905,7 @@
         <v>52</v>
       </c>
       <c r="AG26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH26"/>
       <c r="AI26" t="b">
@@ -3930,21 +3921,21 @@
         <v>1</v>
       </c>
       <c r="AM26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
         <v>42</v>
@@ -3959,7 +3950,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J27" t="s">
         <v>44</v>
@@ -3968,7 +3959,7 @@
         <v>45</v>
       </c>
       <c r="L27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
@@ -3980,13 +3971,13 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q27" t="s">
         <v>48</v>
       </c>
       <c r="R27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S27" t="b">
         <v>1</v>
@@ -3999,10 +3990,10 @@
       </c>
       <c r="V27"/>
       <c r="W27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -4029,7 +4020,7 @@
         <v>52</v>
       </c>
       <c r="AG27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH27"/>
       <c r="AI27" t="b">
@@ -4045,21 +4036,21 @@
         <v>1</v>
       </c>
       <c r="AM27" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
         <v>42</v>
@@ -4074,7 +4065,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J28" t="s">
         <v>44</v>
@@ -4083,7 +4074,7 @@
         <v>45</v>
       </c>
       <c r="L28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
@@ -4095,13 +4086,13 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q28" t="s">
         <v>48</v>
       </c>
       <c r="R28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S28" t="b">
         <v>1</v>
@@ -4114,10 +4105,10 @@
       </c>
       <c r="V28"/>
       <c r="W28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
@@ -4144,7 +4135,7 @@
         <v>52</v>
       </c>
       <c r="AG28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH28"/>
       <c r="AI28" t="b">
@@ -4160,21 +4151,21 @@
         <v>1</v>
       </c>
       <c r="AM28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E29" t="s">
         <v>42</v>
@@ -4189,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J29" t="s">
         <v>44</v>
@@ -4198,7 +4189,7 @@
         <v>45</v>
       </c>
       <c r="L29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M29" t="b">
         <v>1</v>
@@ -4210,13 +4201,13 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q29" t="s">
         <v>48</v>
       </c>
       <c r="R29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S29" t="b">
         <v>1</v>
@@ -4229,10 +4220,10 @@
       </c>
       <c r="V29"/>
       <c r="W29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
@@ -4259,7 +4250,7 @@
         <v>52</v>
       </c>
       <c r="AG29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH29"/>
       <c r="AI29" t="b">
@@ -4278,16 +4269,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
         <v>42</v>
@@ -4302,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J30" t="s">
         <v>44</v>
@@ -4311,7 +4302,7 @@
         <v>45</v>
       </c>
       <c r="L30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
@@ -4323,13 +4314,13 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q30" t="s">
         <v>48</v>
       </c>
       <c r="R30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S30" t="b">
         <v>1</v>
@@ -4342,10 +4333,10 @@
       </c>
       <c r="V30"/>
       <c r="W30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="X30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
@@ -4369,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="AF30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG30" t="s">
         <v>53</v>
@@ -4384,21 +4375,21 @@
         <v>1</v>
       </c>
       <c r="AM30" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
         <v>42</v>
@@ -4413,7 +4404,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J31" t="s">
         <v>44</v>
@@ -4422,7 +4413,7 @@
         <v>45</v>
       </c>
       <c r="L31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
@@ -4434,13 +4425,13 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" t="s">
         <v>48</v>
       </c>
       <c r="R31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S31" t="b">
         <v>1</v>
@@ -4478,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="AF31" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH31"/>
       <c r="AI31"/>
@@ -4493,21 +4484,21 @@
         <v>1</v>
       </c>
       <c r="AM31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E32" t="s">
         <v>42</v>
@@ -4526,10 +4517,10 @@
         <v>44</v>
       </c>
       <c r="K32" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
@@ -4541,13 +4532,13 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" t="s">
         <v>48</v>
       </c>
       <c r="R32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S32" t="b">
         <v>1</v>
@@ -4560,10 +4551,10 @@
       </c>
       <c r="V32"/>
       <c r="W32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y32" t="b">
         <v>1</v>
@@ -4604,21 +4595,21 @@
         <v>1</v>
       </c>
       <c r="AM32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
         <v>42</v>
@@ -4633,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J33" t="s">
         <v>44</v>
@@ -4642,7 +4633,7 @@
         <v>45</v>
       </c>
       <c r="L33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -4654,13 +4645,13 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q33" t="s">
         <v>48</v>
       </c>
       <c r="R33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S33" t="b">
         <v>1</v>
@@ -4673,10 +4664,10 @@
       </c>
       <c r="V33"/>
       <c r="W33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X33" t="s">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="Y33" t="b">
         <v>0</v>
@@ -4703,7 +4694,7 @@
         <v>52</v>
       </c>
       <c r="AG33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH33" t="n">
         <v>20</v>
@@ -4724,16 +4715,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D34" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
         <v>42</v>
@@ -4748,7 +4739,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J34" t="s">
         <v>44</v>
@@ -4757,7 +4748,7 @@
         <v>45</v>
       </c>
       <c r="L34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
@@ -4769,13 +4760,13 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q34" t="s">
         <v>48</v>
       </c>
       <c r="R34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S34" t="b">
         <v>1</v>
@@ -4788,10 +4779,10 @@
       </c>
       <c r="V34"/>
       <c r="W34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y34" t="b">
         <v>1</v>
@@ -4818,7 +4809,7 @@
         <v>52</v>
       </c>
       <c r="AG34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH34"/>
       <c r="AI34" t="b">
@@ -4834,21 +4825,21 @@
         <v>1</v>
       </c>
       <c r="AM34" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E35" t="s">
         <v>42</v>
@@ -4870,7 +4861,7 @@
         <v>45</v>
       </c>
       <c r="L35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -4886,7 +4877,7 @@
         <v>48</v>
       </c>
       <c r="R35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S35" t="b">
         <v>1</v>
@@ -4899,10 +4890,10 @@
       </c>
       <c r="V35"/>
       <c r="W35" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Y35" t="b">
         <v>1</v>
@@ -4945,21 +4936,21 @@
         <v>1</v>
       </c>
       <c r="AM35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E36" t="s">
         <v>42</v>
@@ -4974,7 +4965,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J36" t="s">
         <v>44</v>
@@ -4983,7 +4974,7 @@
         <v>45</v>
       </c>
       <c r="L36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
@@ -4995,13 +4986,13 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q36" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S36" t="b">
         <v>1</v>
@@ -5014,10 +5005,10 @@
       </c>
       <c r="V36"/>
       <c r="W36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y36" t="b">
         <v>1</v>
@@ -5041,7 +5032,7 @@
         <v>1</v>
       </c>
       <c r="AF36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG36" t="s">
         <v>53</v>
@@ -5060,21 +5051,21 @@
         <v>1</v>
       </c>
       <c r="AM36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
         <v>42</v>
@@ -5089,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J37" t="s">
         <v>44</v>
@@ -5098,7 +5089,7 @@
         <v>45</v>
       </c>
       <c r="L37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M37" t="b">
         <v>1</v>
@@ -5110,13 +5101,13 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q37" t="s">
         <v>48</v>
       </c>
       <c r="R37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S37" t="b">
         <v>1</v>
@@ -5129,7 +5120,7 @@
       </c>
       <c r="V37"/>
       <c r="W37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X37" t="s">
         <v>51</v>
@@ -5178,16 +5169,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E38" t="s">
         <v>42</v>
@@ -5202,7 +5193,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J38" t="s">
         <v>44</v>
@@ -5211,7 +5202,7 @@
         <v>45</v>
       </c>
       <c r="L38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
@@ -5223,13 +5214,13 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S38" t="b">
         <v>1</v>
@@ -5242,10 +5233,10 @@
       </c>
       <c r="V38"/>
       <c r="W38" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y38" t="b">
         <v>1</v>
@@ -5286,24 +5277,24 @@
         <v>1</v>
       </c>
       <c r="AM38" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D39" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F39" t="n">
         <v>10</v>
@@ -5322,7 +5313,7 @@
         <v>45</v>
       </c>
       <c r="L39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M39" t="b">
         <v>1</v>
@@ -5334,13 +5325,13 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q39" t="s">
         <v>48</v>
       </c>
       <c r="R39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S39" t="b">
         <v>1</v>
@@ -5353,10 +5344,10 @@
       </c>
       <c r="V39"/>
       <c r="W39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y39" t="b">
         <v>1</v>
@@ -5399,21 +5390,21 @@
         <v>1</v>
       </c>
       <c r="AM39" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D40" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s">
         <v>42</v>
@@ -5428,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
         <v>44</v>
@@ -5437,7 +5428,7 @@
         <v>45</v>
       </c>
       <c r="L40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
@@ -5450,10 +5441,10 @@
       </c>
       <c r="P40"/>
       <c r="Q40" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="R40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S40" t="b">
         <v>1</v>
@@ -5466,10 +5457,10 @@
       </c>
       <c r="V40"/>
       <c r="W40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y40" t="b">
         <v>1</v>
@@ -5512,21 +5503,21 @@
         <v>1</v>
       </c>
       <c r="AM40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D41" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E41" t="s">
         <v>42</v>
@@ -5548,7 +5539,7 @@
         <v>45</v>
       </c>
       <c r="L41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -5560,13 +5551,13 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q41" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S41" t="b">
         <v>1</v>
@@ -5579,10 +5570,10 @@
       </c>
       <c r="V41"/>
       <c r="W41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
@@ -5625,21 +5616,21 @@
         <v>1</v>
       </c>
       <c r="AM41" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E42" t="s">
         <v>42</v>
@@ -5654,7 +5645,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J42" t="s">
         <v>44</v>
@@ -5663,7 +5654,7 @@
         <v>45</v>
       </c>
       <c r="L42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -5675,13 +5666,13 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q42" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S42" t="b">
         <v>1</v>
@@ -5695,7 +5686,7 @@
       <c r="V42"/>
       <c r="W42"/>
       <c r="X42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
@@ -5738,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="AM42" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -5763,25 +5754,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G1" t="s">
         <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2">
@@ -5882,10 +5873,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>45028</v>
@@ -5914,10 +5905,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
         <v>66</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>45035</v>
@@ -5946,10 +5937,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>45035</v>
@@ -5978,10 +5969,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>45042</v>
@@ -6010,10 +6001,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
         <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>45042</v>
@@ -6042,10 +6033,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
         <v>81</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>45055</v>
@@ -6074,10 +6065,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
         <v>85</v>
-      </c>
-      <c r="B11" t="s">
-        <v>86</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45055</v>
@@ -6106,10 +6097,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
         <v>88</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
@@ -6138,10 +6129,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" t="s">
         <v>92</v>
-      </c>
-      <c r="B13" t="s">
-        <v>93</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
@@ -6170,10 +6161,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
         <v>95</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -6202,10 +6193,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
         <v>98</v>
-      </c>
-      <c r="B15" t="s">
-        <v>99</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -6234,10 +6225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
         <v>101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -6266,10 +6257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
         <v>103</v>
-      </c>
-      <c r="B17" t="s">
-        <v>104</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -6298,10 +6289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
         <v>106</v>
-      </c>
-      <c r="B18" t="s">
-        <v>107</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -6330,10 +6321,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
         <v>108</v>
-      </c>
-      <c r="B19" t="s">
-        <v>109</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -6362,10 +6353,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
         <v>111</v>
-      </c>
-      <c r="B20" t="s">
-        <v>112</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -6394,10 +6385,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
         <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>116</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -6426,10 +6417,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" t="s">
         <v>117</v>
-      </c>
-      <c r="B22" t="s">
-        <v>118</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -6458,10 +6449,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
         <v>119</v>
-      </c>
-      <c r="B23" t="s">
-        <v>120</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
@@ -6490,10 +6481,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" t="s">
         <v>123</v>
-      </c>
-      <c r="B24" t="s">
-        <v>124</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
@@ -6522,10 +6513,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
         <v>130</v>
-      </c>
-      <c r="B25" t="s">
-        <v>131</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
@@ -6554,10 +6545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
@@ -6586,10 +6577,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
@@ -6618,10 +6609,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
@@ -6650,10 +6641,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
@@ -6682,10 +6673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
@@ -6714,10 +6705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
@@ -6746,10 +6737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
@@ -6778,10 +6769,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
@@ -6810,10 +6801,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
@@ -6842,10 +6833,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
@@ -6874,10 +6865,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
@@ -6906,10 +6897,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
@@ -6938,10 +6929,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
@@ -6970,10 +6961,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
@@ -7002,10 +6993,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
@@ -7034,10 +7025,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
@@ -7066,10 +7057,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
@@ -7121,13 +7112,13 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2">
@@ -7201,10 +7192,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>45028</v>
@@ -7224,10 +7215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
         <v>66</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>45035</v>
@@ -7247,10 +7238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>45035</v>
@@ -7270,10 +7261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>45042</v>
@@ -7293,10 +7284,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
         <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>45042</v>
@@ -7316,10 +7307,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
         <v>81</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>45055</v>
@@ -7339,10 +7330,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
         <v>85</v>
-      </c>
-      <c r="B11" t="s">
-        <v>86</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45055</v>
@@ -7362,10 +7353,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
         <v>88</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
@@ -7385,10 +7376,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" t="s">
         <v>92</v>
-      </c>
-      <c r="B13" t="s">
-        <v>93</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
@@ -7408,10 +7399,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
         <v>95</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -7431,10 +7422,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
         <v>98</v>
-      </c>
-      <c r="B15" t="s">
-        <v>99</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -7454,10 +7445,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
         <v>101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -7477,10 +7468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
         <v>103</v>
-      </c>
-      <c r="B17" t="s">
-        <v>104</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -7500,10 +7491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
         <v>106</v>
-      </c>
-      <c r="B18" t="s">
-        <v>107</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -7523,10 +7514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
         <v>108</v>
-      </c>
-      <c r="B19" t="s">
-        <v>109</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -7546,10 +7537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
         <v>111</v>
-      </c>
-      <c r="B20" t="s">
-        <v>112</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -7569,10 +7560,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
         <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>116</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -7592,10 +7583,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" t="s">
         <v>117</v>
-      </c>
-      <c r="B22" t="s">
-        <v>118</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -7615,10 +7606,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
         <v>119</v>
-      </c>
-      <c r="B23" t="s">
-        <v>120</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
@@ -7638,10 +7629,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" t="s">
         <v>123</v>
-      </c>
-      <c r="B24" t="s">
-        <v>124</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
@@ -7661,10 +7652,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
         <v>130</v>
-      </c>
-      <c r="B25" t="s">
-        <v>131</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
@@ -7684,10 +7675,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
@@ -7707,10 +7698,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
@@ -7730,10 +7721,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
@@ -7753,10 +7744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
@@ -7776,10 +7767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
@@ -7799,10 +7790,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
@@ -7822,10 +7813,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
@@ -7845,10 +7836,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
@@ -7868,10 +7859,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
@@ -7891,10 +7882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
@@ -7914,10 +7905,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
@@ -7937,10 +7928,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
@@ -7960,10 +7951,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
@@ -7983,10 +7974,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
@@ -8006,10 +7997,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
@@ -8029,10 +8020,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
@@ -8052,10 +8043,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
@@ -8095,82 +8086,82 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1" t="s">
         <v>200</v>
       </c>
-      <c r="E1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>201</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>202</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>203</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>204</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>205</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>206</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>207</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>208</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>209</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>210</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>211</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>212</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>213</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>214</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>215</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>216</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>217</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>218</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>219</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
         <v>220</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
         <v>221</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>222</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="2">
@@ -8184,7 +8175,7 @@
         <v>45022</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -8273,7 +8264,7 @@
         <v>45022</v>
       </c>
       <c r="D3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E3" t="n">
         <v>0.65</v>
@@ -8362,7 +8353,7 @@
         <v>45022</v>
       </c>
       <c r="D4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E4" t="n">
         <v>1.31</v>
@@ -8451,7 +8442,7 @@
         <v>45022</v>
       </c>
       <c r="D5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -8540,7 +8531,7 @@
         <v>45022</v>
       </c>
       <c r="D6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
@@ -8629,7 +8620,7 @@
         <v>45022</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E7" t="n">
         <v>1.82</v>
@@ -8718,7 +8709,7 @@
         <v>45028</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -8807,7 +8798,7 @@
         <v>45028</v>
       </c>
       <c r="D9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
@@ -8896,7 +8887,7 @@
         <v>45028</v>
       </c>
       <c r="D10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E10" t="n">
         <v>1.85</v>
@@ -8976,16 +8967,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
         <v>61</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -9065,16 +9056,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
         <v>61</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -9154,16 +9145,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
         <v>61</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45028</v>
       </c>
       <c r="D13" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E13" t="n">
         <v>1.05</v>
@@ -9243,16 +9234,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D14" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -9332,16 +9323,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
         <v>66</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D15" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E15" t="n">
         <v>0.46</v>
@@ -9421,16 +9412,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
         <v>66</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D16" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E16" t="n">
         <v>0.92</v>
@@ -9510,16 +9501,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
         <v>70</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D17" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -9599,16 +9590,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
         <v>70</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E18" t="n">
         <v>0.7</v>
@@ -9688,16 +9679,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
         <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45035</v>
       </c>
       <c r="D19" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E19" t="n">
         <v>1.39</v>
@@ -9777,16 +9768,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" t="s">
         <v>76</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D20" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -9866,16 +9857,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
         <v>76</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D21" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E21" t="n">
         <v>0.7</v>
@@ -9955,16 +9946,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
         <v>76</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D22" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E22" t="n">
         <v>1.41</v>
@@ -10044,16 +10035,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
         <v>78</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D23" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10133,16 +10124,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s">
         <v>78</v>
-      </c>
-      <c r="B24" t="s">
-        <v>79</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D24" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E24" t="n">
         <v>0.52</v>
@@ -10222,16 +10213,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
         <v>78</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45042</v>
       </c>
       <c r="D25" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E25" t="n">
         <v>1.04</v>
@@ -10311,16 +10302,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
         <v>81</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D26" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -10400,16 +10391,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
         <v>81</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E27" t="n">
         <v>1.055</v>
@@ -10489,16 +10480,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
         <v>81</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D28" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E28" t="n">
         <v>2.11</v>
@@ -10578,16 +10569,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
         <v>85</v>
-      </c>
-      <c r="B29" t="s">
-        <v>86</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D29" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -10667,16 +10658,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s">
         <v>85</v>
-      </c>
-      <c r="B30" t="s">
-        <v>86</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D30" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E30" t="n">
         <v>0.45</v>
@@ -10756,16 +10747,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" t="s">
         <v>85</v>
-      </c>
-      <c r="B31" t="s">
-        <v>86</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45055</v>
       </c>
       <c r="D31" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E31" t="n">
         <v>1.92</v>
@@ -10845,16 +10836,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s">
         <v>88</v>
-      </c>
-      <c r="B32" t="s">
-        <v>89</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D32" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -10934,16 +10925,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" t="s">
         <v>92</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D33" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -11023,16 +11014,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s">
         <v>92</v>
-      </c>
-      <c r="B34" t="s">
-        <v>93</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D34" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E34" t="n">
         <v>0.55</v>
@@ -11112,16 +11103,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" t="s">
         <v>92</v>
-      </c>
-      <c r="B35" t="s">
-        <v>93</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D35" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E35" t="n">
         <v>1.15</v>
@@ -11201,16 +11192,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
         <v>95</v>
-      </c>
-      <c r="B36" t="s">
-        <v>96</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D36" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -11290,16 +11281,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" t="s">
         <v>95</v>
-      </c>
-      <c r="B37" t="s">
-        <v>96</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E37" t="n">
         <v>0.94</v>
@@ -11379,16 +11370,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" t="s">
         <v>95</v>
-      </c>
-      <c r="B38" t="s">
-        <v>96</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D38" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E38" t="n">
         <v>1.88</v>
@@ -11468,16 +11459,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" t="s">
         <v>98</v>
-      </c>
-      <c r="B39" t="s">
-        <v>99</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -11557,16 +11548,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" t="s">
         <v>98</v>
-      </c>
-      <c r="B40" t="s">
-        <v>99</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D40" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E40" t="n">
         <v>0.52</v>
@@ -11646,16 +11637,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" t="s">
         <v>98</v>
-      </c>
-      <c r="B41" t="s">
-        <v>99</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D41" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E41" t="n">
         <v>1.04</v>
@@ -11735,16 +11726,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" t="s">
         <v>101</v>
-      </c>
-      <c r="B42" t="s">
-        <v>102</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D42" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -11824,16 +11815,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" t="s">
         <v>101</v>
-      </c>
-      <c r="B43" t="s">
-        <v>102</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D43" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E43" t="n">
         <v>0.55</v>
@@ -11913,16 +11904,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" t="s">
         <v>101</v>
-      </c>
-      <c r="B44" t="s">
-        <v>102</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D44" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E44" t="n">
         <v>1.11</v>
@@ -12002,16 +11993,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" t="s">
         <v>103</v>
-      </c>
-      <c r="B45" t="s">
-        <v>104</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D45" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -12091,16 +12082,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" t="s">
         <v>103</v>
-      </c>
-      <c r="B46" t="s">
-        <v>104</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D46" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E46" t="n">
         <v>0.42</v>
@@ -12180,16 +12171,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" t="s">
         <v>103</v>
-      </c>
-      <c r="B47" t="s">
-        <v>104</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D47" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E47" t="n">
         <v>0.95</v>
@@ -12269,16 +12260,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" t="s">
         <v>106</v>
-      </c>
-      <c r="B48" t="s">
-        <v>107</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -12358,16 +12349,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" t="s">
         <v>106</v>
-      </c>
-      <c r="B49" t="s">
-        <v>107</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E49" t="n">
         <v>0.67</v>
@@ -12447,16 +12438,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" t="s">
         <v>106</v>
-      </c>
-      <c r="B50" t="s">
-        <v>107</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D50" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E50" t="n">
         <v>1.34</v>
@@ -12536,16 +12527,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" t="s">
         <v>108</v>
-      </c>
-      <c r="B51" t="s">
-        <v>109</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D51" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -12625,16 +12616,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s">
         <v>108</v>
-      </c>
-      <c r="B52" t="s">
-        <v>109</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E52" t="n">
         <v>0.505</v>
@@ -12714,16 +12705,16 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" t="s">
         <v>108</v>
-      </c>
-      <c r="B53" t="s">
-        <v>109</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D53" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E53" t="n">
         <v>1.01</v>
@@ -12803,16 +12794,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s">
         <v>111</v>
-      </c>
-      <c r="B54" t="s">
-        <v>112</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D54" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -12892,16 +12883,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" t="s">
         <v>115</v>
-      </c>
-      <c r="B55" t="s">
-        <v>116</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D55" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -12981,16 +12972,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" t="s">
         <v>115</v>
-      </c>
-      <c r="B56" t="s">
-        <v>116</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D56" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E56" t="n">
         <v>0.61</v>
@@ -13070,16 +13061,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" t="s">
         <v>115</v>
-      </c>
-      <c r="B57" t="s">
-        <v>116</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D57" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E57" t="n">
         <v>1.22</v>
@@ -13159,16 +13150,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" t="s">
         <v>117</v>
-      </c>
-      <c r="B58" t="s">
-        <v>118</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D58" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -13248,16 +13239,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" t="s">
         <v>117</v>
-      </c>
-      <c r="B59" t="s">
-        <v>118</v>
       </c>
       <c r="C59" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D59" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E59" t="n">
         <v>0.735</v>
@@ -13337,16 +13328,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" t="s">
         <v>117</v>
-      </c>
-      <c r="B60" t="s">
-        <v>118</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D60" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E60" t="n">
         <v>1.47</v>
@@ -13426,16 +13417,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" t="s">
         <v>119</v>
-      </c>
-      <c r="B61" t="s">
-        <v>120</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D61" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -13515,16 +13506,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" t="s">
         <v>119</v>
-      </c>
-      <c r="B62" t="s">
-        <v>120</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D62" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E62" t="n">
         <v>0.575</v>
@@ -13604,16 +13595,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" t="s">
         <v>119</v>
-      </c>
-      <c r="B63" t="s">
-        <v>120</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D63" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E63" t="n">
         <v>1.15</v>
@@ -13693,16 +13684,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>122</v>
+      </c>
+      <c r="B64" t="s">
         <v>123</v>
-      </c>
-      <c r="B64" t="s">
-        <v>124</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D64" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -13778,16 +13769,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" t="s">
         <v>123</v>
-      </c>
-      <c r="B65" t="s">
-        <v>124</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D65" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E65" t="n">
         <v>1.05</v>
@@ -13863,16 +13854,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>122</v>
+      </c>
+      <c r="B66" t="s">
         <v>123</v>
-      </c>
-      <c r="B66" t="s">
-        <v>124</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D66" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E66" t="n">
         <v>2.1</v>
@@ -13948,16 +13939,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>129</v>
+      </c>
+      <c r="B67" t="s">
         <v>130</v>
-      </c>
-      <c r="B67" t="s">
-        <v>131</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D67" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -14035,16 +14026,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" t="s">
         <v>130</v>
-      </c>
-      <c r="B68" t="s">
-        <v>131</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D68" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E68" t="n">
         <v>1.75</v>
@@ -14124,16 +14115,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>129</v>
+      </c>
+      <c r="B69" t="s">
         <v>130</v>
-      </c>
-      <c r="B69" t="s">
-        <v>131</v>
       </c>
       <c r="C69" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D69" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E69" t="n">
         <v>3.5</v>
@@ -14213,16 +14204,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C70" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D70" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -14300,16 +14291,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C71" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D71" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -14387,16 +14378,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C72" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D72" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E72" t="n">
         <v>2.05</v>
@@ -14474,16 +14465,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D73" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -14561,16 +14552,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D74" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -14648,16 +14639,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B75" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D75" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E75" t="n">
         <v>2.05</v>
@@ -14737,16 +14728,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B76" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C76" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D76" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -14824,16 +14815,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B77" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C77" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D77" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -14913,16 +14904,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B78" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C78" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D78" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E78" t="n">
         <v>2.05</v>
@@ -15002,16 +14993,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B79" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C79" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D79" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -15091,16 +15082,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B80" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C80" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D80" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E80" t="n">
         <v>1.35</v>
@@ -15180,16 +15171,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B81" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C81" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D81" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E81" t="n">
         <v>2.7</v>
@@ -15269,16 +15260,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C82" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D82" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -15358,16 +15349,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C83" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D83" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E83" t="n">
         <v>0.7</v>
@@ -15447,16 +15438,16 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C84" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D84" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E84" t="n">
         <v>1.85</v>
@@ -15536,16 +15527,16 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C85" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D85" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -15625,16 +15616,16 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C86" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D86" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E86" t="n">
         <v>0.5</v>
@@ -15714,16 +15705,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B87" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C87" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D87" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E87" t="n">
         <v>1.05</v>
@@ -15765,16 +15756,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B88" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C88" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D88" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -15854,16 +15845,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B89" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C89" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D89" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E89" t="n">
         <v>0.5</v>
@@ -15943,16 +15934,16 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B90" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C90" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D90" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -15994,16 +15985,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B91" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C91" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D91" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -16083,16 +16074,16 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B92" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C92" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D92" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E92" t="n">
         <v>1.18</v>
@@ -16172,16 +16163,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B93" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C93" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D93" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E93" t="n">
         <v>2.34</v>
@@ -16261,16 +16252,16 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B94" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C94" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D94" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -16350,16 +16341,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B95" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C95" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D95" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E95" t="n">
         <v>1.08</v>
@@ -16439,16 +16430,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B96" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C96" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D96" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E96" t="n">
         <v>2.15</v>
@@ -16528,16 +16519,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B97" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C97" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D97" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -16617,16 +16608,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B98" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C98" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D98" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E98" t="n">
         <v>1.5</v>
@@ -16706,16 +16697,16 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B99" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C99" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D99" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E99" t="n">
         <v>3</v>
@@ -16795,16 +16786,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C100" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D100" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -16884,16 +16875,16 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C101" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D101" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E101" t="n">
         <v>0.9</v>
@@ -16971,16 +16962,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B102" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C102" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D102" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E102" t="n">
         <v>1.8</v>
@@ -17022,16 +17013,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B103" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C103" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D103" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -17111,16 +17102,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B104" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C104" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D104" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E104" t="n">
         <v>0.9</v>
@@ -17200,16 +17191,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B105" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D105" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E105" t="n">
         <v>1.8</v>
@@ -17289,16 +17280,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B106" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D106" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -17378,16 +17369,16 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B107" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D107" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E107" t="n">
         <v>0.8</v>
@@ -17467,16 +17458,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B108" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D108" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E108" t="n">
         <v>1.65</v>
@@ -17518,16 +17509,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B109" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D109" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -17607,16 +17598,16 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B110" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D110" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E110" t="n">
         <v>0.7</v>
@@ -17696,16 +17687,16 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B111" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C111" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D111" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E111" t="n">
         <v>1.35</v>
@@ -17785,16 +17776,16 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B112" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C112" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D112" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -17874,16 +17865,16 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B113" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C113" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D113" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -17963,16 +17954,16 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B114" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C114" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D114" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E114" t="n">
         <v>4</v>
@@ -18052,16 +18043,16 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B115" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C115" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D115" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -18141,16 +18132,16 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B116" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C116" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D116" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E116" t="n">
         <v>0.9</v>
@@ -18230,16 +18221,16 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C117" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D117" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E117" t="n">
         <v>1.8</v>
@@ -18319,16 +18310,16 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B118" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C118" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D118" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -18408,16 +18399,16 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B119" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C119" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D119" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E119" t="n">
         <v>1.05</v>
@@ -18497,16 +18488,16 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B120" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C120" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D120" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E120" t="n">
         <v>2.15</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -5836,7 +5836,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -5996,7 +5996,7 @@
         <v>91.8181818181818</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -6284,7 +6284,7 @@
         <v>27.6190476190476</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -6316,7 +6316,7 @@
         <v>92</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t xml:space="preserve">sample_id</t>
   </si>
@@ -266,16 +266,13 @@
     <t xml:space="preserve">School</t>
   </si>
   <si>
-    <t xml:space="preserve">Treatment plant</t>
+    <t xml:space="preserve">Aerated Treatment plant</t>
   </si>
   <si>
     <t xml:space="preserve">10-DC-09052023</t>
   </si>
   <si>
     <t xml:space="preserve">5b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wastewater treatment unit</t>
   </si>
   <si>
     <t xml:space="preserve">11-NS-25052023</t>
@@ -2167,7 +2164,7 @@
       </c>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K11" t="s">
         <v>45</v>
@@ -2249,10 +2246,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
         <v>87</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
@@ -2310,10 +2307,10 @@
       </c>
       <c r="U12"/>
       <c r="V12" t="s">
+        <v>88</v>
+      </c>
+      <c r="W12" t="s">
         <v>89</v>
-      </c>
-      <c r="W12" t="s">
-        <v>90</v>
       </c>
       <c r="X12" t="s">
         <v>51</v>
@@ -2364,10 +2361,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
         <v>91</v>
-      </c>
-      <c r="B13" t="s">
-        <v>92</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
@@ -2425,7 +2422,7 @@
       </c>
       <c r="U13"/>
       <c r="V13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W13"/>
       <c r="X13" t="s">
@@ -2475,10 +2472,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s">
         <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>95</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -2538,7 +2535,7 @@
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
@@ -2586,10 +2583,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" t="s">
         <v>97</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -2650,7 +2647,7 @@
       </c>
       <c r="V15"/>
       <c r="W15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X15" t="s">
         <v>51</v>
@@ -2699,10 +2696,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
         <v>100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>101</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -2806,10 +2803,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
         <v>102</v>
-      </c>
-      <c r="B17" t="s">
-        <v>103</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -2839,7 +2836,7 @@
         <v>45</v>
       </c>
       <c r="L17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
@@ -2917,10 +2914,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
         <v>105</v>
-      </c>
-      <c r="B18" t="s">
-        <v>106</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -3028,10 +3025,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
         <v>107</v>
-      </c>
-      <c r="B19" t="s">
-        <v>108</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -3090,7 +3087,7 @@
       <c r="U19"/>
       <c r="V19"/>
       <c r="W19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X19" t="s">
         <v>51</v>
@@ -3139,10 +3136,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
         <v>110</v>
-      </c>
-      <c r="B20" t="s">
-        <v>111</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -3163,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J20" t="s">
         <v>44</v>
@@ -3190,7 +3187,7 @@
         <v>48</v>
       </c>
       <c r="R20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -3252,10 +3249,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
         <v>114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>115</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -3365,10 +3362,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
         <v>116</v>
-      </c>
-      <c r="B22" t="s">
-        <v>117</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -3428,7 +3425,7 @@
       <c r="V22"/>
       <c r="W22"/>
       <c r="X22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
@@ -3476,16 +3473,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" t="s">
         <v>118</v>
-      </c>
-      <c r="B23" t="s">
-        <v>119</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -3541,7 +3538,7 @@
       <c r="V23"/>
       <c r="W23"/>
       <c r="X23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
@@ -3585,16 +3582,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" t="s">
         <v>122</v>
-      </c>
-      <c r="B24" t="s">
-        <v>123</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
         <v>71</v>
@@ -3628,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q24" t="s">
         <v>48</v>
@@ -3647,10 +3644,10 @@
       </c>
       <c r="V24"/>
       <c r="W24" t="s">
+        <v>125</v>
+      </c>
+      <c r="X24" t="s">
         <v>126</v>
-      </c>
-      <c r="X24" t="s">
-        <v>127</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
@@ -3691,21 +3688,21 @@
         <v>1</v>
       </c>
       <c r="AM24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" t="s">
         <v>129</v>
-      </c>
-      <c r="B25" t="s">
-        <v>130</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
         <v>42</v>
@@ -3720,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J25" t="s">
         <v>44</v>
@@ -3741,7 +3738,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q25" t="s">
         <v>48</v>
@@ -3760,7 +3757,7 @@
       </c>
       <c r="V25"/>
       <c r="W25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X25" t="s">
         <v>51</v>
@@ -3806,21 +3803,21 @@
         <v>1</v>
       </c>
       <c r="AM25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
         <v>132</v>
-      </c>
-      <c r="B26" t="s">
-        <v>133</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s">
         <v>42</v>
@@ -3835,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J26" t="s">
         <v>44</v>
@@ -3856,7 +3853,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q26" t="s">
         <v>48</v>
@@ -3875,10 +3872,10 @@
       </c>
       <c r="V26"/>
       <c r="W26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
@@ -3921,21 +3918,21 @@
         <v>1</v>
       </c>
       <c r="AM26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
         <v>134</v>
-      </c>
-      <c r="B27" t="s">
-        <v>135</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
         <v>42</v>
@@ -3950,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J27" t="s">
         <v>44</v>
@@ -3971,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q27" t="s">
         <v>48</v>
@@ -3990,10 +3987,10 @@
       </c>
       <c r="V27"/>
       <c r="W27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y27" t="b">
         <v>1</v>
@@ -4036,21 +4033,21 @@
         <v>1</v>
       </c>
       <c r="AM27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
         <v>136</v>
-      </c>
-      <c r="B28" t="s">
-        <v>137</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
         <v>42</v>
@@ -4065,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J28" t="s">
         <v>44</v>
@@ -4086,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q28" t="s">
         <v>48</v>
@@ -4105,10 +4102,10 @@
       </c>
       <c r="V28"/>
       <c r="W28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
@@ -4151,21 +4148,21 @@
         <v>1</v>
       </c>
       <c r="AM28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" t="s">
         <v>139</v>
-      </c>
-      <c r="B29" t="s">
-        <v>140</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
         <v>42</v>
@@ -4180,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J29" t="s">
         <v>44</v>
@@ -4201,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q29" t="s">
         <v>48</v>
@@ -4220,10 +4217,10 @@
       </c>
       <c r="V29"/>
       <c r="W29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
@@ -4269,16 +4266,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" t="s">
         <v>143</v>
-      </c>
-      <c r="B30" t="s">
-        <v>144</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E30" t="s">
         <v>42</v>
@@ -4293,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J30" t="s">
         <v>44</v>
@@ -4314,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q30" t="s">
         <v>48</v>
@@ -4333,34 +4330,34 @@
       </c>
       <c r="V30"/>
       <c r="W30" t="s">
+        <v>145</v>
+      </c>
+      <c r="X30" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="s">
         <v>146</v>
-      </c>
-      <c r="X30" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>147</v>
       </c>
       <c r="AG30" t="s">
         <v>53</v>
@@ -4375,21 +4372,21 @@
         <v>1</v>
       </c>
       <c r="AM30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" t="s">
         <v>149</v>
-      </c>
-      <c r="B31" t="s">
-        <v>150</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E31" t="s">
         <v>42</v>
@@ -4404,7 +4401,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J31" t="s">
         <v>44</v>
@@ -4425,7 +4422,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q31" t="s">
         <v>48</v>
@@ -4469,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="AF31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG31" t="s">
         <v>74</v>
@@ -4484,21 +4481,21 @@
         <v>1</v>
       </c>
       <c r="AM31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" t="s">
         <v>153</v>
-      </c>
-      <c r="B32" t="s">
-        <v>154</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
         <v>42</v>
@@ -4517,11 +4514,11 @@
         <v>44</v>
       </c>
       <c r="K32" t="s">
+        <v>154</v>
+      </c>
+      <c r="L32" t="s">
         <v>155</v>
       </c>
-      <c r="L32" t="s">
-        <v>156</v>
-      </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
@@ -4532,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q32" t="s">
         <v>48</v>
@@ -4551,7 +4548,7 @@
       </c>
       <c r="V32"/>
       <c r="W32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X32" t="s">
         <v>64</v>
@@ -4595,21 +4592,21 @@
         <v>1</v>
       </c>
       <c r="AM32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" t="s">
         <v>158</v>
-      </c>
-      <c r="B33" t="s">
-        <v>159</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s">
         <v>42</v>
@@ -4624,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J33" t="s">
         <v>44</v>
@@ -4645,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q33" t="s">
         <v>48</v>
@@ -4664,7 +4661,7 @@
       </c>
       <c r="V33"/>
       <c r="W33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X33" t="s">
         <v>51</v>
@@ -4715,16 +4712,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" t="s">
         <v>160</v>
-      </c>
-      <c r="B34" t="s">
-        <v>161</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E34" t="s">
         <v>42</v>
@@ -4739,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J34" t="s">
         <v>44</v>
@@ -4760,7 +4757,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q34" t="s">
         <v>48</v>
@@ -4779,7 +4776,7 @@
       </c>
       <c r="V34"/>
       <c r="W34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X34" t="s">
         <v>73</v>
@@ -4825,21 +4822,21 @@
         <v>1</v>
       </c>
       <c r="AM34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" t="s">
         <v>163</v>
-      </c>
-      <c r="B35" t="s">
-        <v>164</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E35" t="s">
         <v>42</v>
@@ -4890,10 +4887,10 @@
       </c>
       <c r="V35"/>
       <c r="W35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Y35" t="b">
         <v>1</v>
@@ -4936,21 +4933,21 @@
         <v>1</v>
       </c>
       <c r="AM35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" t="s">
         <v>166</v>
-      </c>
-      <c r="B36" t="s">
-        <v>167</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E36" t="s">
         <v>42</v>
@@ -4965,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J36" t="s">
         <v>44</v>
@@ -4986,10 +4983,10 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R36" t="s">
         <v>68</v>
@@ -5005,7 +5002,7 @@
       </c>
       <c r="V36"/>
       <c r="W36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X36" t="s">
         <v>73</v>
@@ -5051,21 +5048,21 @@
         <v>1</v>
       </c>
       <c r="AM36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>169</v>
+      </c>
+      <c r="B37" t="s">
         <v>170</v>
-      </c>
-      <c r="B37" t="s">
-        <v>171</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E37" t="s">
         <v>42</v>
@@ -5080,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J37" t="s">
         <v>44</v>
@@ -5101,7 +5098,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q37" t="s">
         <v>48</v>
@@ -5120,7 +5117,7 @@
       </c>
       <c r="V37"/>
       <c r="W37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X37" t="s">
         <v>51</v>
@@ -5169,16 +5166,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" t="s">
         <v>173</v>
-      </c>
-      <c r="B38" t="s">
-        <v>174</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
         <v>42</v>
@@ -5193,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J38" t="s">
         <v>44</v>
@@ -5214,10 +5211,10 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R38" t="s">
         <v>68</v>
@@ -5233,7 +5230,7 @@
       </c>
       <c r="V38"/>
       <c r="W38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X38" t="s">
         <v>64</v>
@@ -5277,21 +5274,21 @@
         <v>1</v>
       </c>
       <c r="AM38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" t="s">
         <v>176</v>
-      </c>
-      <c r="B39" t="s">
-        <v>177</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E39" t="s">
         <v>71</v>
@@ -5325,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q39" t="s">
         <v>48</v>
@@ -5344,7 +5341,7 @@
       </c>
       <c r="V39"/>
       <c r="W39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X39" t="s">
         <v>64</v>
@@ -5390,21 +5387,21 @@
         <v>1</v>
       </c>
       <c r="AM39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" t="s">
         <v>179</v>
-      </c>
-      <c r="B40" t="s">
-        <v>180</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E40" t="s">
         <v>42</v>
@@ -5419,7 +5416,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J40" t="s">
         <v>44</v>
@@ -5441,7 +5438,7 @@
       </c>
       <c r="P40"/>
       <c r="Q40" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R40" t="s">
         <v>68</v>
@@ -5457,7 +5454,7 @@
       </c>
       <c r="V40"/>
       <c r="W40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X40" t="s">
         <v>73</v>
@@ -5503,21 +5500,21 @@
         <v>1</v>
       </c>
       <c r="AM40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" t="s">
         <v>182</v>
-      </c>
-      <c r="B41" t="s">
-        <v>183</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E41" t="s">
         <v>42</v>
@@ -5551,10 +5548,10 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R41" t="s">
         <v>68</v>
@@ -5570,7 +5567,7 @@
       </c>
       <c r="V41"/>
       <c r="W41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X41" t="s">
         <v>73</v>
@@ -5616,21 +5613,21 @@
         <v>1</v>
       </c>
       <c r="AM41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" t="s">
         <v>185</v>
-      </c>
-      <c r="B42" t="s">
-        <v>186</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E42" t="s">
         <v>42</v>
@@ -5645,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J42" t="s">
         <v>44</v>
@@ -5666,10 +5663,10 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R42" t="s">
         <v>68</v>
@@ -5729,7 +5726,7 @@
         <v>1</v>
       </c>
       <c r="AM42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -5754,25 +5751,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1" t="s">
         <v>188</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>189</v>
-      </c>
-      <c r="F1" t="s">
-        <v>190</v>
       </c>
       <c r="G1" t="s">
         <v>33</v>
       </c>
       <c r="H1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1" t="s">
         <v>191</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>192</v>
-      </c>
-      <c r="J1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="2">
@@ -6092,15 +6089,15 @@
         <v>1.6304347826087</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
         <v>87</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
@@ -6129,10 +6126,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
         <v>91</v>
-      </c>
-      <c r="B13" t="s">
-        <v>92</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
@@ -6161,10 +6158,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s">
         <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>95</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -6193,10 +6190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" t="s">
         <v>97</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -6225,10 +6222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
         <v>100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>101</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -6257,10 +6254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
         <v>102</v>
-      </c>
-      <c r="B17" t="s">
-        <v>103</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -6289,10 +6286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
         <v>105</v>
-      </c>
-      <c r="B18" t="s">
-        <v>106</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -6321,10 +6318,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
         <v>107</v>
-      </c>
-      <c r="B19" t="s">
-        <v>108</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -6353,10 +6350,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
         <v>110</v>
-      </c>
-      <c r="B20" t="s">
-        <v>111</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -6385,10 +6382,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
         <v>114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>115</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -6417,10 +6414,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
         <v>116</v>
-      </c>
-      <c r="B22" t="s">
-        <v>117</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -6449,10 +6446,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" t="s">
         <v>118</v>
-      </c>
-      <c r="B23" t="s">
-        <v>119</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
@@ -6481,10 +6478,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" t="s">
         <v>122</v>
-      </c>
-      <c r="B24" t="s">
-        <v>123</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
@@ -6513,10 +6510,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" t="s">
         <v>129</v>
-      </c>
-      <c r="B25" t="s">
-        <v>130</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
@@ -6545,10 +6542,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
         <v>132</v>
-      </c>
-      <c r="B26" t="s">
-        <v>133</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
@@ -6577,10 +6574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
         <v>134</v>
-      </c>
-      <c r="B27" t="s">
-        <v>135</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
@@ -6609,10 +6606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
         <v>136</v>
-      </c>
-      <c r="B28" t="s">
-        <v>137</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
@@ -6641,10 +6638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" t="s">
         <v>139</v>
-      </c>
-      <c r="B29" t="s">
-        <v>140</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
@@ -6673,10 +6670,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" t="s">
         <v>143</v>
-      </c>
-      <c r="B30" t="s">
-        <v>144</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
@@ -6705,10 +6702,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" t="s">
         <v>149</v>
-      </c>
-      <c r="B31" t="s">
-        <v>150</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
@@ -6737,10 +6734,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" t="s">
         <v>153</v>
-      </c>
-      <c r="B32" t="s">
-        <v>154</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
@@ -6769,10 +6766,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" t="s">
         <v>158</v>
-      </c>
-      <c r="B33" t="s">
-        <v>159</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
@@ -6801,10 +6798,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" t="s">
         <v>160</v>
-      </c>
-      <c r="B34" t="s">
-        <v>161</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
@@ -6833,10 +6830,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" t="s">
         <v>163</v>
-      </c>
-      <c r="B35" t="s">
-        <v>164</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
@@ -6865,10 +6862,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" t="s">
         <v>166</v>
-      </c>
-      <c r="B36" t="s">
-        <v>167</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
@@ -6897,10 +6894,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>169</v>
+      </c>
+      <c r="B37" t="s">
         <v>170</v>
-      </c>
-      <c r="B37" t="s">
-        <v>171</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
@@ -6929,10 +6926,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" t="s">
         <v>173</v>
-      </c>
-      <c r="B38" t="s">
-        <v>174</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
@@ -6961,10 +6958,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" t="s">
         <v>176</v>
-      </c>
-      <c r="B39" t="s">
-        <v>177</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
@@ -6993,10 +6990,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" t="s">
         <v>179</v>
-      </c>
-      <c r="B40" t="s">
-        <v>180</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
@@ -7025,10 +7022,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" t="s">
         <v>182</v>
-      </c>
-      <c r="B41" t="s">
-        <v>183</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
@@ -7057,10 +7054,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" t="s">
         <v>185</v>
-      </c>
-      <c r="B42" t="s">
-        <v>186</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
@@ -7112,13 +7109,13 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" t="s">
         <v>194</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>195</v>
-      </c>
-      <c r="G1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="2">
@@ -7342,7 +7339,7 @@
         <v>368</v>
       </c>
       <c r="E11" t="n">
-        <v>1.12880556599633</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0.398772880015029</v>
@@ -7353,10 +7350,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
         <v>87</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>45071</v>
@@ -7376,10 +7373,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
         <v>91</v>
-      </c>
-      <c r="B13" t="s">
-        <v>92</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>45071</v>
@@ -7399,10 +7396,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s">
         <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>95</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>45077</v>
@@ -7422,10 +7419,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" t="s">
         <v>97</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>45077</v>
@@ -7445,10 +7442,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
         <v>100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>101</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>45077</v>
@@ -7468,10 +7465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
         <v>102</v>
-      </c>
-      <c r="B17" t="s">
-        <v>103</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>45084</v>
@@ -7491,10 +7488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
         <v>105</v>
-      </c>
-      <c r="B18" t="s">
-        <v>106</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>45084</v>
@@ -7514,10 +7511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
         <v>107</v>
-      </c>
-      <c r="B19" t="s">
-        <v>108</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>45085</v>
@@ -7537,10 +7534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
         <v>110</v>
-      </c>
-      <c r="B20" t="s">
-        <v>111</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>45085</v>
@@ -7560,10 +7557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
         <v>114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>115</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>45085</v>
@@ -7583,10 +7580,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
         <v>116</v>
-      </c>
-      <c r="B22" t="s">
-        <v>117</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>45098</v>
@@ -7606,10 +7603,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" t="s">
         <v>118</v>
-      </c>
-      <c r="B23" t="s">
-        <v>119</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>45098</v>
@@ -7629,10 +7626,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" t="s">
         <v>122</v>
-      </c>
-      <c r="B24" t="s">
-        <v>123</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>45306</v>
@@ -7652,10 +7649,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" t="s">
         <v>129</v>
-      </c>
-      <c r="B25" t="s">
-        <v>130</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>45307</v>
@@ -7675,10 +7672,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
         <v>132</v>
-      </c>
-      <c r="B26" t="s">
-        <v>133</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>45307</v>
@@ -7698,10 +7695,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
         <v>134</v>
-      </c>
-      <c r="B27" t="s">
-        <v>135</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>45307</v>
@@ -7721,10 +7718,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
         <v>136</v>
-      </c>
-      <c r="B28" t="s">
-        <v>137</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>45307</v>
@@ -7744,10 +7741,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" t="s">
         <v>139</v>
-      </c>
-      <c r="B29" t="s">
-        <v>140</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>45313</v>
@@ -7767,10 +7764,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" t="s">
         <v>143</v>
-      </c>
-      <c r="B30" t="s">
-        <v>144</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>45314</v>
@@ -7790,10 +7787,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" t="s">
         <v>149</v>
-      </c>
-      <c r="B31" t="s">
-        <v>150</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>45320</v>
@@ -7813,10 +7810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" t="s">
         <v>153</v>
-      </c>
-      <c r="B32" t="s">
-        <v>154</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45320</v>
@@ -7836,10 +7833,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" t="s">
         <v>158</v>
-      </c>
-      <c r="B33" t="s">
-        <v>159</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45321</v>
@@ -7859,10 +7856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" t="s">
         <v>160</v>
-      </c>
-      <c r="B34" t="s">
-        <v>161</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45321</v>
@@ -7882,10 +7879,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" t="s">
         <v>163</v>
-      </c>
-      <c r="B35" t="s">
-        <v>164</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45321</v>
@@ -7905,10 +7902,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" t="s">
         <v>166</v>
-      </c>
-      <c r="B36" t="s">
-        <v>167</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45327</v>
@@ -7928,10 +7925,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>169</v>
+      </c>
+      <c r="B37" t="s">
         <v>170</v>
-      </c>
-      <c r="B37" t="s">
-        <v>171</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45328</v>
@@ -7951,10 +7948,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" t="s">
         <v>173</v>
-      </c>
-      <c r="B38" t="s">
-        <v>174</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45328</v>
@@ -7974,10 +7971,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" t="s">
         <v>176</v>
-      </c>
-      <c r="B39" t="s">
-        <v>177</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45334</v>
@@ -7997,10 +7994,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" t="s">
         <v>179</v>
-      </c>
-      <c r="B40" t="s">
-        <v>180</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45334</v>
@@ -8020,10 +8017,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" t="s">
         <v>182</v>
-      </c>
-      <c r="B41" t="s">
-        <v>183</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45335</v>
@@ -8043,10 +8040,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" t="s">
         <v>185</v>
-      </c>
-      <c r="B42" t="s">
-        <v>186</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45335</v>
@@ -8086,82 +8083,82 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1" t="s">
         <v>197</v>
       </c>
-      <c r="E1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>198</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>199</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>200</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>201</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>202</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>203</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>204</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>205</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>206</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>207</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>208</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>209</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>210</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>211</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>212</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>213</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>214</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>215</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>216</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>217</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>218</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>219</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>220</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2">
@@ -8175,7 +8172,7 @@
         <v>45022</v>
       </c>
       <c r="D2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -8264,7 +8261,7 @@
         <v>45022</v>
       </c>
       <c r="D3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" t="n">
         <v>0.65</v>
@@ -8353,7 +8350,7 @@
         <v>45022</v>
       </c>
       <c r="D4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E4" t="n">
         <v>1.31</v>
@@ -8442,7 +8439,7 @@
         <v>45022</v>
       </c>
       <c r="D5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -8531,7 +8528,7 @@
         <v>45022</v>
       </c>
       <c r="D6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
@@ -8620,7 +8617,7 @@
         <v>45022</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E7" t="n">
         <v>1.82</v>
@@ -8709,7 +8706,7 @@
         <v>45028</v>
       </c>
       <c r="D8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -8798,7 +8795,7 @@
         <v>45028</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
@@ -8887,7 +8884,7 @@
         <v>45028</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E10" t="n">
         <v>1.85</v>
@@ -8976,7 +8973,7 @@
         <v>45028</v>
       </c>
       <c r="D11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -9065,7 +9062,7 @@
         <v>45028</v>
       </c>
       <c r="D12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -9154,7 +9151,7 @@
         <v>45028</v>
       </c>
       <c r="D13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E13" t="n">
         <v>1.05</v>
@@ -9243,7 +9240,7 @@
         <v>45035</v>
       </c>
       <c r="D14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -9332,7 +9329,7 @@
         <v>45035</v>
       </c>
       <c r="D15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E15" t="n">
         <v>0.46</v>
@@ -9421,7 +9418,7 @@
         <v>45035</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E16" t="n">
         <v>0.92</v>
@@ -9510,7 +9507,7 @@
         <v>45035</v>
       </c>
       <c r="D17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -9599,7 +9596,7 @@
         <v>45035</v>
       </c>
       <c r="D18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E18" t="n">
         <v>0.7</v>
@@ -9688,7 +9685,7 @@
         <v>45035</v>
       </c>
       <c r="D19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E19" t="n">
         <v>1.39</v>
@@ -9777,7 +9774,7 @@
         <v>45042</v>
       </c>
       <c r="D20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -9866,7 +9863,7 @@
         <v>45042</v>
       </c>
       <c r="D21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E21" t="n">
         <v>0.7</v>
@@ -9955,7 +9952,7 @@
         <v>45042</v>
       </c>
       <c r="D22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E22" t="n">
         <v>1.41</v>
@@ -10044,7 +10041,7 @@
         <v>45042</v>
       </c>
       <c r="D23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10133,7 +10130,7 @@
         <v>45042</v>
       </c>
       <c r="D24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E24" t="n">
         <v>0.52</v>
@@ -10222,7 +10219,7 @@
         <v>45042</v>
       </c>
       <c r="D25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E25" t="n">
         <v>1.04</v>
@@ -10311,7 +10308,7 @@
         <v>45055</v>
       </c>
       <c r="D26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -10400,7 +10397,7 @@
         <v>45055</v>
       </c>
       <c r="D27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E27" t="n">
         <v>1.055</v>
@@ -10489,7 +10486,7 @@
         <v>45055</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E28" t="n">
         <v>2.11</v>
@@ -10578,7 +10575,7 @@
         <v>45055</v>
       </c>
       <c r="D29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -10667,7 +10664,7 @@
         <v>45055</v>
       </c>
       <c r="D30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E30" t="n">
         <v>0.45</v>
@@ -10756,7 +10753,7 @@
         <v>45055</v>
       </c>
       <c r="D31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E31" t="n">
         <v>1.92</v>
@@ -10836,16 +10833,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" t="s">
         <v>87</v>
-      </c>
-      <c r="B32" t="s">
-        <v>88</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -10925,16 +10922,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s">
         <v>91</v>
-      </c>
-      <c r="B33" t="s">
-        <v>92</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -11014,16 +11011,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" t="s">
         <v>91</v>
-      </c>
-      <c r="B34" t="s">
-        <v>92</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D34" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E34" t="n">
         <v>0.55</v>
@@ -11103,16 +11100,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" t="s">
         <v>91</v>
-      </c>
-      <c r="B35" t="s">
-        <v>92</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>45071</v>
       </c>
       <c r="D35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E35" t="n">
         <v>1.15</v>
@@ -11192,16 +11189,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
         <v>94</v>
-      </c>
-      <c r="B36" t="s">
-        <v>95</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -11281,16 +11278,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" t="s">
         <v>94</v>
-      </c>
-      <c r="B37" t="s">
-        <v>95</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E37" t="n">
         <v>0.94</v>
@@ -11370,16 +11367,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" t="s">
         <v>94</v>
-      </c>
-      <c r="B38" t="s">
-        <v>95</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E38" t="n">
         <v>1.88</v>
@@ -11459,16 +11456,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" t="s">
         <v>97</v>
-      </c>
-      <c r="B39" t="s">
-        <v>98</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -11548,16 +11545,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
         <v>97</v>
-      </c>
-      <c r="B40" t="s">
-        <v>98</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D40" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E40" t="n">
         <v>0.52</v>
@@ -11637,16 +11634,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
         <v>97</v>
-      </c>
-      <c r="B41" t="s">
-        <v>98</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E41" t="n">
         <v>1.04</v>
@@ -11726,16 +11723,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" t="s">
         <v>100</v>
-      </c>
-      <c r="B42" t="s">
-        <v>101</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -11815,16 +11812,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" t="s">
         <v>100</v>
-      </c>
-      <c r="B43" t="s">
-        <v>101</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D43" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E43" t="n">
         <v>0.55</v>
@@ -11904,16 +11901,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" t="s">
         <v>100</v>
-      </c>
-      <c r="B44" t="s">
-        <v>101</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="D44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E44" t="n">
         <v>1.11</v>
@@ -11993,16 +11990,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s">
         <v>102</v>
-      </c>
-      <c r="B45" t="s">
-        <v>103</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -12082,16 +12079,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" t="s">
         <v>102</v>
-      </c>
-      <c r="B46" t="s">
-        <v>103</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E46" t="n">
         <v>0.42</v>
@@ -12171,16 +12168,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" t="s">
         <v>102</v>
-      </c>
-      <c r="B47" t="s">
-        <v>103</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E47" t="n">
         <v>0.95</v>
@@ -12260,16 +12257,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" t="s">
         <v>105</v>
-      </c>
-      <c r="B48" t="s">
-        <v>106</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D48" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -12349,16 +12346,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" t="s">
         <v>105</v>
-      </c>
-      <c r="B49" t="s">
-        <v>106</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E49" t="n">
         <v>0.67</v>
@@ -12438,16 +12435,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" t="s">
         <v>105</v>
-      </c>
-      <c r="B50" t="s">
-        <v>106</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="D50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E50" t="n">
         <v>1.34</v>
@@ -12527,16 +12524,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" t="s">
         <v>107</v>
-      </c>
-      <c r="B51" t="s">
-        <v>108</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D51" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -12616,16 +12613,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B52" t="s">
         <v>107</v>
-      </c>
-      <c r="B52" t="s">
-        <v>108</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D52" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E52" t="n">
         <v>0.505</v>
@@ -12705,16 +12702,16 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" t="s">
         <v>107</v>
-      </c>
-      <c r="B53" t="s">
-        <v>108</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D53" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E53" t="n">
         <v>1.01</v>
@@ -12794,16 +12791,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" t="s">
         <v>110</v>
-      </c>
-      <c r="B54" t="s">
-        <v>111</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D54" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -12883,16 +12880,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" t="s">
         <v>114</v>
-      </c>
-      <c r="B55" t="s">
-        <v>115</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -12972,16 +12969,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" t="s">
         <v>114</v>
-      </c>
-      <c r="B56" t="s">
-        <v>115</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E56" t="n">
         <v>0.61</v>
@@ -13061,16 +13058,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" t="s">
         <v>114</v>
-      </c>
-      <c r="B57" t="s">
-        <v>115</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>45085</v>
       </c>
       <c r="D57" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E57" t="n">
         <v>1.22</v>
@@ -13150,16 +13147,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
         <v>116</v>
-      </c>
-      <c r="B58" t="s">
-        <v>117</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D58" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -13239,16 +13236,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" t="s">
         <v>116</v>
-      </c>
-      <c r="B59" t="s">
-        <v>117</v>
       </c>
       <c r="C59" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E59" t="n">
         <v>0.735</v>
@@ -13328,16 +13325,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" t="s">
         <v>116</v>
-      </c>
-      <c r="B60" t="s">
-        <v>117</v>
       </c>
       <c r="C60" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E60" t="n">
         <v>1.47</v>
@@ -13417,16 +13414,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" t="s">
         <v>118</v>
-      </c>
-      <c r="B61" t="s">
-        <v>119</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D61" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -13506,16 +13503,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" t="s">
         <v>118</v>
-      </c>
-      <c r="B62" t="s">
-        <v>119</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D62" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E62" t="n">
         <v>0.575</v>
@@ -13595,16 +13592,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" t="s">
         <v>118</v>
-      </c>
-      <c r="B63" t="s">
-        <v>119</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>45098</v>
       </c>
       <c r="D63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E63" t="n">
         <v>1.15</v>
@@ -13684,16 +13681,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" t="s">
         <v>122</v>
-      </c>
-      <c r="B64" t="s">
-        <v>123</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D64" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -13769,16 +13766,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" t="s">
         <v>122</v>
-      </c>
-      <c r="B65" t="s">
-        <v>123</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D65" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E65" t="n">
         <v>1.05</v>
@@ -13854,16 +13851,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>121</v>
+      </c>
+      <c r="B66" t="s">
         <v>122</v>
-      </c>
-      <c r="B66" t="s">
-        <v>123</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="D66" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E66" t="n">
         <v>2.1</v>
@@ -13939,16 +13936,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67" t="s">
         <v>129</v>
-      </c>
-      <c r="B67" t="s">
-        <v>130</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D67" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -14026,16 +14023,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68" t="s">
         <v>129</v>
-      </c>
-      <c r="B68" t="s">
-        <v>130</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D68" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E68" t="n">
         <v>1.75</v>
@@ -14115,16 +14112,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" t="s">
         <v>129</v>
-      </c>
-      <c r="B69" t="s">
-        <v>130</v>
       </c>
       <c r="C69" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E69" t="n">
         <v>3.5</v>
@@ -14204,16 +14201,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>131</v>
+      </c>
+      <c r="B70" t="s">
         <v>132</v>
-      </c>
-      <c r="B70" t="s">
-        <v>133</v>
       </c>
       <c r="C70" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D70" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -14291,16 +14288,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" t="s">
         <v>132</v>
-      </c>
-      <c r="B71" t="s">
-        <v>133</v>
       </c>
       <c r="C71" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -14378,16 +14375,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>131</v>
+      </c>
+      <c r="B72" t="s">
         <v>132</v>
-      </c>
-      <c r="B72" t="s">
-        <v>133</v>
       </c>
       <c r="C72" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D72" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E72" t="n">
         <v>2.05</v>
@@ -14465,16 +14462,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" t="s">
         <v>134</v>
-      </c>
-      <c r="B73" t="s">
-        <v>135</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -14552,16 +14549,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>133</v>
+      </c>
+      <c r="B74" t="s">
         <v>134</v>
-      </c>
-      <c r="B74" t="s">
-        <v>135</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -14639,16 +14636,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>133</v>
+      </c>
+      <c r="B75" t="s">
         <v>134</v>
-      </c>
-      <c r="B75" t="s">
-        <v>135</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D75" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E75" t="n">
         <v>2.05</v>
@@ -14728,16 +14725,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>135</v>
+      </c>
+      <c r="B76" t="s">
         <v>136</v>
-      </c>
-      <c r="B76" t="s">
-        <v>137</v>
       </c>
       <c r="C76" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D76" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -14815,16 +14812,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" t="s">
         <v>136</v>
-      </c>
-      <c r="B77" t="s">
-        <v>137</v>
       </c>
       <c r="C77" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D77" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -14904,16 +14901,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>135</v>
+      </c>
+      <c r="B78" t="s">
         <v>136</v>
-      </c>
-      <c r="B78" t="s">
-        <v>137</v>
       </c>
       <c r="C78" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="D78" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E78" t="n">
         <v>2.05</v>
@@ -14993,16 +14990,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>138</v>
+      </c>
+      <c r="B79" t="s">
         <v>139</v>
-      </c>
-      <c r="B79" t="s">
-        <v>140</v>
       </c>
       <c r="C79" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D79" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -15082,16 +15079,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>138</v>
+      </c>
+      <c r="B80" t="s">
         <v>139</v>
-      </c>
-      <c r="B80" t="s">
-        <v>140</v>
       </c>
       <c r="C80" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D80" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E80" t="n">
         <v>1.35</v>
@@ -15171,16 +15168,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>138</v>
+      </c>
+      <c r="B81" t="s">
         <v>139</v>
-      </c>
-      <c r="B81" t="s">
-        <v>140</v>
       </c>
       <c r="C81" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="D81" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E81" t="n">
         <v>2.7</v>
@@ -15260,16 +15257,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>142</v>
+      </c>
+      <c r="B82" t="s">
         <v>143</v>
-      </c>
-      <c r="B82" t="s">
-        <v>144</v>
       </c>
       <c r="C82" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D82" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -15349,16 +15346,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>142</v>
+      </c>
+      <c r="B83" t="s">
         <v>143</v>
-      </c>
-      <c r="B83" t="s">
-        <v>144</v>
       </c>
       <c r="C83" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D83" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E83" t="n">
         <v>0.7</v>
@@ -15438,16 +15435,16 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>142</v>
+      </c>
+      <c r="B84" t="s">
         <v>143</v>
-      </c>
-      <c r="B84" t="s">
-        <v>144</v>
       </c>
       <c r="C84" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="D84" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E84" t="n">
         <v>1.85</v>
@@ -15527,16 +15524,16 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>148</v>
+      </c>
+      <c r="B85" t="s">
         <v>149</v>
-      </c>
-      <c r="B85" t="s">
-        <v>150</v>
       </c>
       <c r="C85" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D85" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -15616,16 +15613,16 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>148</v>
+      </c>
+      <c r="B86" t="s">
         <v>149</v>
-      </c>
-      <c r="B86" t="s">
-        <v>150</v>
       </c>
       <c r="C86" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D86" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E86" t="n">
         <v>0.5</v>
@@ -15705,16 +15702,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>148</v>
+      </c>
+      <c r="B87" t="s">
         <v>149</v>
-      </c>
-      <c r="B87" t="s">
-        <v>150</v>
       </c>
       <c r="C87" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D87" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E87" t="n">
         <v>1.05</v>
@@ -15756,16 +15753,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>152</v>
+      </c>
+      <c r="B88" t="s">
         <v>153</v>
-      </c>
-      <c r="B88" t="s">
-        <v>154</v>
       </c>
       <c r="C88" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D88" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -15845,16 +15842,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" t="s">
         <v>153</v>
-      </c>
-      <c r="B89" t="s">
-        <v>154</v>
       </c>
       <c r="C89" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D89" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E89" t="n">
         <v>0.5</v>
@@ -15934,16 +15931,16 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" t="s">
         <v>153</v>
-      </c>
-      <c r="B90" t="s">
-        <v>154</v>
       </c>
       <c r="C90" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="D90" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -15985,16 +15982,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>157</v>
+      </c>
+      <c r="B91" t="s">
         <v>158</v>
-      </c>
-      <c r="B91" t="s">
-        <v>159</v>
       </c>
       <c r="C91" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D91" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -16074,16 +16071,16 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>157</v>
+      </c>
+      <c r="B92" t="s">
         <v>158</v>
-      </c>
-      <c r="B92" t="s">
-        <v>159</v>
       </c>
       <c r="C92" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D92" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E92" t="n">
         <v>1.18</v>
@@ -16163,16 +16160,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>157</v>
+      </c>
+      <c r="B93" t="s">
         <v>158</v>
-      </c>
-      <c r="B93" t="s">
-        <v>159</v>
       </c>
       <c r="C93" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D93" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E93" t="n">
         <v>2.34</v>
@@ -16252,16 +16249,16 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>159</v>
+      </c>
+      <c r="B94" t="s">
         <v>160</v>
-      </c>
-      <c r="B94" t="s">
-        <v>161</v>
       </c>
       <c r="C94" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D94" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -16341,16 +16338,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>159</v>
+      </c>
+      <c r="B95" t="s">
         <v>160</v>
-      </c>
-      <c r="B95" t="s">
-        <v>161</v>
       </c>
       <c r="C95" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D95" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E95" t="n">
         <v>1.08</v>
@@ -16430,16 +16427,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>159</v>
+      </c>
+      <c r="B96" t="s">
         <v>160</v>
-      </c>
-      <c r="B96" t="s">
-        <v>161</v>
       </c>
       <c r="C96" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D96" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E96" t="n">
         <v>2.15</v>
@@ -16519,16 +16516,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
+        <v>162</v>
+      </c>
+      <c r="B97" t="s">
         <v>163</v>
-      </c>
-      <c r="B97" t="s">
-        <v>164</v>
       </c>
       <c r="C97" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D97" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -16608,16 +16605,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>162</v>
+      </c>
+      <c r="B98" t="s">
         <v>163</v>
-      </c>
-      <c r="B98" t="s">
-        <v>164</v>
       </c>
       <c r="C98" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D98" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E98" t="n">
         <v>1.5</v>
@@ -16697,16 +16694,16 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>162</v>
+      </c>
+      <c r="B99" t="s">
         <v>163</v>
-      </c>
-      <c r="B99" t="s">
-        <v>164</v>
       </c>
       <c r="C99" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="D99" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E99" t="n">
         <v>3</v>
@@ -16786,16 +16783,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
+        <v>165</v>
+      </c>
+      <c r="B100" t="s">
         <v>166</v>
-      </c>
-      <c r="B100" t="s">
-        <v>167</v>
       </c>
       <c r="C100" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D100" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -16875,16 +16872,16 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>165</v>
+      </c>
+      <c r="B101" t="s">
         <v>166</v>
-      </c>
-      <c r="B101" t="s">
-        <v>167</v>
       </c>
       <c r="C101" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D101" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E101" t="n">
         <v>0.9</v>
@@ -16962,16 +16959,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>165</v>
+      </c>
+      <c r="B102" t="s">
         <v>166</v>
-      </c>
-      <c r="B102" t="s">
-        <v>167</v>
       </c>
       <c r="C102" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="D102" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E102" t="n">
         <v>1.8</v>
@@ -17013,16 +17010,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
+        <v>169</v>
+      </c>
+      <c r="B103" t="s">
         <v>170</v>
-      </c>
-      <c r="B103" t="s">
-        <v>171</v>
       </c>
       <c r="C103" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D103" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -17102,16 +17099,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
+        <v>169</v>
+      </c>
+      <c r="B104" t="s">
         <v>170</v>
-      </c>
-      <c r="B104" t="s">
-        <v>171</v>
       </c>
       <c r="C104" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D104" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E104" t="n">
         <v>0.9</v>
@@ -17191,16 +17188,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>169</v>
+      </c>
+      <c r="B105" t="s">
         <v>170</v>
-      </c>
-      <c r="B105" t="s">
-        <v>171</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D105" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E105" t="n">
         <v>1.8</v>
@@ -17280,16 +17277,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
+        <v>172</v>
+      </c>
+      <c r="B106" t="s">
         <v>173</v>
-      </c>
-      <c r="B106" t="s">
-        <v>174</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D106" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -17369,16 +17366,16 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
+        <v>172</v>
+      </c>
+      <c r="B107" t="s">
         <v>173</v>
-      </c>
-      <c r="B107" t="s">
-        <v>174</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E107" t="n">
         <v>0.8</v>
@@ -17458,16 +17455,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
+        <v>172</v>
+      </c>
+      <c r="B108" t="s">
         <v>173</v>
-      </c>
-      <c r="B108" t="s">
-        <v>174</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E108" t="n">
         <v>1.65</v>
@@ -17509,16 +17506,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>175</v>
+      </c>
+      <c r="B109" t="s">
         <v>176</v>
-      </c>
-      <c r="B109" t="s">
-        <v>177</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D109" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -17598,16 +17595,16 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>175</v>
+      </c>
+      <c r="B110" t="s">
         <v>176</v>
-      </c>
-      <c r="B110" t="s">
-        <v>177</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D110" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E110" t="n">
         <v>0.7</v>
@@ -17687,16 +17684,16 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
+        <v>175</v>
+      </c>
+      <c r="B111" t="s">
         <v>176</v>
-      </c>
-      <c r="B111" t="s">
-        <v>177</v>
       </c>
       <c r="C111" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E111" t="n">
         <v>1.35</v>
@@ -17776,16 +17773,16 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
+        <v>178</v>
+      </c>
+      <c r="B112" t="s">
         <v>179</v>
-      </c>
-      <c r="B112" t="s">
-        <v>180</v>
       </c>
       <c r="C112" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D112" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -17865,16 +17862,16 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>178</v>
+      </c>
+      <c r="B113" t="s">
         <v>179</v>
-      </c>
-      <c r="B113" t="s">
-        <v>180</v>
       </c>
       <c r="C113" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D113" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -17954,16 +17951,16 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>178</v>
+      </c>
+      <c r="B114" t="s">
         <v>179</v>
-      </c>
-      <c r="B114" t="s">
-        <v>180</v>
       </c>
       <c r="C114" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="D114" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E114" t="n">
         <v>4</v>
@@ -18043,16 +18040,16 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>181</v>
+      </c>
+      <c r="B115" t="s">
         <v>182</v>
-      </c>
-      <c r="B115" t="s">
-        <v>183</v>
       </c>
       <c r="C115" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D115" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -18132,16 +18129,16 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>181</v>
+      </c>
+      <c r="B116" t="s">
         <v>182</v>
-      </c>
-      <c r="B116" t="s">
-        <v>183</v>
       </c>
       <c r="C116" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D116" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E116" t="n">
         <v>0.9</v>
@@ -18221,16 +18218,16 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
+        <v>181</v>
+      </c>
+      <c r="B117" t="s">
         <v>182</v>
-      </c>
-      <c r="B117" t="s">
-        <v>183</v>
       </c>
       <c r="C117" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D117" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E117" t="n">
         <v>1.8</v>
@@ -18310,16 +18307,16 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
+        <v>184</v>
+      </c>
+      <c r="B118" t="s">
         <v>185</v>
-      </c>
-      <c r="B118" t="s">
-        <v>186</v>
       </c>
       <c r="C118" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D118" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -18399,16 +18396,16 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>184</v>
+      </c>
+      <c r="B119" t="s">
         <v>185</v>
-      </c>
-      <c r="B119" t="s">
-        <v>186</v>
       </c>
       <c r="C119" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D119" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E119" t="n">
         <v>1.05</v>
@@ -18488,16 +18485,16 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>184</v>
+      </c>
+      <c r="B120" t="s">
         <v>185</v>
-      </c>
-      <c r="B120" t="s">
-        <v>186</v>
       </c>
       <c r="C120" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="D120" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E120" t="n">
         <v>2.15</v>

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -10380,10 +10380,10 @@
         <v>0.0333333333333334</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.0433333333333341</v>
+        <v>0.0333333333333334</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.30000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -10469,10 +10469,10 @@
         <v>0.0633333333333338</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.0833333333333334</v>
+        <v>0.0633333333333338</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.3157894736842</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -10825,10 +10825,10 @@
         <v>25.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.02380952380952</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -15338,10 +15338,10 @@
         <v>0.0842105263157904</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.163157894736842</v>
+        <v>0.0842105263157904</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.93749999999997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -15427,10 +15427,10 @@
         <v>0.0900000000000012</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.145000000000001</v>
+        <v>0.0900000000000012</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.6111111111111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -14104,10 +14104,10 @@
         <v>0.01456</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.03456</v>
+        <v>0.01456</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.37362637362637</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">

--- a/inst/extdata/fecalcanuga.xlsx
+++ b/inst/extdata/fecalcanuga.xlsx
@@ -8,14 +8,13 @@
   <sheets>
     <sheet name="Household Survey Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Containment Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GHG Data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Phys Chem Parameter Data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Phys Chem Parameter Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
   <si>
     <t xml:space="preserve">sample_id</t>
   </si>
@@ -594,15 +593,6 @@
   </si>
   <si>
     <t xml:space="preserve">scum_depth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flux_ch4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flux_co2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flux_n20</t>
   </si>
   <si>
     <t xml:space="preserve">depth_id</t>
@@ -7106,16 +7096,82 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
       <c r="E1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F1" t="s">
         <v>194</v>
       </c>
       <c r="G1" t="s">
         <v>195</v>
+      </c>
+      <c r="H1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1" t="s">
+        <v>201</v>
+      </c>
+      <c r="N1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O1" t="s">
+        <v>203</v>
+      </c>
+      <c r="P1" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>205</v>
+      </c>
+      <c r="R1" t="s">
+        <v>206</v>
+      </c>
+      <c r="S1" t="s">
+        <v>207</v>
+      </c>
+      <c r="T1" t="s">
+        <v>208</v>
+      </c>
+      <c r="U1" t="s">
+        <v>209</v>
+      </c>
+      <c r="V1" t="s">
+        <v>210</v>
+      </c>
+      <c r="W1" t="s">
+        <v>211</v>
+      </c>
+      <c r="X1" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>216</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="2">
@@ -7128,1051 +7184,8 @@
       <c r="C2" s="1" t="n">
         <v>45022</v>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.2560329603118</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>45022</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>31.6839087476299</v>
-      </c>
-      <c r="F3" t="n">
-        <v>87.4345981301277</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>45028</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>7.05696469602596</v>
-      </c>
-      <c r="F4" t="n">
-        <v>63.1432744737226</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>45028</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>40.083047620108</v>
-      </c>
-      <c r="F5" t="n">
-        <v>19.3254504152049</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>45035</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>85.6196766726526</v>
-      </c>
-      <c r="F6" t="n">
-        <v>161.516002704894</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>45035</v>
-      </c>
-      <c r="D7" t="n">
-        <v>410</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.418042154143449</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>45042</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>41.5812684610042</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>45042</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>116.931953337674</v>
-      </c>
-      <c r="F9" t="n">
-        <v>179.60486212834</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>45055</v>
-      </c>
-      <c r="D10" t="n">
-        <v>304</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>45055</v>
-      </c>
-      <c r="D11" t="n">
-        <v>368</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.398772880015029</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>45071</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.167779417271585</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3.49669944063345</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>45071</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>14.5719489770412</v>
-      </c>
-      <c r="F13" t="n">
-        <v>19.8036293337893</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3.47199432365575</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>153.242356075774</v>
-      </c>
-      <c r="F15" t="n">
-        <v>176.11862559466</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>45084</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>28.4853414538738</v>
-      </c>
-      <c r="F17" t="n">
-        <v>81.1197413616831</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>45084</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>30.7601642715924</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>45085</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>15.2095004951554</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>45085</v>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>36.1174196010493</v>
-      </c>
-      <c r="F20" t="n">
-        <v>59.7184067673525</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>45085</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>13.6916997203912</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>45098</v>
-      </c>
-      <c r="D22" t="n">
-        <v>200</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.784252236544445</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.32788011504695</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" t="s">
-        <v>118</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>45098</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>121</v>
-      </c>
-      <c r="B24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="D24" t="n">
-        <v>23</v>
-      </c>
-      <c r="E24" t="n">
-        <v>40.7605297469947</v>
-      </c>
-      <c r="F24" t="n">
-        <v>77.8379282927321</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>45307</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" t="n">
-        <v>13.7818968442006</v>
-      </c>
-      <c r="F25" t="n">
-        <v>489.551167461809</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>131</v>
-      </c>
-      <c r="B26" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>45307</v>
-      </c>
-      <c r="D26" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13.92256539862</v>
-      </c>
-      <c r="F26" t="n">
-        <v>142.941859135691</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>133</v>
-      </c>
-      <c r="B27" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>45307</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>37.8630425374192</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>45307</v>
-      </c>
-      <c r="D28" t="n">
-        <v>15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>21.6094847868012</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>45313</v>
-      </c>
-      <c r="D29" t="n">
-        <v>9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>16.9404675162311</v>
-      </c>
-      <c r="F29" t="n">
-        <v>16.2509044834474</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>142</v>
-      </c>
-      <c r="B30" t="s">
-        <v>143</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>45314</v>
-      </c>
-      <c r="D30" t="n">
-        <v>15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>6.90140153131008</v>
-      </c>
-      <c r="F30" t="n">
-        <v>23.3603081609197</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>148</v>
-      </c>
-      <c r="B31" t="s">
-        <v>149</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="D31" t="n">
-        <v>14</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.682280530392119</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>152</v>
-      </c>
-      <c r="B32" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>45320</v>
-      </c>
-      <c r="D32" t="n">
-        <v>35</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.76502851822708</v>
-      </c>
-      <c r="F32" t="n">
-        <v>7.73917745909456</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>157</v>
-      </c>
-      <c r="B33" t="s">
-        <v>158</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>45321</v>
-      </c>
-      <c r="D33" t="n">
-        <v>30</v>
-      </c>
-      <c r="E33" t="n">
-        <v>18.9946622972448</v>
-      </c>
-      <c r="F33" t="n">
-        <v>160.385524565915</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>159</v>
-      </c>
-      <c r="B34" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>45321</v>
-      </c>
-      <c r="D34" t="n">
-        <v>30</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10.9054868168041</v>
-      </c>
-      <c r="F34" t="n">
-        <v>31.7640581080592</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" t="s">
-        <v>163</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>45321</v>
-      </c>
-      <c r="D35" t="n">
-        <v>88</v>
-      </c>
-      <c r="E35" t="n">
-        <v>25.1839141857233</v>
-      </c>
-      <c r="F35" t="n">
-        <v>39.861061346201</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>165</v>
-      </c>
-      <c r="B36" t="s">
-        <v>166</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>45327</v>
-      </c>
-      <c r="D36" t="n">
-        <v>35</v>
-      </c>
-      <c r="E36" t="n">
-        <v>12.5601837915343</v>
-      </c>
-      <c r="F36" t="n">
-        <v>33.0356504245321</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>169</v>
-      </c>
-      <c r="B37" t="s">
-        <v>170</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>45328</v>
-      </c>
-      <c r="D37" t="n">
-        <v>43</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3.25216968243562</v>
-      </c>
-      <c r="F37" t="n">
-        <v>15.0464351300317</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>172</v>
-      </c>
-      <c r="B38" t="s">
-        <v>173</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>45328</v>
-      </c>
-      <c r="D38" t="n">
-        <v>29</v>
-      </c>
-      <c r="E38" t="n">
-        <v>5.29238719834521</v>
-      </c>
-      <c r="F38" t="n">
-        <v>9.68965819806905</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>175</v>
-      </c>
-      <c r="B39" t="s">
-        <v>176</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>19.447947290656</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>178</v>
-      </c>
-      <c r="B40" t="s">
-        <v>179</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="D40" t="n">
-        <v>16</v>
-      </c>
-      <c r="E40" t="n">
-        <v>41.4873367008572</v>
-      </c>
-      <c r="F40" t="n">
-        <v>71.6871984130468</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>181</v>
-      </c>
-      <c r="B41" t="s">
-        <v>182</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>45335</v>
-      </c>
-      <c r="D41" t="n">
-        <v>52</v>
-      </c>
-      <c r="E41" t="n">
-        <v>4.60436461329772</v>
-      </c>
-      <c r="F41" t="n">
-        <v>8.85828755155557</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>184</v>
-      </c>
-      <c r="B42" t="s">
-        <v>185</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>45335</v>
-      </c>
-      <c r="D42" t="n">
-        <v>14</v>
-      </c>
-      <c r="E42" t="n">
-        <v>3.56663954822773</v>
-      </c>
-      <c r="F42" t="n">
-        <v>25.9659080323872</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J1" t="s">
-        <v>201</v>
-      </c>
-      <c r="K1" t="s">
-        <v>202</v>
-      </c>
-      <c r="L1" t="s">
-        <v>203</v>
-      </c>
-      <c r="M1" t="s">
-        <v>204</v>
-      </c>
-      <c r="N1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O1" t="s">
-        <v>206</v>
-      </c>
-      <c r="P1" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>208</v>
-      </c>
-      <c r="R1" t="s">
-        <v>209</v>
-      </c>
-      <c r="S1" t="s">
-        <v>210</v>
-      </c>
-      <c r="T1" t="s">
-        <v>211</v>
-      </c>
-      <c r="U1" t="s">
-        <v>212</v>
-      </c>
-      <c r="V1" t="s">
-        <v>213</v>
-      </c>
-      <c r="W1" t="s">
-        <v>214</v>
-      </c>
-      <c r="X1" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA1" t="s">
+      <c r="D2" t="s">
         <v>218</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>45022</v>
-      </c>
-      <c r="D2" t="s">
-        <v>221</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -8261,7 +7274,7 @@
         <v>45022</v>
       </c>
       <c r="D3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E3" t="n">
         <v>0.65</v>
@@ -8350,7 +7363,7 @@
         <v>45022</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E4" t="n">
         <v>1.31</v>
@@ -8439,7 +7452,7 @@
         <v>45022</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -8528,7 +7541,7 @@
         <v>45022</v>
       </c>
       <c r="D6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E6" t="n">
         <v>0.9</v>
@@ -8617,7 +7630,7 @@
         <v>45022</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E7" t="n">
         <v>1.82</v>
@@ -8706,7 +7719,7 @@
         <v>45028</v>
       </c>
       <c r="D8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -8795,7 +7808,7 @@
         <v>45028</v>
       </c>
       <c r="D9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
@@ -8884,7 +7897,7 @@
         <v>45028</v>
       </c>
       <c r="D10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E10" t="n">
         <v>1.85</v>
@@ -8973,7 +7986,7 @@
         <v>45028</v>
       </c>
       <c r="D11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -9062,7 +8075,7 @@
         <v>45028</v>
       </c>
       <c r="D12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -9151,7 +8164,7 @@
         <v>45028</v>
       </c>
       <c r="D13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E13" t="n">
         <v>1.05</v>
@@ -9240,7 +8253,7 @@
         <v>45035</v>
       </c>
       <c r="D14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -9329,7 +8342,7 @@
         <v>45035</v>
       </c>
       <c r="D15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E15" t="n">
         <v>0.46</v>
@@ -9418,7 +8431,7 @@
         <v>45035</v>
       </c>
       <c r="D16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E16" t="n">
         <v>0.92</v>
@@ -9507,7 +8520,7 @@
         <v>45035</v>
       </c>
       <c r="D17" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -9596,7 +8609,7 @@
         <v>45035</v>
       </c>
       <c r="D18" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E18" t="n">
         <v>0.7</v>
@@ -9685,7 +8698,7 @@
         <v>45035</v>
       </c>
       <c r="D19" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E19" t="n">
         <v>1.39</v>
@@ -9774,7 +8787,7 @@
         <v>45042</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -9863,7 +8876,7 @@
         <v>45042</v>
       </c>
       <c r="D21" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E21" t="n">
         <v>0.7</v>
@@ -9952,7 +8965,7 @@
         <v>45042</v>
       </c>
       <c r="D22" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E22" t="n">
         <v>1.41</v>
@@ -10041,7 +9054,7 @@
         <v>45042</v>
       </c>
       <c r="D23" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10130,7 +9143,7 @@
         <v>45042</v>
       </c>
       <c r="D24" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E24" t="n">
         <v>0.52</v>
@@ -10219,7 +9232,7 @@
         <v>45042</v>
       </c>
       <c r="D25" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E25" t="n">
         <v>1.04</v>
@@ -10308,7 +9321,7 @@
         <v>45055</v>
       </c>
       <c r="D26" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -10397,7 +9410,7 @@
         <v>45055</v>
       </c>
       <c r="D27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E27" t="n">
         <v>1.055</v>
@@ -10486,7 +9499,7 @@
         <v>45055</v>
       </c>
       <c r="D28" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E28" t="n">
         <v>2.11</v>
@@ -10575,7 +9588,7 @@
         <v>45055</v>
       </c>
       <c r="D29" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -10664,7 +9677,7 @@
         <v>45055</v>
       </c>
       <c r="D30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E30" t="n">
         <v>0.45</v>
@@ -10753,7 +9766,7 @@
         <v>45055</v>
       </c>
       <c r="D31" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E31" t="n">
         <v>1.92</v>
@@ -10842,7 +9855,7 @@
         <v>45071</v>
       </c>
       <c r="D32" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -10931,7 +9944,7 @@
         <v>45071</v>
       </c>
       <c r="D33" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -11020,7 +10033,7 @@
         <v>45071</v>
       </c>
       <c r="D34" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E34" t="n">
         <v>0.55</v>
@@ -11109,7 +10122,7 @@
         <v>45071</v>
       </c>
       <c r="D35" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E35" t="n">
         <v>1.15</v>
@@ -11198,7 +10211,7 @@
         <v>45077</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -11287,7 +10300,7 @@
         <v>45077</v>
       </c>
       <c r="D37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E37" t="n">
         <v>0.94</v>
@@ -11376,7 +10389,7 @@
         <v>45077</v>
       </c>
       <c r="D38" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E38" t="n">
         <v>1.88</v>
@@ -11465,7 +10478,7 @@
         <v>45077</v>
       </c>
       <c r="D39" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -11554,7 +10567,7 @@
         <v>45077</v>
       </c>
       <c r="D40" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E40" t="n">
         <v>0.52</v>
@@ -11643,7 +10656,7 @@
         <v>45077</v>
       </c>
       <c r="D41" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E41" t="n">
         <v>1.04</v>
@@ -11732,7 +10745,7 @@
         <v>45077</v>
       </c>
       <c r="D42" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -11821,7 +10834,7 @@
         <v>45077</v>
       </c>
       <c r="D43" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E43" t="n">
         <v>0.55</v>
@@ -11910,7 +10923,7 @@
         <v>45077</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E44" t="n">
         <v>1.11</v>
@@ -11999,7 +11012,7 @@
         <v>45084</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -12088,7 +11101,7 @@
         <v>45084</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E46" t="n">
         <v>0.42</v>
@@ -12177,7 +11190,7 @@
         <v>45084</v>
       </c>
       <c r="D47" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E47" t="n">
         <v>0.95</v>
@@ -12266,7 +11279,7 @@
         <v>45084</v>
       </c>
       <c r="D48" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -12355,7 +11368,7 @@
         <v>45084</v>
       </c>
       <c r="D49" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E49" t="n">
         <v>0.67</v>
@@ -12444,7 +11457,7 @@
         <v>45084</v>
       </c>
       <c r="D50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E50" t="n">
         <v>1.34</v>
@@ -12533,7 +11546,7 @@
         <v>45085</v>
       </c>
       <c r="D51" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -12622,7 +11635,7 @@
         <v>45085</v>
       </c>
       <c r="D52" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E52" t="n">
         <v>0.505</v>
@@ -12711,7 +11724,7 @@
         <v>45085</v>
       </c>
       <c r="D53" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E53" t="n">
         <v>1.01</v>
@@ -12800,7 +11813,7 @@
         <v>45085</v>
       </c>
       <c r="D54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -12889,7 +11902,7 @@
         <v>45085</v>
       </c>
       <c r="D55" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -12978,7 +11991,7 @@
         <v>45085</v>
       </c>
       <c r="D56" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E56" t="n">
         <v>0.61</v>
@@ -13067,7 +12080,7 @@
         <v>45085</v>
       </c>
       <c r="D57" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E57" t="n">
         <v>1.22</v>
@@ -13156,7 +12169,7 @@
         <v>45098</v>
       </c>
       <c r="D58" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -13245,7 +12258,7 @@
         <v>45098</v>
       </c>
       <c r="D59" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E59" t="n">
         <v>0.735</v>
@@ -13334,7 +12347,7 @@
         <v>45098</v>
       </c>
       <c r="D60" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E60" t="n">
         <v>1.47</v>
@@ -13423,7 +12436,7 @@
         <v>45098</v>
       </c>
       <c r="D61" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -13512,7 +12525,7 @@
         <v>45098</v>
       </c>
       <c r="D62" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E62" t="n">
         <v>0.575</v>
@@ -13601,7 +12614,7 @@
         <v>45098</v>
       </c>
       <c r="D63" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E63" t="n">
         <v>1.15</v>
@@ -13690,7 +12703,7 @@
         <v>45306</v>
       </c>
       <c r="D64" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -13775,7 +12788,7 @@
         <v>45306</v>
       </c>
       <c r="D65" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E65" t="n">
         <v>1.05</v>
@@ -13860,7 +12873,7 @@
         <v>45306</v>
       </c>
       <c r="D66" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E66" t="n">
         <v>2.1</v>
@@ -13945,7 +12958,7 @@
         <v>45307</v>
       </c>
       <c r="D67" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -14032,7 +13045,7 @@
         <v>45307</v>
       </c>
       <c r="D68" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E68" t="n">
         <v>1.75</v>
@@ -14121,7 +13134,7 @@
         <v>45307</v>
       </c>
       <c r="D69" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E69" t="n">
         <v>3.5</v>
@@ -14210,7 +13223,7 @@
         <v>45307</v>
       </c>
       <c r="D70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -14297,7 +13310,7 @@
         <v>45307</v>
       </c>
       <c r="D71" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -14384,7 +13397,7 @@
         <v>45307</v>
       </c>
       <c r="D72" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E72" t="n">
         <v>2.05</v>
@@ -14471,7 +13484,7 @@
         <v>45307</v>
       </c>
       <c r="D73" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -14558,7 +13571,7 @@
         <v>45307</v>
       </c>
       <c r="D74" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -14645,7 +13658,7 @@
         <v>45307</v>
       </c>
       <c r="D75" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E75" t="n">
         <v>2.05</v>
@@ -14734,7 +13747,7 @@
         <v>45307</v>
       </c>
       <c r="D76" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -14821,7 +13834,7 @@
         <v>45307</v>
       </c>
       <c r="D77" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -14910,7 +13923,7 @@
         <v>45307</v>
       </c>
       <c r="D78" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E78" t="n">
         <v>2.05</v>
@@ -14999,7 +14012,7 @@
         <v>45313</v>
       </c>
       <c r="D79" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -15088,7 +14101,7 @@
         <v>45313</v>
       </c>
       <c r="D80" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E80" t="n">
         <v>1.35</v>
@@ -15177,7 +14190,7 @@
         <v>45313</v>
       </c>
       <c r="D81" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E81" t="n">
         <v>2.7</v>
@@ -15266,7 +14279,7 @@
         <v>45314</v>
       </c>
       <c r="D82" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -15355,7 +14368,7 @@
         <v>45314</v>
       </c>
       <c r="D83" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E83" t="n">
         <v>0.7</v>
@@ -15444,7 +14457,7 @@
         <v>45314</v>
       </c>
       <c r="D84" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E84" t="n">
         <v>1.85</v>
@@ -15533,7 +14546,7 @@
         <v>45320</v>
       </c>
       <c r="D85" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -15622,7 +14635,7 @@
         <v>45320</v>
       </c>
       <c r="D86" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E86" t="n">
         <v>0.5</v>
@@ -15711,7 +14724,7 @@
         <v>45320</v>
       </c>
       <c r="D87" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E87" t="n">
         <v>1.05</v>
@@ -15762,7 +14775,7 @@
         <v>45320</v>
       </c>
       <c r="D88" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -15851,7 +14864,7 @@
         <v>45320</v>
       </c>
       <c r="D89" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E89" t="n">
         <v>0.5</v>
@@ -15940,7 +14953,7 @@
         <v>45320</v>
       </c>
       <c r="D90" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -15991,7 +15004,7 @@
         <v>45321</v>
       </c>
       <c r="D91" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -16080,7 +15093,7 @@
         <v>45321</v>
       </c>
       <c r="D92" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E92" t="n">
         <v>1.18</v>
@@ -16169,7 +15182,7 @@
         <v>45321</v>
       </c>
       <c r="D93" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E93" t="n">
         <v>2.34</v>
@@ -16258,7 +15271,7 @@
         <v>45321</v>
       </c>
       <c r="D94" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -16347,7 +15360,7 @@
         <v>45321</v>
       </c>
       <c r="D95" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E95" t="n">
         <v>1.08</v>
@@ -16436,7 +15449,7 @@
         <v>45321</v>
       </c>
       <c r="D96" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E96" t="n">
         <v>2.15</v>
@@ -16525,7 +15538,7 @@
         <v>45321</v>
       </c>
       <c r="D97" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -16614,7 +15627,7 @@
         <v>45321</v>
       </c>
       <c r="D98" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E98" t="n">
         <v>1.5</v>
@@ -16703,7 +15716,7 @@
         <v>45321</v>
       </c>
       <c r="D99" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E99" t="n">
         <v>3</v>
@@ -16792,7 +15805,7 @@
         <v>45327</v>
       </c>
       <c r="D100" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -16881,7 +15894,7 @@
         <v>45327</v>
       </c>
       <c r="D101" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E101" t="n">
         <v>0.9</v>
@@ -16968,7 +15981,7 @@
         <v>45327</v>
       </c>
       <c r="D102" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E102" t="n">
         <v>1.8</v>
@@ -17019,7 +16032,7 @@
         <v>45328</v>
       </c>
       <c r="D103" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -17108,7 +16121,7 @@
         <v>45328</v>
       </c>
       <c r="D104" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E104" t="n">
         <v>0.9</v>
@@ -17197,7 +16210,7 @@
         <v>45328</v>
       </c>
       <c r="D105" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E105" t="n">
         <v>1.8</v>
@@ -17286,7 +16299,7 @@
         <v>45328</v>
       </c>
       <c r="D106" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -17375,7 +16388,7 @@
         <v>45328</v>
       </c>
       <c r="D107" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E107" t="n">
         <v>0.8</v>
@@ -17464,7 +16477,7 @@
         <v>45328</v>
       </c>
       <c r="D108" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E108" t="n">
         <v>1.65</v>
@@ -17515,7 +16528,7 @@
         <v>45334</v>
       </c>
       <c r="D109" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -17604,7 +16617,7 @@
         <v>45334</v>
       </c>
       <c r="D110" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E110" t="n">
         <v>0.7</v>
@@ -17693,7 +16706,7 @@
         <v>45334</v>
       </c>
       <c r="D111" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E111" t="n">
         <v>1.35</v>
@@ -17782,7 +16795,7 @@
         <v>45334</v>
       </c>
       <c r="D112" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -17871,7 +16884,7 @@
         <v>45334</v>
       </c>
       <c r="D113" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -17960,7 +16973,7 @@
         <v>45334</v>
       </c>
       <c r="D114" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E114" t="n">
         <v>4</v>
@@ -18049,7 +17062,7 @@
         <v>45335</v>
       </c>
       <c r="D115" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -18138,7 +17151,7 @@
         <v>45335</v>
       </c>
       <c r="D116" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E116" t="n">
         <v>0.9</v>
@@ -18227,7 +17240,7 @@
         <v>45335</v>
       </c>
       <c r="D117" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E117" t="n">
         <v>1.8</v>
@@ -18316,7 +17329,7 @@
         <v>45335</v>
       </c>
       <c r="D118" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -18405,7 +17418,7 @@
         <v>45335</v>
       </c>
       <c r="D119" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E119" t="n">
         <v>1.05</v>
@@ -18494,7 +17507,7 @@
         <v>45335</v>
       </c>
       <c r="D120" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E120" t="n">
         <v>2.15</v>
